--- a/Note/输出.xlsx
+++ b/Note/输出.xlsx
@@ -1011,7 +1011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H92"/>
+  <dimension ref="A1:H63"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.888888888888889" defaultRowHeight="14.4"/>
   <cols>
     <col width="9.66666666666667" customWidth="1" style="1" min="1" max="1"/>
@@ -1024,31 +1024,31 @@
         <v/>
       </c>
       <c r="B1" s="3">
-        <f>COUNTA(B2:B2128)/COLUMN()</f>
+        <f>COUNTA(B2:B2192)/COLUMN()</f>
         <v/>
       </c>
       <c r="C1" s="3">
-        <f>COUNTA(C2:C2128)/COLUMN()</f>
+        <f>COUNTA(C2:C2192)/COLUMN()</f>
         <v/>
       </c>
       <c r="D1" s="3">
-        <f>COUNTA(D2:D2128)/COLUMN()</f>
+        <f>COUNTA(D2:D2192)/COLUMN()</f>
         <v/>
       </c>
       <c r="E1" s="3">
-        <f>COUNTA(E2:E2128)/COLUMN()</f>
+        <f>COUNTA(E2:E2192)/COLUMN()</f>
         <v/>
       </c>
       <c r="F1" s="3">
-        <f>COUNTA(F2:F2128)/COLUMN()</f>
+        <f>COUNTA(F2:F2192)/COLUMN()</f>
         <v/>
       </c>
       <c r="G1" s="3">
-        <f>COUNTA(G2:G2128)/COLUMN()</f>
+        <f>COUNTA(G2:G2192)/COLUMN()</f>
         <v/>
       </c>
       <c r="H1" s="3">
-        <f>COUNTA(H2:H2128)/COLUMN()</f>
+        <f>COUNTA(H2:H2192)/COLUMN()</f>
         <v/>
       </c>
     </row>
@@ -1059,637 +1059,434 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>无论是齐次还是非齐次线性方程组，只要系数阵###满秩###（填写矩阵性质），那么解的情况就是唯一的。### ###</t>
+          <t>统筹好###有为政府与有效市场的关系###（填写关键关系）是破除内卷是竞争的关键### ###</t>
         </is>
       </c>
     </row>
     <row r="3" customFormat="1" s="1">
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>###自由变量###（填写变量类型）没了，解就被限定住了</t>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>汇率政策不能###完全市场化###（填写政策限制），亚洲金融危机有前车之鉴### ###</t>
         </is>
       </c>
     </row>
     <row r="4" customFormat="1" s="1">
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>对齐次来说就只有###0解###（填写解的类型）</t>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>###两新两重###（填写政策简称）### ###</t>
         </is>
       </c>
     </row>
     <row r="5" customFormat="1" s="1">
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>对非齐次来说就失去了齐次通解的部分，只有唯一一个###特解###（填写解的类型）</t>
+          <t>###设备更新和消费品以旧换新###（填写两新内容）</t>
         </is>
       </c>
     </row>
     <row r="6" customFormat="1" s="1">
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>###自由变量的个数###（填写变量属性）是固定的，但是选取是不固定的### ###</t>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>###重大战略实施和重点领域安全能力建设###（填写两重内容）</t>
         </is>
       </c>
     </row>
     <row r="7" customFormat="1" s="1">
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>系数阵###m*n###（填写矩阵维度），也就是m行n列，列对应变量，看作实际的维度### ###</t>
+          <t>###财产性收入###（填写收入类型）### ###</t>
         </is>
       </c>
     </row>
     <row r="8" customFormat="1" s="1">
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>###秩等于n###（填写矩阵条件），也就是说，哪怕行m大于n，实际有效的也就只有其中n行</t>
+          <t>居民依托"动产"、"不动产"的所有权，赚到的###租金###（填写收入形式）</t>
         </is>
       </c>
     </row>
     <row r="9" customFormat="1" s="1">
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>秩大于n是不可能的，因为###秩小于等于行列数中较小的那一个###（填写秩的性质）</t>
+          <t>分类：金融资产收益、不动产收益、知识产权、财产增值</t>
         </is>
       </c>
     </row>
     <row r="10" customFormat="1" s="1">
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>唯一解方程暗示r(A)=n，克拉默使用条件满足，如果只求解坐标的其中一个分量，那就一定是###克拉默###（填写定理名称）### ###</t>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>按要素分配中的###资本要素###（填写要素类型）分配，属于此次分配领域</t>
         </is>
       </c>
     </row>
     <row r="11" customFormat="1" s="1">
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>当###A和B不是方阵###（填写矩阵类型）时，AB也许可逆，但是A和B不可逆</t>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>核心特征：###非劳动性###（填写特征）</t>
         </is>
       </c>
     </row>
     <row r="12" customFormat="1" s="1">
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>乘积矩阵的维度若大于两个矩阵的秩，###必非满秩###（填写矩阵性质）</t>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>我国现阶段的###分配方式###（填写经济制度）### ###</t>
         </is>
       </c>
     </row>
     <row r="13" customFormat="1" s="1">
-      <c r="D13" s="1" t="inlineStr">
-        <is>
-          <t>如果高矩阵*宽矩阵，那么###必非满秩###（填写矩阵性质）</t>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>核心：###按劳分配为主体，多重分配方式并存###（填写分配原则）</t>
         </is>
       </c>
     </row>
     <row r="14" customFormat="1" s="1">
-      <c r="D14" s="1" t="inlineStr">
-        <is>
-          <t>如果宽矩阵*高矩阵，那么###可能满秩###（填写矩阵性质）</t>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>###三次分配体系###（填写分配体系）</t>
         </is>
       </c>
     </row>
     <row r="15" customFormat="1" s="1">
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>幂零矩阵的要求：存在正整数###k###（填写指数）使得A^k=零矩阵### ###</t>
+      <c r="D15" s="1" t="inlineStr">
+        <is>
+          <t>初次分配：生产领域中###按生产要素分配###（填写分配方式），直接与效率挂钩</t>
         </is>
       </c>
     </row>
     <row r="16" customFormat="1" s="1">
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>如果次数n小于k，###A^n为非零矩阵###（填写矩阵类型）</t>
+      <c r="E16" s="1" t="inlineStr">
+        <is>
+          <t>按劳分配、按要素分配、经营性收入</t>
         </is>
       </c>
     </row>
     <row r="17" customFormat="1" s="1">
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>只有次数n大于k，###A^n为零矩阵###（填写矩阵类型）</t>
+      <c r="F17" s="1" t="inlineStr">
+        <is>
+          <t>按劳分配仅限###公有制经济###（填写经济类型）</t>
         </is>
       </c>
     </row>
     <row r="18" customFormat="1" s="1">
-      <c r="B18" s="1" t="inlineStr">
-        <is>
-          <t>###r(X)+r(Y)&gt;=r(X+Y)###（填写秩的关系）### ###</t>
+      <c r="F18" s="1" t="inlineStr">
+        <is>
+          <t>按要素分配的要素：###劳动、资本、土地、技术、管理、数据###（填写要素种类）</t>
         </is>
       </c>
     </row>
     <row r="19" customFormat="1" s="1">
-      <c r="B19" s="1" t="inlineStr">
-        <is>
-          <t>商品生产者的劳动的社会性质是###社会分工###（填写决定因素）决定的### ###</t>
+      <c r="D19" s="1" t="inlineStr">
+        <is>
+          <t>再分配：政府宏观调控控制收入差距，侧重###公平###（填写分配原则）</t>
         </is>
       </c>
     </row>
     <row r="20" customFormat="1" s="1">
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>社会主义改造基本完成后的外交策略### ###</t>
+      <c r="E20" s="1" t="inlineStr">
+        <is>
+          <t>###税收、转移支付###（填写再分配手段）</t>
         </is>
       </c>
     </row>
     <row r="21" customFormat="1" s="1">
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>时间是###1950s-1970s###（填写年代）</t>
+      <c r="D21" s="1" t="inlineStr">
+        <is>
+          <t>第三次分配：基于###道德自愿###（填写分配基础）的慈善捐赠、公益帮扶，是前两次分配的补充</t>
         </is>
       </c>
     </row>
     <row r="22" customFormat="1" s="1">
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>50-60年代中期，毛泽东提出###两个中间地带战略###（填写毛泽东的战略）</t>
+      <c r="B22" s="1" t="inlineStr">
+        <is>
+          <t>乡村全面振兴的###底线任务###（填写任务类型）### ###</t>
         </is>
       </c>
     </row>
     <row r="23" customFormat="1" s="1">
-      <c r="D23" s="1" t="inlineStr">
-        <is>
-          <t>亚洲、非洲、拉丁美洲广大经济落后的国家</t>
+      <c r="C23" s="1" t="inlineStr">
+        <is>
+          <t>持续增强###粮食等重要农产品的攻击保障能力###（填写底线任务）</t>
         </is>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
-      <c r="D24" s="1" t="inlineStr">
-        <is>
-          <t>欧洲、北美、大洋洲等发达资本主义国家，及部分东欧国家</t>
+      <c r="C24" s="1" t="inlineStr">
+        <is>
+          <t>持续###巩固拓展脱贫攻坚成果###（填写底线任务）</t>
         </is>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
-      <c r="D25" s="1" t="inlineStr">
-        <is>
-          <t>中国不属于这两个，但是依靠第一个，争取第二个</t>
+      <c r="B25" s="1" t="inlineStr">
+        <is>
+          <t>巩固和完善农村基本经营制度并不要求在土地承包到期后###打乱重分###（填写政策要求）### ###</t>
         </is>
       </c>
     </row>
     <row r="26" customFormat="1" s="1">
       <c r="C26" s="1" t="inlineStr">
         <is>
-          <t>70年代前期，毛泽东提出###“三个世界”划分###（填写毛泽东的划分）</t>
+          <t>底线三条：###土地公有、耕地红线、农民利益不受损###（填写底线内容）</t>
         </is>
       </c>
     </row>
     <row r="27" customFormat="1" s="1">
-      <c r="D27" s="1" t="inlineStr">
-        <is>
-          <t>美苏</t>
+      <c r="B27" s="1" t="inlineStr">
+        <is>
+          <t>乡村全面振兴的重点（三个水平）是###提升乡村产业发展水平###（填写重点内容）### ###</t>
         </is>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
-      <c r="D28" s="1" t="inlineStr">
-        <is>
-          <t>美苏间的发达国家，欧洲、日本、加拿大、澳大利亚</t>
+      <c r="C28" s="1" t="inlineStr">
+        <is>
+          <t>###提升乡村产业发展水平###（填写振兴重点）</t>
         </is>
       </c>
     </row>
     <row r="29" customFormat="1" s="1">
-      <c r="D29" s="1" t="inlineStr">
-        <is>
-          <t>亚洲（除日本）、非洲、拉丁美洲和其它地区，包括中国</t>
+      <c r="C29" s="1" t="inlineStr">
+        <is>
+          <t>###提升乡村建设水平###（填写振兴重点）</t>
         </is>
       </c>
     </row>
     <row r="30" customFormat="1" s="1">
-      <c r="B30" s="1" t="inlineStr">
-        <is>
-          <t>中国经济长期稳定发展的强大引擎是### ###</t>
+      <c r="C30" s="1" t="inlineStr">
+        <is>
+          <t>###提升乡村治理水平###（填写振兴重点）</t>
         </is>
       </c>
     </row>
     <row r="31" customFormat="1" s="1">
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>###超大规模市场###（填写经济引擎）</t>
+      <c r="B31" s="1" t="inlineStr">
+        <is>
+          <t>三农工作的底线任务是###确保国家粮食安全和不发生规模性返贫致贫###（填写底线任务）### ###</t>
         </is>
       </c>
     </row>
     <row r="32" customFormat="1" s="1">
-      <c r="C32" s="1" t="inlineStr">
-        <is>
-          <t>###创新驱动发展###（填写发展动力）</t>
+      <c r="B32" s="1" t="inlineStr">
+        <is>
+          <t>抓产业创新要###守牢实体经济这个根基###（填写创新要求）### ###</t>
         </is>
       </c>
     </row>
     <row r="33" customFormat="1" s="1">
       <c r="C33" s="1" t="inlineStr">
         <is>
-          <t>###相互促进、良性循环###（填写循环特点）</t>
+          <t>###守牢实体经济这个根基###（填写产业创新要求）</t>
         </is>
       </c>
     </row>
     <row r="34" customFormat="1" s="1">
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t>建设高质量教育体系，办好人民满意的教育，根本在于### ###</t>
+      <c r="C34" s="1" t="inlineStr">
+        <is>
+          <t>坚持推动###传统产业改造升级和开辟战略性新兴产业、未来产业新赛道并重###（填写产业创新路径）</t>
         </is>
       </c>
     </row>
     <row r="35" customFormat="1" s="1">
-      <c r="C35" s="1" t="inlineStr">
-        <is>
-          <t>###深化教育综合改革###（填写教育根本）</t>
+      <c r="B35" s="1" t="inlineStr">
+        <is>
+          <t>中国特色现代企业制度的基础是###产权清晰###（填写制度基础）### ###</t>
         </is>
       </c>
     </row>
     <row r="36" customFormat="1" s="1">
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>洋务派优先集中发展军事工业，官办企业是辅助的### ###</t>
+      <c r="C36" s="1" t="inlineStr">
+        <is>
+          <t>###产权清晰###（填写企业制度基础）</t>
         </is>
       </c>
     </row>
     <row r="37" customFormat="1" s="1">
       <c r="C37" s="1" t="inlineStr">
         <is>
-          <t>为军事工业提供###配套支持和资金支持###（填写官办企业作用）</t>
+          <t>###权责明确###（填写企业制度基础）</t>
         </is>
       </c>
     </row>
     <row r="38" customFormat="1" s="1">
-      <c r="B38" s="1" t="inlineStr">
-        <is>
-          <t>《中共抗日救国十大纲领》、《中共中央关于目前形势与党的任务的决定》### ###</t>
+      <c r="C38" s="1" t="inlineStr">
+        <is>
+          <t>###政企分开###（填写企业制度基础）</t>
         </is>
       </c>
     </row>
     <row r="39" customFormat="1" s="1">
       <c r="C39" s="1" t="inlineStr">
         <is>
-          <t>###洛川会议###（填写会议名称），1937年8月</t>
+          <t>###管理科学###（填写企业制度基础）</t>
         </is>
       </c>
     </row>
     <row r="40" customFormat="1" s="1">
-      <c r="C40" s="1" t="inlineStr">
-        <is>
-          <t>标志着党的###全面抗战路线###（填写路线名称）的正式形成</t>
+      <c r="B40" s="1" t="inlineStr">
+        <is>
+          <t>完善企业制度###与社会治理无关###（填写制度特点）### ###</t>
         </is>
       </c>
     </row>
     <row r="41" customFormat="1" s="1">
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>二战胜利成果的集中体现是以联合国为核心的国际体系### ###</t>
+          <t>人大代表不是由选民###直接选举###（填写选举方式）产生### ###</t>
         </is>
       </c>
     </row>
     <row r="42" customFormat="1" s="1">
-      <c r="B42" s="1" t="inlineStr">
-        <is>
-          <t>认识发展的动力### ###</t>
+      <c r="C42" s="1" t="inlineStr">
+        <is>
+          <t>###县乡两级人大代表###（填写选举级别）直接选举</t>
         </is>
       </c>
     </row>
     <row r="43" customFormat="1" s="1">
       <c r="C43" s="1" t="inlineStr">
         <is>
-          <t>根本动力：###实践###（填写根本动力）</t>
+          <t>###县级以上人大###（填写选举级别）由下级人大代表间接选举产生</t>
         </is>
       </c>
     </row>
     <row r="44" customFormat="1" s="1">
-      <c r="C44" s="1" t="inlineStr">
-        <is>
-          <t>强大动力：###认识工具###（填写强大动力）</t>
+      <c r="B44" s="1" t="inlineStr">
+        <is>
+          <t>###变通执行权###（填写特殊权力）### ###</t>
         </is>
       </c>
     </row>
     <row r="45" customFormat="1" s="1">
-      <c r="B45" s="1" t="inlineStr">
-        <is>
-          <t>事物的固有联系是不会被技术手段改变的，技术手段只是发现和利用固有联系### ###</t>
+      <c r="C45" s="1" t="inlineStr">
+        <is>
+          <t>###特定地方国家机关###（填写权力主体）</t>
         </is>
       </c>
     </row>
     <row r="46" customFormat="1" s="1">
-      <c r="B46" s="1" t="inlineStr">
-        <is>
-          <t>价值评价的反映内容：客体对主体有什么用？### ###</t>
+      <c r="C46" s="1" t="inlineStr">
+        <is>
+          <t>在不违背###宪法、法律、行政法规基本原则###（填写前提条件）的前提下</t>
         </is>
       </c>
     </row>
     <row r="47" customFormat="1" s="1">
       <c r="C47" s="1" t="inlineStr">
         <is>
-          <t>离我而去的人，与死者何异？</t>
+          <t>针对###本地区特殊情况###（填写适用条件）</t>
         </is>
       </c>
     </row>
     <row r="48" customFormat="1" s="1">
-      <c r="B48" s="1" t="inlineStr">
-        <is>
-          <t>国家资本所有制的特点### ###</t>
+      <c r="C48" s="1" t="inlineStr">
+        <is>
+          <t>对上级制定的政策、法律、法规作出灵活调整并执行的权力</t>
         </is>
       </c>
     </row>
     <row r="49" customFormat="1" s="1">
-      <c r="C49" s="1" t="inlineStr">
-        <is>
-          <t>所有权与出资主体是###国家###（填写所有权主体）</t>
+      <c r="B49" s="1" t="inlineStr">
+        <is>
+          <t>引领发展的第一动力是###创新###（填写发展动力）### ###</t>
         </is>
       </c>
     </row>
     <row r="50" customFormat="1" s="1">
-      <c r="C50" s="1" t="inlineStr">
-        <is>
-          <t>经营管理采用###委托代理制###（填写经营方式）</t>
+      <c r="B50" s="1" t="inlineStr">
+        <is>
+          <t>###《新时代的中国国家安全》###（填写文件名称）### ###</t>
         </is>
       </c>
     </row>
     <row r="51" customFormat="1" s="1">
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t>根本目的：###维护资本主义制度和垄断资本利益###（填写根本目的）</t>
+          <t>###捍卫国家利益的坚定力量###（填写国家形象）</t>
         </is>
       </c>
     </row>
     <row r="52" customFormat="1" s="1">
       <c r="C52" s="1" t="inlineStr">
         <is>
-          <t>主要存在于###经济命脉、公共利益或战略利益的领域###（填写主要领域）</t>
+          <t>###维护世界和平稳定的正义力量###（填写国家形象）</t>
         </is>
       </c>
     </row>
     <row r="53" customFormat="1" s="1">
-      <c r="D53" s="1" t="inlineStr">
-        <is>
-          <t>不赚钱但是必须有人做的事</t>
+      <c r="C53" s="1" t="inlineStr">
+        <is>
+          <t>###维护国际公平正义的进步力量###（填写国家形象）</t>
         </is>
       </c>
     </row>
     <row r="54" customFormat="1" s="1">
       <c r="C54" s="1" t="inlineStr">
         <is>
-          <t>不是###资本主义所有制的主体###（填写所有制主体）</t>
+          <t>###促进全球共同发展的建设力量###（填写国家形象）</t>
         </is>
       </c>
     </row>
     <row r="55" customFormat="1" s="1">
-      <c r="D55" s="1" t="inlineStr">
-        <is>
-          <t>主体是###法人资本所有制###（填写主体类型）</t>
+      <c r="B55" s="1" t="inlineStr">
+        <is>
+          <t>总体国家安全观是当代中国对世界的###重要思想理论贡献###（填写理论地位）### ###</t>
         </is>
       </c>
     </row>
     <row r="56" customFormat="1" s="1">
-      <c r="C56" s="1" t="inlineStr">
-        <is>
-          <t>稳定经济、保障公共利益、支持战略产业</t>
+      <c r="B56" s="1" t="inlineStr">
+        <is>
+          <t>###KMP算法###（填写算法名称）### ###</t>
         </is>
       </c>
     </row>
     <row r="57" customFormat="1" s="1">
       <c r="C57" s="1" t="inlineStr">
         <is>
-          <t>维护垄断、加重财政负担、无法解决根本矛盾</t>
+          <t>主串指针###不动###（填写指针行为），模式串指针动</t>
         </is>
       </c>
     </row>
     <row r="58" customFormat="1" s="1">
       <c r="C58" s="1" t="inlineStr">
         <is>
-          <t>体现###总资本家剥削雇佣劳动者的关系###（填写体现关系）</t>
+          <t>模式串的###next[j]数组###（填写关键数组）记录失配后模式串指针跳转位置</t>
         </is>
       </c>
     </row>
     <row r="59" customFormat="1" s="1">
-      <c r="B59" s="1" t="inlineStr">
-        <is>
-          <t>科学社会主义的理论基石的是唯物史观和剩余价值学说### ###</t>
+      <c r="C59" s="1" t="inlineStr">
+        <is>
+          <t>next[j]的生成</t>
         </is>
       </c>
     </row>
     <row r="60" customFormat="1" s="1">
-      <c r="B60" s="1" t="inlineStr">
-        <is>
-          <t>古田会议### ###</t>
+      <c r="D60" s="1" t="inlineStr">
+        <is>
+          <t>取最后一个字符是模式串下标###j-1###（填写下标位置）字符的模式子串</t>
         </is>
       </c>
     </row>
     <row r="61" customFormat="1" s="1">
-      <c r="C61" s="1" t="inlineStr">
-        <is>
-          <t>确立###党对军队绝对领导###（填写古田会议内容）</t>
+      <c r="D61" s="1" t="inlineStr">
+        <is>
+          <t>求出这个模式子串的前后缀</t>
         </is>
       </c>
     </row>
     <row r="62" customFormat="1" s="1">
-      <c r="C62" s="1" t="inlineStr">
-        <is>
-          <t>纠正###红军错误思想###（填写古田会议内容）</t>
+      <c r="E62" s="1" t="inlineStr">
+        <is>
+          <t>注意，前后缀不包括模式子串本身，不然长度必然是模式子串的长度</t>
         </is>
       </c>
     </row>
     <row r="63" customFormat="1" s="1">
-      <c r="C63" s="1" t="inlineStr">
-        <is>
-          <t>制定###红军建设的各项纲领###（填写古田会议内容）</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" customFormat="1" s="1">
-      <c r="C64" s="1" t="inlineStr">
-        <is>
-          <t>确立###思想建党、政治建军原则###（填写古田会议内容）</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" customFormat="1" s="1">
-      <c r="C65" s="1" t="inlineStr">
-        <is>
-          <t>规定红军是一个###执行革命的政治任务的武装集团###（填写古田会议内容）</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" customFormat="1" s="1">
-      <c r="B66" s="1" t="inlineStr">
-        <is>
-          <t>加强党的思想建设的极端重要性### ###</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" customFormat="1" s="1">
-      <c r="C67" s="1" t="inlineStr">
-        <is>
-          <t>出自六届六中全会的###《论新阶段》###（填写文献名称）</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" customFormat="1" s="1">
-      <c r="B68" s="1" t="inlineStr">
-        <is>
-          <t>构建新发展格局加快推动高质量发展### ###</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" customFormat="1" s="1">
-      <c r="C69" s="1" t="inlineStr">
-        <is>
-          <t>###扩大内需###（填写构建新发展格局方式）</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" customFormat="1" s="1">
-      <c r="C70" s="1" t="inlineStr">
-        <is>
-          <t>###创新驱动发展###（填写构建新发展格局方式）</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" customFormat="1" s="1">
-      <c r="C71" s="1" t="inlineStr">
-        <is>
-          <t>###高水平开放###（填写构建新发展格局方式）</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" customFormat="1" s="1">
-      <c r="C72" s="1" t="inlineStr">
-        <is>
-          <t>###安全保障###（填写构建新发展格局方式）</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" customFormat="1" s="1">
-      <c r="B73" s="1" t="inlineStr">
-        <is>
-          <t>内卷为何削弱行业整体竞争力### ###</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" customFormat="1" s="1">
-      <c r="C74" s="1" t="inlineStr">
-        <is>
-          <t>###资源错配###（填写内卷影响）（资源向低价倾销倾斜，质量降低）</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" customFormat="1" s="1">
-      <c r="C75" s="1" t="inlineStr">
-        <is>
-          <t>###创新动力枯竭###（填写内卷影响）（创新的风险性太大）</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" customFormat="1" s="1">
-      <c r="C76" s="1" t="inlineStr">
-        <is>
-          <t>###利润空间压缩###（填写内卷影响）（加重企业经济负担，缺乏资金，就无法提供优质的产品）</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" customFormat="1" s="1">
-      <c r="C77" s="1" t="inlineStr">
-        <is>
-          <t>###行业生态恶化###（填写内卷影响）（透支消费者信任，A家造假，也怕B家）</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" customFormat="1" s="1">
-      <c r="B78" s="1" t="inlineStr">
-        <is>
-          <t>中国特色社会主义文化建设的根本方向是### ###</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" customFormat="1" s="1">
-      <c r="C79" s="1" t="inlineStr">
-        <is>
-          <t>###坚持马克思主义指导###（填写文化建设方向）</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" customFormat="1" s="1">
-      <c r="C80" s="1" t="inlineStr">
-        <is>
-          <t>###坚持为人民服务、为社会主义服务###（填写文化建设方向）</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" customFormat="1" s="1">
-      <c r="B81" s="1" t="inlineStr">
-        <is>
-          <t>抗战胜利是中华民族从近代以来陷入深重危机走向伟大复兴的历史转折点### ###</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" customFormat="1" s="1">
-      <c r="B82" s="1" t="inlineStr">
-        <is>
-          <t>新民主主义社会：1949-1956### ###</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" customFormat="1" s="1">
-      <c r="C83" s="1" t="inlineStr">
-        <is>
-          <t>###三大改造完成前###（填写新民主主义社会时间）</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" customFormat="1" s="1">
-      <c r="B84" s="1" t="inlineStr">
-        <is>
-          <t>长征的胜利是中国革命转危为安的关键### ###</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" customFormat="1" s="1">
-      <c r="B85" s="1" t="inlineStr">
-        <is>
-          <t>没有信念的理想不叫作理想，而叫作空想（可行）或幻想（不可行）### ###</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" customFormat="1" s="1">
-      <c r="C86" s="1" t="inlineStr">
-        <is>
-          <t>即使盲信，不具备可行性的想法不是理想，而是###“有信念的幻想”###（填写理想类型）</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" customFormat="1" s="1">
-      <c r="C87" s="1" t="inlineStr">
-        <is>
-          <t>因此，理想和信念总是###相互依存###（填写理想和信念关系）</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" customFormat="1" s="1">
-      <c r="B88" s="1" t="inlineStr">
-        <is>
-          <t>信仰和信念的区别：前者具体，后者抽象，前者细微，后者宏大，前者零散，后者系统### ###</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" customFormat="1" s="1">
-      <c r="B89" s="1" t="inlineStr">
-        <is>
-          <t>坚持依法治国和以德治国相结合，需要### ###</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" customFormat="1" s="1">
-      <c r="C90" s="1" t="inlineStr">
-        <is>
-          <t>###运用法治手段解决道德领域突出问题###（填写依法治国和以德治国结合方式）</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" customFormat="1" s="1">
-      <c r="C91" s="1" t="inlineStr">
-        <is>
-          <t>###强化道德对法治的支撑作用###（填写依法治国和以德治国结合方式）</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" customFormat="1" s="1">
-      <c r="C92" s="1" t="inlineStr">
-        <is>
-          <t>###在立法、执法、司法中都体现社会主义道德要求###（填写依法治国和以德治国结合方式）</t>
+      <c r="D63" s="1" t="inlineStr">
+        <is>
+          <t>前缀和后缀的交集中选择###最长的那个###（填写选择条件），取它的长度作为next[j]的元素</t>
         </is>
       </c>
     </row>

--- a/Note/输出.xlsx
+++ b/Note/输出.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="22188" windowHeight="9180" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="23040" windowHeight="9180" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待处理" sheetId="1" state="visible" r:id="rId1"/>
@@ -1011,7 +1011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H63"/>
+  <dimension ref="A1:H153"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.888888888888889" defaultRowHeight="14.4"/>
   <cols>
     <col width="9.66666666666667" customWidth="1" style="1" min="1" max="1"/>
@@ -1024,31 +1024,31 @@
         <v/>
       </c>
       <c r="B1" s="3">
-        <f>COUNTA(B2:B2192)/COLUMN()</f>
+        <f>COUNTA(B2:B1805)/COLUMN()</f>
         <v/>
       </c>
       <c r="C1" s="3">
-        <f>COUNTA(C2:C2192)/COLUMN()</f>
+        <f>COUNTA(C2:C1805)/COLUMN()</f>
         <v/>
       </c>
       <c r="D1" s="3">
-        <f>COUNTA(D2:D2192)/COLUMN()</f>
+        <f>COUNTA(D2:D1805)/COLUMN()</f>
         <v/>
       </c>
       <c r="E1" s="3">
-        <f>COUNTA(E2:E2192)/COLUMN()</f>
+        <f>COUNTA(E2:E1805)/COLUMN()</f>
         <v/>
       </c>
       <c r="F1" s="3">
-        <f>COUNTA(F2:F2192)/COLUMN()</f>
+        <f>COUNTA(F2:F1805)/COLUMN()</f>
         <v/>
       </c>
       <c r="G1" s="3">
-        <f>COUNTA(G2:G2192)/COLUMN()</f>
+        <f>COUNTA(G2:G1805)/COLUMN()</f>
         <v/>
       </c>
       <c r="H1" s="3">
-        <f>COUNTA(H2:H2192)/COLUMN()</f>
+        <f>COUNTA(H2:H1805)/COLUMN()</f>
         <v/>
       </c>
     </row>
@@ -1059,434 +1059,1064 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>统筹好###有为政府与有效市场的关系###（填写关键关系）是破除内卷是竞争的关键### ###</t>
+          <t>绿色发展（绿水青山就是金山银山）为何成为共识### ###</t>
         </is>
       </c>
     </row>
     <row r="3" customFormat="1" s="1">
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>汇率政策不能###完全市场化###（填写政策限制），亚洲金融危机有前车之鉴### ###</t>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>第一，以“两个结合”继承发展了马克思主义生态观和发展观</t>
         </is>
       </c>
     </row>
     <row r="4" customFormat="1" s="1">
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>###两新两重###（填写政策简称）### ###</t>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>根植于中华民族深厚的###生态文化基因###（填写绿色发展的文化基础）</t>
         </is>
       </c>
     </row>
     <row r="5" customFormat="1" s="1">
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>###设备更新和消费品以旧换新###（填写两新内容）</t>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>彰显###时代价值###（填写绿色发展彰显的价值）</t>
         </is>
       </c>
     </row>
     <row r="6" customFormat="1" s="1">
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>###重大战略实施和重点领域安全能力建设###（填写两重内容）</t>
+          <t>第二，指引新时代###生态文明建设###（填写绿色发展指引的建设领域）取得举世瞩目成就</t>
         </is>
       </c>
     </row>
     <row r="7" customFormat="1" s="1">
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>###财产性收入###（填写收入类型）### ###</t>
+      <c r="D7" s="1" t="inlineStr">
+        <is>
+          <t>新时代党和国家事业###历史性成就与变革###（填写绿色发展成就的性质）的显著标志</t>
         </is>
       </c>
     </row>
     <row r="8" customFormat="1" s="1">
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>居民依托"动产"、"不动产"的所有权，赚到的###租金###（填写收入形式）</t>
+          <t>第三，实现了对###西方传统发展范式###（填写超越的对象）的历史性超越</t>
         </is>
       </c>
     </row>
     <row r="9" customFormat="1" s="1">
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>分类：金融资产收益、不动产收益、知识产权、财产增值</t>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t>以这一理念为指引，建设###人与自然和谐共生###（填写建设的现代化类型）的现代化</t>
         </is>
       </c>
     </row>
     <row r="10" customFormat="1" s="1">
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>按要素分配中的###资本要素###（填写要素类型）分配，属于此次分配领域</t>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>开创了###人类文明新形态###（填写开创的文明形态）</t>
         </is>
       </c>
     </row>
     <row r="11" customFormat="1" s="1">
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>核心特征：###非劳动性###（填写特征）</t>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>“两山”是中国的，也是世界的### ###</t>
         </is>
       </c>
     </row>
     <row r="12" customFormat="1" s="1">
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>我国现阶段的###分配方式###（填写经济制度）### ###</t>
+      <c r="D12" s="1" t="inlineStr">
+        <is>
+          <t>“两山”理念为全球生态治理和实现联合国可持续发展目标提供了中国方案</t>
         </is>
       </c>
     </row>
     <row r="13" customFormat="1" s="1">
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>核心：###按劳分配为主体，多重分配方式并存###（填写分配原则）</t>
+      <c r="E13" s="1" t="inlineStr">
+        <is>
+          <t>“两山”理念科学回应生态文明世界之问</t>
         </is>
       </c>
     </row>
     <row r="14" customFormat="1" s="1">
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>###三次分配体系###（填写分配体系）</t>
+      <c r="E14" s="1" t="inlineStr">
+        <is>
+          <t>高度契合###全球绿色发展理念###（填写契合的理念）</t>
         </is>
       </c>
     </row>
     <row r="15" customFormat="1" s="1">
-      <c r="D15" s="1" t="inlineStr">
-        <is>
-          <t>初次分配：生产领域中###按生产要素分配###（填写分配方式），直接与效率挂钩</t>
+      <c r="E15" s="1" t="inlineStr">
+        <is>
+          <t>深刻启迪###全球生态文明建设###（填写启迪的领域）</t>
         </is>
       </c>
     </row>
     <row r="16" customFormat="1" s="1">
       <c r="E16" s="1" t="inlineStr">
         <is>
-          <t>按劳分配、按要素分配、经营性收入</t>
+          <t>凝聚了###全球绿色共识###（填写凝聚的共识类型）</t>
         </is>
       </c>
     </row>
     <row r="17" customFormat="1" s="1">
-      <c r="F17" s="1" t="inlineStr">
-        <is>
-          <t>按劳分配仅限###公有制经济###（填写经济类型）</t>
+      <c r="D17" s="1" t="inlineStr">
+        <is>
+          <t>在实践上，“两山”理念指引开创人类文明新形态</t>
         </is>
       </c>
     </row>
     <row r="18" customFormat="1" s="1">
-      <c r="F18" s="1" t="inlineStr">
-        <is>
-          <t>按要素分配的要素：###劳动、资本、土地、技术、管理、数据###（填写要素种类）</t>
+      <c r="E18" s="1" t="inlineStr">
+        <is>
+          <t>破解全球可持续发展面临的###两难困境###（填写破解的困境类型）</t>
         </is>
       </c>
     </row>
     <row r="19" customFormat="1" s="1">
-      <c r="D19" s="1" t="inlineStr">
-        <is>
-          <t>再分配：政府宏观调控控制收入差距，侧重###公平###（填写分配原则）</t>
+      <c r="E19" s="1" t="inlineStr">
+        <is>
+          <t>激发###绿色转型###（填写激发的转型类型）活力</t>
         </is>
       </c>
     </row>
     <row r="20" customFormat="1" s="1">
       <c r="E20" s="1" t="inlineStr">
         <is>
-          <t>###税收、转移支付###（填写再分配手段）</t>
+          <t>引领###全球环境治理###（填写引领的治理领域）</t>
         </is>
       </c>
     </row>
     <row r="21" customFormat="1" s="1">
-      <c r="D21" s="1" t="inlineStr">
-        <is>
-          <t>第三次分配：基于###道德自愿###（填写分配基础）的慈善捐赠、公益帮扶，是前两次分配的补充</t>
+      <c r="E21" s="1" t="inlineStr">
+        <is>
+          <t>共建绿色“一带一路”</t>
         </is>
       </c>
     </row>
     <row r="22" customFormat="1" s="1">
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>乡村全面振兴的###底线任务###（填写任务类型）### ###</t>
+      <c r="E22" s="1" t="inlineStr">
+        <is>
+          <t>推动共建###地球生命共同体###（填写推动共建的共同体类型）</t>
         </is>
       </c>
     </row>
     <row r="23" customFormat="1" s="1">
-      <c r="C23" s="1" t="inlineStr">
-        <is>
-          <t>持续增强###粮食等重要农产品的攻击保障能力###（填写底线任务）</t>
+      <c r="D23" s="1" t="inlineStr">
+        <is>
+          <t>“两山”理念不仅深刻改变了中国，也深刻影响了世界。</t>
         </is>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
-      <c r="C24" s="1" t="inlineStr">
-        <is>
-          <t>持续###巩固拓展脱贫攻坚成果###（填写底线任务）</t>
+      <c r="B24" s="1" t="inlineStr">
+        <is>
+          <t>中国命运转变的关键### ###</t>
         </is>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
-      <c r="B25" s="1" t="inlineStr">
-        <is>
-          <t>巩固和完善农村基本经营制度并不要求在土地承包到期后###打乱重分###（填写政策要求）### ###</t>
+      <c r="C25" s="1" t="inlineStr">
+        <is>
+          <t>###中国共产党###（填写在民族危亡关头挺身担当的政党）在民族危亡关头挺身担当</t>
         </is>
       </c>
     </row>
     <row r="26" customFormat="1" s="1">
-      <c r="C26" s="1" t="inlineStr">
-        <is>
-          <t>底线三条：###土地公有、耕地红线、农民利益不受损###（填写底线内容）</t>
+      <c r="D26" s="1" t="inlineStr">
+        <is>
+          <t>始终发挥###中流砥柱###（填写发挥的作用类型）作用</t>
         </is>
       </c>
     </row>
     <row r="27" customFormat="1" s="1">
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>乡村全面振兴的重点（三个水平）是###提升乡村产业发展水平###（填写重点内容）### ###</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" customFormat="1" s="1">
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>###提升乡村产业发展水平###（填写振兴重点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" customFormat="1" s="1">
+      <c r="D27" s="1" t="inlineStr">
+        <is>
+          <t>以###政治主张、坚定意志和模范行动###（填写支撑希望的要素）支撑起民族救亡图存的希望</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="D28" s="1" t="inlineStr">
+        <is>
+          <t>成为夺取战争胜利的###民族先锋###（填写党的历史角色）</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
       <c r="C29" s="1" t="inlineStr">
         <is>
-          <t>###提升乡村建设水平###（填写振兴重点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" customFormat="1" s="1">
-      <c r="C30" s="1" t="inlineStr">
-        <is>
-          <t>###提升乡村治理水平###（填写振兴重点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" customFormat="1" s="1">
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>三农工作的底线任务是###确保国家粮食安全和不发生规模性返贫致贫###（填写底线任务）### ###</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" customFormat="1" s="1">
-      <c r="B32" s="1" t="inlineStr">
-        <is>
-          <t>抓产业创新要###守牢实体经济这个根基###（填写创新要求）### ###</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" customFormat="1" s="1">
-      <c r="C33" s="1" t="inlineStr">
-        <is>
-          <t>###守牢实体经济这个根基###（填写产业创新要求）</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" customFormat="1" s="1">
+          <t>中国共产党的###坚强领导###（填写结束近代民族内部软弱涣散局面的因素）结束了近代民族内部软弱涣散的局面</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="D30" s="1" t="inlineStr">
+        <is>
+          <t>让争取民族独立和解放的斗争有了###主心骨###（填写斗争的核心力量）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="D31" s="1" t="inlineStr">
+        <is>
+          <t>使###民族觉醒和精神升华###（填写达到新高度的方面）达到了新高度</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="D32" s="1" t="inlineStr">
+        <is>
+          <t>汇聚起中国人民###坚不可摧的磅礴力量###（填写汇聚的力量特征）</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="1" t="inlineStr">
+        <is>
+          <t>伟大复兴，从“不可逆转”到“势不可挡”### ###</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
       <c r="C34" s="1" t="inlineStr">
         <is>
-          <t>坚持推动###传统产业改造升级和开辟战略性新兴产业、未来产业新赛道并重###（填写产业创新路径）</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" customFormat="1" s="1">
-      <c r="B35" s="1" t="inlineStr">
-        <is>
-          <t>中国特色现代企业制度的基础是###产权清晰###（填写制度基础）### ###</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" customFormat="1" s="1">
-      <c r="C36" s="1" t="inlineStr">
-        <is>
-          <t>###产权清晰###（填写企业制度基础）</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" customFormat="1" s="1">
-      <c r="C37" s="1" t="inlineStr">
-        <is>
-          <t>###权责明确###（填写企业制度基础）</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" customFormat="1" s="1">
-      <c r="C38" s="1" t="inlineStr">
-        <is>
-          <t>###政企分开###（填写企业制度基础）</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" customFormat="1" s="1">
+          <t>第一，势不可挡，势在“最大优势”——党的领导是实现民族复兴的根本保证</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="D35" s="1" t="inlineStr">
+        <is>
+          <t>中国人民能够扭转近代历史命运，根本在于有###中国共产党的坚强领导###（填写扭转历史命运的根本原因）</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="D36" s="1" t="inlineStr">
+        <is>
+          <t>社会主义中国能够巍然屹立于世界东方，根本在于有###中国共产党的坚强领导###（填写社会主义中国屹立东方的根本原因）</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="D37" s="1" t="inlineStr">
+        <is>
+          <t>民族复兴进入不可逆转的进程，根本在于有###中国共产党的坚强领导###（填写民族复兴进入不可逆转进程的根本原因）</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="D38" s="1" t="inlineStr">
+        <is>
+          <t>###党的领导###（填写复兴大势不可阻挡的根本所在）是复兴大势不可阻挡的根本所在</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
       <c r="C39" s="1" t="inlineStr">
         <is>
-          <t>###管理科学###（填写企业制度基础）</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" customFormat="1" s="1">
-      <c r="B40" s="1" t="inlineStr">
-        <is>
-          <t>完善企业制度###与社会治理无关###（填写制度特点）### ###</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" customFormat="1" s="1">
-      <c r="B41" s="1" t="inlineStr">
-        <is>
-          <t>人大代表不是由选民###直接选举###（填写选举方式）产生### ###</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" customFormat="1" s="1">
+          <t>第二，势不可挡，势在“康庄大道”——中国式现代化是强国复兴的唯一正确道路</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="D40" s="1" t="inlineStr">
+        <is>
+          <t>党的十八大以来，党领导人民书写了新篇章，成功推进和拓展了###中国式现代化###（填写成功推进和拓展的现代化道路）</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="D41" s="1" t="inlineStr">
+        <is>
+          <t>历史和现实证明，###中国式现代化###（填写复兴大势不可阻挡的牢固基础）是复兴大势不可阻挡的牢固基础</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t>###县乡两级人大代表###（填写选举级别）直接选举</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" customFormat="1" s="1">
-      <c r="C43" s="1" t="inlineStr">
-        <is>
-          <t>###县级以上人大###（填写选举级别）由下级人大代表间接选举产生</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" customFormat="1" s="1">
-      <c r="B44" s="1" t="inlineStr">
-        <is>
-          <t>###变通执行权###（填写特殊权力）### ###</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" customFormat="1" s="1">
-      <c r="C45" s="1" t="inlineStr">
-        <is>
-          <t>###特定地方国家机关###（填写权力主体）</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" customFormat="1" s="1">
+          <t>第三，势不可挡，势在“磅礴伟力”——亿万人民汇聚起推进中国式现代化的合力</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="D43" s="1" t="inlineStr">
+        <is>
+          <t>###中华民族一家亲###（填写民族关系状态），###同心共筑中国梦###（填写共同目标）</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="D44" s="1" t="inlineStr">
+        <is>
+          <t>这是全体中华儿女的###共同心愿###（填写中华儿女的共同心愿）和全国各族人民的###共同目标###（填写全国各族人民的共同目标）</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="D45" s="1" t="inlineStr">
+        <is>
+          <t>###中华民族共同体###（填写把握复兴大势不可阻挡的重要维度）是我们把握复兴大势不可阻挡的一个重要维度</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
       <c r="C46" s="1" t="inlineStr">
         <is>
-          <t>在不违背###宪法、法律、行政法规基本原则###（填写前提条件）的前提下</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" customFormat="1" s="1">
-      <c r="C47" s="1" t="inlineStr">
-        <is>
-          <t>针对###本地区特殊情况###（填写适用条件）</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" customFormat="1" s="1">
-      <c r="C48" s="1" t="inlineStr">
-        <is>
-          <t>对上级制定的政策、法律、法规作出灵活调整并执行的权力</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" customFormat="1" s="1">
-      <c r="B49" s="1" t="inlineStr">
-        <is>
-          <t>引领发展的第一动力是###创新###（填写发展动力）### ###</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" customFormat="1" s="1">
+          <t>第四，势不可挡，势在“世界潮流”——站在历史正确一边，携手迈向人类命运共同体</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="D47" s="1" t="inlineStr">
+        <is>
+          <t>###中国式现代化###（填写开辟人类迈向现代化新道路的现代化类型）开辟了人类迈向现代化的新道路</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="D48" s="1" t="inlineStr">
+        <is>
+          <t>###中国式现代化###（填写开创人类文明新形态的现代化类型）开创了人类文明新形态</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="D49" s="1" t="inlineStr">
+        <is>
+          <t>这是复兴大势不可阻挡的###关键所在###（填写复兴大势不可阻挡的决定因素）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>###《新时代的中国国家安全》###（填写文件名称）### ###</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" customFormat="1" s="1">
+          <t>爱国主义的内涵（是什么）### ###</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t>###捍卫国家利益的坚定力量###（填写国家形象）</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" customFormat="1" s="1">
-      <c r="C52" s="1" t="inlineStr">
-        <is>
-          <t>###维护世界和平稳定的正义力量###（填写国家形象）</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" customFormat="1" s="1">
-      <c r="C53" s="1" t="inlineStr">
-        <is>
-          <t>###维护国际公平正义的进步力量###（填写国家形象）</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" customFormat="1" s="1">
-      <c r="C54" s="1" t="inlineStr">
-        <is>
-          <t>###促进全球共同发展的建设力量###（填写国家形象）</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" customFormat="1" s="1">
-      <c r="B55" s="1" t="inlineStr">
-        <is>
-          <t>总体国家安全观是当代中国对世界的###重要思想理论贡献###（填写理论地位）### ###</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" customFormat="1" s="1">
-      <c r="B56" s="1" t="inlineStr">
-        <is>
-          <t>###KMP算法###（填写算法名称）### ###</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" customFormat="1" s="1">
-      <c r="C57" s="1" t="inlineStr">
-        <is>
-          <t>主串指针###不动###（填写指针行为），模式串指针动</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" customFormat="1" s="1">
-      <c r="C58" s="1" t="inlineStr">
-        <is>
-          <t>模式串的###next[j]数组###（填写关键数组）记录失配后模式串指针跳转位置</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" customFormat="1" s="1">
-      <c r="C59" s="1" t="inlineStr">
-        <is>
-          <t>next[j]的生成</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" customFormat="1" s="1">
-      <c r="D60" s="1" t="inlineStr">
-        <is>
-          <t>取最后一个字符是模式串下标###j-1###（填写下标位置）字符的模式子串</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" customFormat="1" s="1">
-      <c r="D61" s="1" t="inlineStr">
-        <is>
-          <t>求出这个模式子串的前后缀</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" customFormat="1" s="1">
-      <c r="E62" s="1" t="inlineStr">
-        <is>
-          <t>注意，前后缀不包括模式子串本身，不然长度必然是模式子串的长度</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" customFormat="1" s="1">
-      <c r="D63" s="1" t="inlineStr">
-        <is>
-          <t>前缀和后缀的交集中选择###最长的那个###（填写选择条件），取它的长度作为next[j]的元素</t>
+          <t>爱国主义</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="D52" s="1" t="inlineStr">
+        <is>
+          <t>体现了人们对祖国的###深厚感情###（填写爱国主义体现的感情类型）</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="D53" s="1" t="inlineStr">
+        <is>
+          <t>揭示了个人对祖国的###依存关系###（填写爱国主义揭示的关系类型）</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="D54" s="1" t="inlineStr">
+        <is>
+          <t>是对###家园、民族和文化###（填写归属感、认同感等的对象）的###归属感、认同感、尊严感与荣誉感###（填写情感类型）的统一</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="C55" s="1" t="inlineStr">
+        <is>
+          <t>爱国主义</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="D56" s="1" t="inlineStr">
+        <is>
+          <t>是中华民族的###优良传统和精神基因###（填写爱国主义的性质）</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="D57" s="1" t="inlineStr">
+        <is>
+          <t>是中华民族的###民族心、民族魂###（填写爱国主义的地位）与###民族精神###（填写爱国主义的归属）的核心</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="D58" s="1" t="inlineStr">
+        <is>
+          <t>是中华民族###团结奋斗、自强不息###（填写精神纽带的作用）的精神纽带</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="D59" s="1" t="inlineStr">
+        <is>
+          <t>是中华民族最重要的###精神财富###（填写爱国主义的价值属性）</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="C60" s="1" t="inlineStr">
+        <is>
+          <t>中华民族发展史就是一部###中华儿女的爱国奋斗史###（填写中华民族发展史的性质）</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="C61" s="1" t="inlineStr">
+        <is>
+          <t>爱国是###最深层、最持久###（填写爱国情感的特征）的情感</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="C62" s="1" t="inlineStr">
+        <is>
+          <t>是一个人的###立德之源、立功之本###（填写爱国对个人的意义）</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="C63" s="1" t="inlineStr">
+        <is>
+          <t>爱国主义至今仍激励中华儿女为###祖国发展繁荣###（填写激励的目标）而###自强不息、不懈奋斗###（填写激励的行动）</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" s="1" t="inlineStr">
+        <is>
+          <t>怎样弘扬爱国主义### ###</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="C65" s="1" t="inlineStr">
+        <is>
+          <t>爱国主义是###具体的、现实的###（填写爱国主义的性质）</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="C66" s="1" t="inlineStr">
+        <is>
+          <t>实现###中华民族伟大复兴的中国梦###（填写新时代爱国主义的鲜明主题）是新时代爱国主义的鲜明主题</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="C67" s="1" t="inlineStr">
+        <is>
+          <t>大力弘扬新时代的爱国主义，必须坚持</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="D68" s="1" t="inlineStr">
+        <is>
+          <t>###爱国爱党爱社会主义相统一###（填写弘扬爱国主义必须坚持的原则之一）</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="D69" s="1" t="inlineStr">
+        <is>
+          <t>###维护祖国统一和民族团结###（填写弘扬爱国主义必须坚持的原则之二）</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="D70" s="1" t="inlineStr">
+        <is>
+          <t>###尊重和传承中华民族历史文化###（填写弘扬爱国主义必须坚持的原则之三）</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="D71" s="1" t="inlineStr">
+        <is>
+          <t>###坚持立足中国又面向世界###（填写弘扬爱国主义必须坚持的原则之四）</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="C72" s="1" t="inlineStr">
+        <is>
+          <t>爱国，不能停留在口号上，而是要</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="D73" s="1" t="inlineStr">
+        <is>
+          <t>把自己的理想同###祖国的前途、民族的命运###（填写需要紧密联系的对象）紧密联系在一起</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="D74" s="1" t="inlineStr">
+        <is>
+          <t>以实际行动体现</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="E75" s="1" t="inlineStr">
+        <is>
+          <t>###对祖国的热爱###（填写以实际行动体现的情感之一）</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="E76" s="1" t="inlineStr">
+        <is>
+          <t>###对党的热爱###（填写以实际行动体现的情感之二）</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="E77" s="1" t="inlineStr">
+        <is>
+          <t>###对社会主义的热爱###（填写以实际行动体现的情感之三）</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="D78" s="1" t="inlineStr">
+        <is>
+          <t>###扎根人民，奉献国家###（填写爱国行动的具体要求）</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="D79" s="1" t="inlineStr">
+        <is>
+          <t>以###一生的真情投人、一辈子的顽强奋斗###（填写践行爱国主义的方式）来践行爱国主义</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" s="1" t="inlineStr">
+        <is>
+          <t>为什么全球治理倡议正逢其时### ###</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="C81" s="1" t="inlineStr">
+        <is>
+          <t>当前国际形势###变乱交织###（填写国际形势的特征）</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="C82" s="1" t="inlineStr">
+        <is>
+          <t>###联合国和多边主义###（填写受到冲击的对象）受到冲击</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="C83" s="1" t="inlineStr">
+        <is>
+          <t>###全球治理赤字###（填写持续扩大的问题）持续扩大</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="C84" s="1" t="inlineStr">
+        <is>
+          <t>现行国际机制存在###三大短板###（填写存在问题的数量）</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="D85" s="1" t="inlineStr">
+        <is>
+          <t>第一，###全球南方###（填写代表性严重不足的地区）在国际机制中的代表性严重不足</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="E86" s="1" t="inlineStr">
+        <is>
+          <t>###新兴市场国家和发展中国家###（填写群体性崛起的国家类型）群体性崛起</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="E87" s="1" t="inlineStr">
+        <is>
+          <t>有必要提升###全球南方代表性###（填写需要提升的方面）并纠正###历史不公###（填写需要纠正的问题）</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="D88" s="1" t="inlineStr">
+        <is>
+          <t>第二，###权威性###（填写遭到侵蚀的性质）遭到侵蚀</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="E89" s="1" t="inlineStr">
+        <is>
+          <t>###全球性问题###（填写超越国界、需国际协作的挑战）是超越国界、需国际协作的复杂挑战</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="E90" s="1" t="inlineStr">
+        <is>
+          <t>###多边主义###（填写全球治理的基本路径）是全球治理的基本路径</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="E91" s="1" t="inlineStr">
+        <is>
+          <t>当前，###联合国宗旨和原则###（填写未能得到有效遵守的对象）未能得到有效遵守</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="F92" s="1" t="inlineStr">
+        <is>
+          <t>###安理会决议###（填写受到抵制的对象）受到抵制</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="F93" s="1" t="inlineStr">
+        <is>
+          <t>###单边制裁###（填写违反国际法并破坏国际秩序的行径）等行径违反国际法并破坏国际秩序</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="D94" s="1" t="inlineStr">
+        <is>
+          <t>第三，从治理效能看，###有效性###（填写亟待提升的方面）亟待提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="E95" s="1" t="inlineStr">
+        <is>
+          <t>###联合国2030年可持续发展议程###（填写落实进展严重滞后的议程）落实进展严重滞后</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="E96" s="1" t="inlineStr">
+        <is>
+          <t>###气候变化、数字鸿沟###（填写日益突出的问题）等问题日益突出</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="E97" s="1" t="inlineStr">
+        <is>
+          <t>###人工智能、网络空间###（填写治理存在缺位的新疆域）等新疆域治理存在缺位</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="C98" s="1" t="inlineStr">
+        <is>
+          <t>在此背景下，###构建与改革全球治理体系###（填写国际社会的重大命题）成为国际社会重大命题</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="C99" s="1" t="inlineStr">
+        <is>
+          <t>中国提出的###全球治理倡议###（填写回应了时代之问的倡议）回应了时代之问</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="D100" s="1" t="inlineStr">
+        <is>
+          <t>该倡议引领了###全球治理变革方向###（填写引领的方向）</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="D101" s="1" t="inlineStr">
+        <is>
+          <t>该倡议符合当今世界的###紧迫需求###（填写符合的需求类型）</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" s="1" t="inlineStr">
+        <is>
+          <t>全球治理倡议是中国向世界提供的重要公共产品### ###</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="C103" s="1" t="inlineStr">
+        <is>
+          <t>核心理念与原则</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="D104" s="1" t="inlineStr">
+        <is>
+          <t>秉承###《联合国宪章》宗旨###（填写秉承的宗旨），呼应###各国普遍期待###（填写呼应的期待）</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="D105" s="1" t="inlineStr">
+        <is>
+          <t>体现中国引领应对###全球治理赤字###（填写应对的赤字类型）、推动构建###人类命运共同体###（填写推动构建的共同体）的担当</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="C106" s="1" t="inlineStr">
+        <is>
+          <t>改革路径与目标</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="D107" s="1" t="inlineStr">
+        <is>
+          <t>非###颠覆性改革###（填写改革的性质），而是提升###现行国际体系与机制###（填写提升效能的对象）的效能</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="D108" s="1" t="inlineStr">
+        <is>
+          <t>使其更适应形势，有效应对###全球挑战###（填写应对的挑战类型），更好服务###各国尤其是发展中国家###（填写服务的对象）利益</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="C109" s="1" t="inlineStr">
+        <is>
+          <t>贡献与反响</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="D110" s="1" t="inlineStr">
+        <is>
+          <t>提出###全球治理改革的中国方案###（填写提出的方案类型），贡献###治理智慧###（填写贡献的内容）</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="D111" s="1" t="inlineStr">
+        <is>
+          <t>作为重要###国际公共产品###（填写产品的属性），获广泛积极响应</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" s="1" t="inlineStr">
+        <is>
+          <t>以辩证思维认识与处理新旧关系### ###</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="C113" s="1" t="inlineStr">
+        <is>
+          <t>新旧###对立统一###（填写新旧关系的性质），相互依存贯通，可在###一定条件###（填写转化的条件）下转化</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="C114" s="1" t="inlineStr">
+        <is>
+          <t>以###联系、发展的观点###（填写看问题的观点）看问题，在###对立统一###（填写把握关系的原则）中把握关系</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="D115" s="1" t="inlineStr">
+        <is>
+          <t>用###联系眼光###（填写看待新旧关系的眼光）看待新旧，###转换思路、创造条件###（填写采取的行动），化不利为有利，寻求新突破</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="D116" s="1" t="inlineStr">
+        <is>
+          <t>用###发展眼光###（填写看待旧资源的眼光）看待旧资源，###把握趋势、找准新方向###（填写采取的行动），放大自身优势</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="C117" s="1" t="inlineStr">
+        <is>
+          <t>新旧非绝对对立，其###交织交融###（填写新旧关系的状态）能激发新活力</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" s="1" t="inlineStr">
+        <is>
+          <t>辩证否定原理### ###</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="C119" s="1" t="inlineStr">
+        <is>
+          <t>事物发展通过###内在矛盾自我否定###（填写事物发展的实现方式）实现</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="C120" s="1" t="inlineStr">
+        <is>
+          <t>（发展）否定是###旧事物向新事物###（填写否定的转变方向）的转变与质的飞跃</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="C121" s="1" t="inlineStr">
+        <is>
+          <t>（联系）新事物孕育于###旧事物###（填写新事物的孕育场所），二者通过###否定###（填写联系的方式）相联系</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="C122" s="1" t="inlineStr">
+        <is>
+          <t>新事物对旧事物###既批判又继承###（填写新事物对旧事物的态度），克服###消极因素###（填写克服的因素），保留###积极因素###（填写保留的因素）</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="C123" s="1" t="inlineStr">
+        <is>
+          <t>并非###简单否定一切###（填写否定的性质）</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="D124" s="1" t="inlineStr">
+        <is>
+          <t>而是从旧事物中吸收###合理成分###（填写吸收的内容）</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="D125" s="1" t="inlineStr">
+        <is>
+          <t>加入###新内容###（填写加入的内容）</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="D126" s="1" t="inlineStr">
+        <is>
+          <t>形成具有###新结构功能###（填写形成的事物的特征）的事物以适应变化</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="B127" s="1" t="inlineStr">
+        <is>
+          <t>为什么要改善民生### ###</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="C128" s="1" t="inlineStr">
+        <is>
+          <t>第一，###中国式现代化###（填写坚持民生为大的现代化类型）坚持民生为大</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="D129" s="1" t="inlineStr">
+        <is>
+          <t>###保障和改善民生###（填写重大任务的内容）是重大任务</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="D130" s="1" t="inlineStr">
+        <is>
+          <t>“投资于人”、服务民生，体现了以人民为中心的发展思想</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="E131" s="1" t="inlineStr">
+        <is>
+          <t>人是###消费主体、生产核心和创新源泉###（填写人在经济社会中的角色）</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="E132" s="1" t="inlineStr">
+        <is>
+          <t>投资于人的###多维需求与全面发展###（填写投资的对象）</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="F133" s="1" t="inlineStr">
+        <is>
+          <t>涵盖###就业、收入、教育、医疗###（填写涵盖的领域）等领域，旨在提升###民众福祉与能力###（填写提升的目标）</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="D134" s="1" t="inlineStr">
+        <is>
+          <t>对###高质量发展###（填写具有长远意义的领域）的长远意义</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="E135" s="1" t="inlineStr">
+        <is>
+          <t>有助于释放###消费潜力###（填写有助于释放的潜力），培育###强大国内市场###（填写培育的市场类型），畅通###国内大循环###（填写畅通的循环类型）</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="E136" s="1" t="inlineStr">
+        <is>
+          <t>可积累###人力资本###（填写积累的资本类型），激发###创新活力###（填写激发的活力类型），加快###新质生产力###（填写加快发展的生产力类型）发展，夯实###高质量发展###（填写夯实的根基类型）根基</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="C137" s="1" t="inlineStr">
+        <is>
+          <t>第二，“投资于人”是高质量发展的长远举措</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="D138" s="1" t="inlineStr">
+        <is>
+          <t>通过满足人的###全面需求###（填写满足的需求类型），促进###能消费、敢消费、愿消费###（填写促进的消费状态）</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="D139" s="1" t="inlineStr">
+        <is>
+          <t>既破解###消费增长困境###（填写破解的困境），又为###创新与新质生产力发展###（填写注入动力的领域）注入动力，巩固###发展根基###（填写巩固的根基）</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="B140" s="1" t="inlineStr">
+        <is>
+          <t>如何认识经济发展与改善民生### ###</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="C141" s="1" t="inlineStr">
+        <is>
+          <t>发展是解决民生的“总钥匙”，民生是发展的“指南针”</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="C142" s="1" t="inlineStr">
+        <is>
+          <t>第一，发展是民生的###物质基础###（填写发展的作用）</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="D143" s="1" t="inlineStr">
+        <is>
+          <t>离开###发展###（填写民生改善的前提）则民生改善无从谈起</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="D144" s="1" t="inlineStr">
+        <is>
+          <t>发展必须回应###人民期待###（填写回应的对象）、带来###实际利益###（填写带来的利益），才可持续</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="C145" s="1" t="inlineStr">
+        <is>
+          <t>第二，###民生###（填写促进发展的因素）促进发展</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="D146" s="1" t="inlineStr">
+        <is>
+          <t>抓###民生###（填写即抓发展的对象）即抓发展</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="D147" s="1" t="inlineStr">
+        <is>
+          <t>持续改善民生能缓解###群众后顾之忧###（填写缓解的担忧）</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="E148" s="1" t="inlineStr">
+        <is>
+          <t>调动###生产积极性###（填写调动的积极性），提升###消费预期###（填写提升的预期）</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="E149" s="1" t="inlineStr">
+        <is>
+          <t>从而扩大###内需###（填写扩大的需求类型）、催生###新增长点###（填写催生的增长类型）</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="C150" s="1" t="inlineStr">
+        <is>
+          <t>第三，实现###民生与发展###（填写实现良性互动的两个方面）的良性互动</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="D151" s="1" t="inlineStr">
+        <is>
+          <t>应全面把握二者###互为牵动、互为条件###（填写二者关系的特征）的关系</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="D152" s="1" t="inlineStr">
+        <is>
+          <t>推动###民生改善与经济发展###（填写推动对接的两个方面）有效对接</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="D153" s="1" t="inlineStr">
+        <is>
+          <t>形成###有机统一###（填写长效机制的特征）的长效机制</t>
         </is>
       </c>
     </row>

--- a/Note/输出.xlsx
+++ b/Note/输出.xlsx
@@ -1011,7 +1011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H153"/>
+  <dimension ref="A1:H98"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.888888888888889" defaultRowHeight="14.4"/>
   <cols>
     <col width="9.66666666666667" customWidth="1" style="1" min="1" max="1"/>
@@ -1024,31 +1024,31 @@
         <v/>
       </c>
       <c r="B1" s="3">
-        <f>COUNTA(B2:B1805)/COLUMN()</f>
+        <f>COUNTA(B2:B1698)/COLUMN()</f>
         <v/>
       </c>
       <c r="C1" s="3">
-        <f>COUNTA(C2:C1805)/COLUMN()</f>
+        <f>COUNTA(C2:C1698)/COLUMN()</f>
         <v/>
       </c>
       <c r="D1" s="3">
-        <f>COUNTA(D2:D1805)/COLUMN()</f>
+        <f>COUNTA(D2:D1698)/COLUMN()</f>
         <v/>
       </c>
       <c r="E1" s="3">
-        <f>COUNTA(E2:E1805)/COLUMN()</f>
+        <f>COUNTA(E2:E1698)/COLUMN()</f>
         <v/>
       </c>
       <c r="F1" s="3">
-        <f>COUNTA(F2:F1805)/COLUMN()</f>
+        <f>COUNTA(F2:F1698)/COLUMN()</f>
         <v/>
       </c>
       <c r="G1" s="3">
-        <f>COUNTA(G2:G1805)/COLUMN()</f>
+        <f>COUNTA(G2:G1698)/COLUMN()</f>
         <v/>
       </c>
       <c r="H1" s="3">
-        <f>COUNTA(H2:H1805)/COLUMN()</f>
+        <f>COUNTA(H2:H1698)/COLUMN()</f>
         <v/>
       </c>
     </row>
@@ -1059,1064 +1059,679 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>绿色发展（绿水青山就是金山银山）为何成为共识### ###</t>
+          <t>中国的投资价值### ###</t>
         </is>
       </c>
     </row>
     <row r="3" customFormat="1" s="1">
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>第一，以“两个结合”继承发展了马克思主义生态观和发展观</t>
+          <t>第一，坚持###高水平对外开放###（填写坚持的开放战略）</t>
         </is>
       </c>
     </row>
     <row r="4" customFormat="1" s="1">
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>根植于中华民族深厚的###生态文化基因###（填写绿色发展的文化基础）</t>
+          <t>###对外开放###（填写基本国策的内容）是基本国策</t>
         </is>
       </c>
     </row>
     <row r="5" customFormat="1" s="1">
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>彰显###时代价值###（填写绿色发展彰显的价值）</t>
+          <t>正稳步推进###规则、规制等制度型开放###（填写推进的开放类型）</t>
         </is>
       </c>
     </row>
     <row r="6" customFormat="1" s="1">
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>第二，指引新时代###生态文明建设###（填写绿色发展指引的建设领域）取得举世瞩目成就</t>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>###利用外资政策###（填写长期稳定的政策类型）长期稳定</t>
         </is>
       </c>
     </row>
     <row r="7" customFormat="1" s="1">
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t>新时代党和国家事业###历史性成就与变革###（填写绿色发展成就的性质）的显著标志</t>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>第二，###市场潜力巨大且转型加速###（填写中国的市场特征）</t>
         </is>
       </c>
     </row>
     <row r="8" customFormat="1" s="1">
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>第三，实现了对###西方传统发展范式###（填写超越的对象）的历史性超越</t>
+      <c r="D8" s="1" t="inlineStr">
+        <is>
+          <t>作为全球第二大消费市场，拥有###最大规模中等收入群体###（填写拥有的消费群体特征）</t>
         </is>
       </c>
     </row>
     <row r="9" customFormat="1" s="1">
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>以这一理念为指引，建设###人与自然和谐共生###（填写建设的现代化类型）的现代化</t>
+          <t>###绿色化、数字化、智能化###（填写转型加快的领域）转型加快，产业配套强</t>
         </is>
       </c>
     </row>
     <row r="10" customFormat="1" s="1">
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>开创了###人类文明新形态###（填写开创的文明形态）</t>
+          <t>是###科技革命与产业变革###（填写最佳应用场景的领域）的最佳应用场景</t>
         </is>
       </c>
     </row>
     <row r="11" customFormat="1" s="1">
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>“两山”是中国的，也是世界的### ###</t>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>第三，###外资法规政策体系###（填写健全的体系类型）健全</t>
         </is>
       </c>
     </row>
     <row r="12" customFormat="1" s="1">
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>“两山”理念为全球生态治理和实现联合国可持续发展目标提供了中国方案</t>
+          <t>已形成较为完备的###利用外资法规政策与工作体系###（填写形成的体系类型）</t>
         </is>
       </c>
     </row>
     <row r="13" customFormat="1" s="1">
-      <c r="E13" s="1" t="inlineStr">
-        <is>
-          <t>“两山”理念科学回应生态文明世界之问</t>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>第四，###社会环境###（填写安全稳定的领域）安全稳定</t>
         </is>
       </c>
     </row>
     <row r="14" customFormat="1" s="1">
-      <c r="E14" s="1" t="inlineStr">
-        <is>
-          <t>高度契合###全球绿色发展理念###（填写契合的理念）</t>
+      <c r="D14" s="1" t="inlineStr">
+        <is>
+          <t>长期保持###政局稳定与社会安定###（填写长期保持的状态）</t>
         </is>
       </c>
     </row>
     <row r="15" customFormat="1" s="1">
-      <c r="E15" s="1" t="inlineStr">
-        <is>
-          <t>深刻启迪###全球生态文明建设###（填写启迪的领域）</t>
+      <c r="D15" s="1" t="inlineStr">
+        <is>
+          <t>是国际公认的###最安全国家之一###（填写中国的国际安全地位）</t>
         </is>
       </c>
     </row>
     <row r="16" customFormat="1" s="1">
-      <c r="E16" s="1" t="inlineStr">
-        <is>
-          <t>凝聚了###全球绿色共识###（填写凝聚的共识类型）</t>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>抗日是持久战### ###</t>
         </is>
       </c>
     </row>
     <row r="17" customFormat="1" s="1">
-      <c r="D17" s="1" t="inlineStr">
-        <is>
-          <t>在实践上，“两山”理念指引开创人类文明新形态</t>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>战争性质：是###半殖民地中国###（填写战争一方）与###帝国主义日本###（填写战争另一方）之间的决死战争</t>
         </is>
       </c>
     </row>
     <row r="18" customFormat="1" s="1">
-      <c r="E18" s="1" t="inlineStr">
-        <is>
-          <t>破解全球可持续发展面临的###两难困境###（填写破解的困境类型）</t>
+      <c r="C18" s="1" t="inlineStr">
+        <is>
+          <t>第一方面：###强弱对比###（填写决定战争形态的因素）决定战争形态</t>
         </is>
       </c>
     </row>
     <row r="19" customFormat="1" s="1">
-      <c r="E19" s="1" t="inlineStr">
-        <is>
-          <t>激发###绿色转型###（填写激发的转型类型）活力</t>
+      <c r="D19" s="1" t="inlineStr">
+        <is>
+          <t>日本是###强国###（填写日本的实力地位）</t>
         </is>
       </c>
     </row>
     <row r="20" customFormat="1" s="1">
-      <c r="E20" s="1" t="inlineStr">
-        <is>
-          <t>引领###全球环境治理###（填写引领的治理领域）</t>
+      <c r="D20" s="1" t="inlineStr">
+        <is>
+          <t>中国是###弱国###（填写中国的实力地位）</t>
         </is>
       </c>
     </row>
     <row r="21" customFormat="1" s="1">
-      <c r="E21" s="1" t="inlineStr">
-        <is>
-          <t>共建绿色“一带一路”</t>
+      <c r="D21" s="1" t="inlineStr">
+        <is>
+          <t>###强弱对比###（填写决定战争形态的关键因素）决定了抗日战争只能是持久战</t>
         </is>
       </c>
     </row>
     <row r="22" customFormat="1" s="1">
-      <c r="E22" s="1" t="inlineStr">
-        <is>
-          <t>推动共建###地球生命共同体###（填写推动共建的共同体类型）</t>
+      <c r="C22" s="1" t="inlineStr">
+        <is>
+          <t>第二方面：###多因素对比###（填写决定最终胜利的因素）决定最终胜利</t>
         </is>
       </c>
     </row>
     <row r="23" customFormat="1" s="1">
       <c r="D23" s="1" t="inlineStr">
         <is>
-          <t>“两山”理念不仅深刻改变了中国，也深刻影响了世界。</t>
+          <t>日本是###小国###（填写日本的国家规模），进行###退步、野蛮的侵略战争###（填写日本进行的战争性质），在国际上###失道寡助###（填写日本在国际上的处境）</t>
         </is>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
-      <c r="B24" s="1" t="inlineStr">
-        <is>
-          <t>中国命运转变的关键### ###</t>
+      <c r="D24" s="1" t="inlineStr">
+        <is>
+          <t>中国是###大国###（填写中国的国家规模），进行###进步、正义的反侵略战争###（填写中国进行的战争性质），在国际上###得道多助###（填写中国在国际上的处境）</t>
         </is>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
-      <c r="C25" s="1" t="inlineStr">
-        <is>
-          <t>###中国共产党###（填写在民族危亡关头挺身担当的政党）在民族危亡关头挺身担当</t>
+      <c r="D25" s="1" t="inlineStr">
+        <is>
+          <t>中国已有政治上成熟的###中国共产党###（填写政治上成熟的政党）及其领导的###抗日根据地与人民军队###（填写党领导的抗战力量）</t>
         </is>
       </c>
     </row>
     <row r="26" customFormat="1" s="1">
-      <c r="D26" s="1" t="inlineStr">
-        <is>
-          <t>始终发挥###中流砥柱###（填写发挥的作用类型）作用</t>
+      <c r="C26" s="1" t="inlineStr">
+        <is>
+          <t>因此，###最后胜利###（填写必将属于中国的成果）必将属于中国。</t>
         </is>
       </c>
     </row>
     <row r="27" customFormat="1" s="1">
-      <c r="D27" s="1" t="inlineStr">
-        <is>
-          <t>以###政治主张、坚定意志和模范行动###（填写支撑希望的要素）支撑起民族救亡图存的希望</t>
+      <c r="B27" s="1" t="inlineStr">
+        <is>
+          <t>敌后战场的作用### ###</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="D28" s="1" t="inlineStr">
-        <is>
-          <t>成为夺取战争胜利的###民族先锋###（填写党的历史角色）</t>
+      <c r="C28" s="1" t="inlineStr">
+        <is>
+          <t>决策内容与意义</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t>中国共产党的###坚强领导###（填写结束近代民族内部软弱涣散局面的因素）结束了近代民族内部软弱涣散的局面</t>
+      <c r="D29" s="1" t="inlineStr">
+        <is>
+          <t>为执行###全面抗战路线###（填写执行的路线），作出开辟###敌后战场###（填写开辟的战场类型）的决策</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="D30" s="1" t="inlineStr">
-        <is>
-          <t>让争取民族独立和解放的斗争有了###主心骨###（填写斗争的核心力量）</t>
+      <c r="E30" s="1" t="inlineStr">
+        <is>
+          <t>延续###农村包围城市、武装夺取政权###（填写延续的革命道路）的道路</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="D31" s="1" t="inlineStr">
         <is>
-          <t>使###民族觉醒和精神升华###（填写达到新高度的方面）达到了新高度</t>
+          <t>###敌后战场###（填写为抗战胜利作出巨大贡献的战场）的坚持与发展为抗战胜利作出巨大贡献</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="D32" s="1" t="inlineStr">
-        <is>
-          <t>汇聚起中国人民###坚不可摧的磅礴力量###（填写汇聚的力量特征）</t>
+      <c r="E32" s="1" t="inlineStr">
+        <is>
+          <t>起到###改变战局的战略引领###（填写起到的作用类型）作用</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="1" t="inlineStr">
-        <is>
-          <t>伟大复兴，从“不可逆转”到“势不可挡”### ###</t>
+      <c r="C33" s="1" t="inlineStr">
+        <is>
+          <t>敌后战场在各阶段的作用</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="C34" s="1" t="inlineStr">
-        <is>
-          <t>第一，势不可挡，势在“最大优势”——党的领导是实现民族复兴的根本保证</t>
+      <c r="D34" s="1" t="inlineStr">
+        <is>
+          <t>战略防御阶段</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="D35" s="1" t="inlineStr">
-        <is>
-          <t>中国人民能够扭转近代历史命运，根本在于有###中国共产党的坚强领导###（填写扭转历史命运的根本原因）</t>
+      <c r="E35" s="1" t="inlineStr">
+        <is>
+          <t>###正面战场###（填写为主战场的战场类型）为主战场</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="D36" s="1" t="inlineStr">
-        <is>
-          <t>社会主义中国能够巍然屹立于世界东方，根本在于有###中国共产党的坚强领导###（填写社会主义中国屹立东方的根本原因）</t>
+      <c r="E36" s="1" t="inlineStr">
+        <is>
+          <t>###敌后战场###（填写是重要力量的战场类型）是重要力量</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="D37" s="1" t="inlineStr">
-        <is>
-          <t>民族复兴进入不可逆转的进程，根本在于有###中国共产党的坚强领导###（填写民族复兴进入不可逆转进程的根本原因）</t>
+      <c r="E37" s="1" t="inlineStr">
+        <is>
+          <t>推动战争转入###相持阶段###（填写转入的阶段），实现###持久抗战###（填写实现的战略）</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="D38" s="1" t="inlineStr">
         <is>
-          <t>###党的领导###（填写复兴大势不可阻挡的根本所在）是复兴大势不可阻挡的根本所在</t>
+          <t>战略相持阶段</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="C39" s="1" t="inlineStr">
-        <is>
-          <t>第二，势不可挡，势在“康庄大道”——中国式现代化是强国复兴的唯一正确道路</t>
+      <c r="E39" s="1" t="inlineStr">
+        <is>
+          <t>###敌后战场###（填写逐渐成为主战场的战场）逐渐成为主战场</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="D40" s="1" t="inlineStr">
-        <is>
-          <t>党的十八大以来，党领导人民书写了新篇章，成功推进和拓展了###中国式现代化###（填写成功推进和拓展的现代化道路）</t>
+      <c r="E40" s="1" t="inlineStr">
+        <is>
+          <t>极大振奋###全国信心###（填写振奋的对象）</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="D41" s="1" t="inlineStr">
-        <is>
-          <t>历史和现实证明，###中国式现代化###（填写复兴大势不可阻挡的牢固基础）是复兴大势不可阻挡的牢固基础</t>
+      <c r="E41" s="1" t="inlineStr">
+        <is>
+          <t>展现###人民战争###（填写展现的战争类型）的强大威力</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="C42" s="1" t="inlineStr">
-        <is>
-          <t>第三，势不可挡，势在“磅礴伟力”——亿万人民汇聚起推进中国式现代化的合力</t>
+      <c r="D42" s="1" t="inlineStr">
+        <is>
+          <t>战略反攻阶段</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="D43" s="1" t="inlineStr">
-        <is>
-          <t>###中华民族一家亲###（填写民族关系状态），###同心共筑中国梦###（填写共同目标）</t>
+      <c r="E43" s="1" t="inlineStr">
+        <is>
+          <t>###敌后战场###（填写成为决胜力量的战场）成为决胜力量</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="D44" s="1" t="inlineStr">
-        <is>
-          <t>这是全体中华儿女的###共同心愿###（填写中华儿女的共同心愿）和全国各族人民的###共同目标###（填写全国各族人民的共同目标）</t>
+      <c r="C44" s="1" t="inlineStr">
+        <is>
+          <t>总结</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="D45" s="1" t="inlineStr">
         <is>
-          <t>###中华民族共同体###（填写把握复兴大势不可阻挡的重要维度）是我们把握复兴大势不可阻挡的一个重要维度</t>
+          <t>###中国共产党###（填写领导人民武装的政党）领导的人民武装在敌后战场发展壮大，由弱变强</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="C46" s="1" t="inlineStr">
-        <is>
-          <t>第四，势不可挡，势在“世界潮流”——站在历史正确一边，携手迈向人类命运共同体</t>
+      <c r="D46" s="1" t="inlineStr">
+        <is>
+          <t>为夺取###最后胜利###（填写发挥决定性作用的目标）发挥决定性作用</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="D47" s="1" t="inlineStr">
-        <is>
-          <t>###中国式现代化###（填写开辟人类迈向现代化新道路的现代化类型）开辟了人类迈向现代化的新道路</t>
+      <c r="B47" s="1" t="inlineStr">
+        <is>
+          <t>崇尚英雄### ###</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="D48" s="1" t="inlineStr">
-        <is>
-          <t>###中国式现代化###（填写开创人类文明新形态的现代化类型）开创了人类文明新形态</t>
+      <c r="C48" s="1" t="inlineStr">
+        <is>
+          <t>伟大时代与英雄精神</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="D49" s="1" t="inlineStr">
         <is>
-          <t>这是复兴大势不可阻挡的###关键所在###（填写复兴大势不可阻挡的决定因素）。</t>
+          <t>###伟大时代###（填写呼唤并造就英雄的时代）呼唤并造就英雄，###英雄辈出###（填写推动事业兴旺发达的因素）推动党和人民事业兴旺发达</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="B50" s="1" t="inlineStr">
-        <is>
-          <t>爱国主义的内涵（是什么）### ###</t>
+      <c r="D50" s="1" t="inlineStr">
+        <is>
+          <t>###崇尚英雄###（填写产生英雄的前提）才能产生英雄，###争做英雄###（填写英雄辈出的条件）方能英雄辈出</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t>爱国主义</t>
+          <t>英雄精神对民族复兴的意义</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="D52" s="1" t="inlineStr">
         <is>
-          <t>体现了人们对祖国的###深厚感情###（填写爱国主义体现的感情类型）</t>
+          <t>###国家强盛与民族复兴###（填写既需物质积累又需精神文明升华的目标）既需物质积累，亦需精神文明升华</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="D53" s="1" t="inlineStr">
         <is>
-          <t>揭示了个人对祖国的###依存关系###（填写爱国主义揭示的关系类型）</t>
+          <t>###缅怀英烈事迹、传承英烈精神###（填写对价值观的洗礼活动）是对价值观的洗礼</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="D54" s="1" t="inlineStr">
-        <is>
-          <t>是对###家园、民族和文化###（填写归属感、认同感等的对象）的###归属感、认同感、尊严感与荣誉感###（填写情感类型）的统一</t>
+      <c r="E54" s="1" t="inlineStr">
+        <is>
+          <t>可转化为###爱国情、强国志、报国行###（填写转化的内生动力内容）的内生动力</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="C55" s="1" t="inlineStr">
         <is>
-          <t>爱国主义</t>
+          <t>纪念活动的现实作用</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="D56" s="1" t="inlineStr">
         <is>
-          <t>是中华民族的###优良传统和精神基因###（填写爱国主义的性质）</t>
+          <t>在###烈士纪念日###（填写追思先烈的日期）追思先烈、致敬英雄，有助于增强###历史自信、激扬历史主动精神###（填写有助于增强的精神）</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="D57" s="1" t="inlineStr">
         <is>
-          <t>是中华民族的###民族心、民族魂###（填写爱国主义的地位）与###民族精神###（填写爱国主义的归属）的核心</t>
+          <t>使###爱国主义与革命英雄主义###（填写成为强大精神动力的主义）成为引领向前、催人奋斗的强大精神动力</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="D58" s="1" t="inlineStr">
-        <is>
-          <t>是中华民族###团结奋斗、自强不息###（填写精神纽带的作用）的精神纽带</t>
+      <c r="B58" s="1" t="inlineStr">
+        <is>
+          <t>做堂堂正正光荣自豪的中国人### ###</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="D59" s="1" t="inlineStr">
-        <is>
-          <t>是中华民族最重要的###精神财富###（填写爱国主义的价值属性）</t>
+      <c r="C59" s="1" t="inlineStr">
+        <is>
+          <t>一、'###堂堂正正###'的民族气节</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="C60" s="1" t="inlineStr">
-        <is>
-          <t>中华民族发展史就是一部###中华儿女的爱国奋斗史###（填写中华民族发展史的性质）</t>
+      <c r="D60" s="1" t="inlineStr">
+        <is>
+          <t>中华民族在磨难中###愈挫愈勇、奋起成长###（填写中华民族在磨难中的表现）</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="C61" s="1" t="inlineStr">
-        <is>
-          <t>爱国是###最深层、最持久###（填写爱国情感的特征）的情感</t>
+      <c r="D61" s="1" t="inlineStr">
+        <is>
+          <t>'堂堂正正'体现为</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="C62" s="1" t="inlineStr">
-        <is>
-          <t>是一个人的###立德之源、立功之本###（填写爱国对个人的意义）</t>
+      <c r="E62" s="1" t="inlineStr">
+        <is>
+          <t>###危难中不甘屈辱###（填写'堂堂正正'的体现之一）</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="C63" s="1" t="inlineStr">
-        <is>
-          <t>爱国主义至今仍激励中华儿女为###祖国发展繁荣###（填写激励的目标）而###自强不息、不懈奋斗###（填写激励的行动）</t>
+      <c r="E63" s="1" t="inlineStr">
+        <is>
+          <t>###敢于斗争的精神坚守与担当###（填写'堂堂正正'的体现之二）</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="B64" s="1" t="inlineStr">
-        <is>
-          <t>怎样弘扬爱国主义### ###</t>
+      <c r="D64" s="1" t="inlineStr">
+        <is>
+          <t>这种姿态是百年风雨淬炼出的###民族气质###（填写淬炼出的精神品质）</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="C65" s="1" t="inlineStr">
-        <is>
-          <t>爱国主义是###具体的、现实的###（填写爱国主义的性质）</t>
+      <c r="D65" s="1" t="inlineStr">
+        <is>
+          <t>是亿万中国人的###血脉共鸣与心灵选择###（填写是亿万中国人的情感认同）</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="C66" s="1" t="inlineStr">
         <is>
-          <t>实现###中华民族伟大复兴的中国梦###（填写新时代爱国主义的鲜明主题）是新时代爱国主义的鲜明主题</t>
+          <t>二、'###光荣自豪###'的从容自信</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="C67" s="1" t="inlineStr">
-        <is>
-          <t>大力弘扬新时代的爱国主义，必须坚持</t>
+      <c r="D67" s="1" t="inlineStr">
+        <is>
+          <t>体现为</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="D68" s="1" t="inlineStr">
-        <is>
-          <t>###爱国爱党爱社会主义相统一###（填写弘扬爱国主义必须坚持的原则之一）</t>
+      <c r="E68" s="1" t="inlineStr">
+        <is>
+          <t>###面对压力有信心###（填写'光荣自豪'的体现之一）</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="D69" s="1" t="inlineStr">
-        <is>
-          <t>###维护祖国统一和民族团结###（填写弘扬爱国主义必须坚持的原则之二）</t>
+      <c r="E69" s="1" t="inlineStr">
+        <is>
+          <t>###应对挑战有定力###（填写'光荣自豪'的体现之二）</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="D70" s="1" t="inlineStr">
-        <is>
-          <t>###尊重和传承中华民族历史文化###（填写弘扬爱国主义必须坚持的原则之三）</t>
+      <c r="E70" s="1" t="inlineStr">
+        <is>
+          <t>###面向世界有风采###（填写'光荣自豪'的体现之三）</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="D71" s="1" t="inlineStr">
         <is>
-          <t>###坚持立足中国又面向世界###（填写弘扬爱国主义必须坚持的原则之四）</t>
+          <t>这是一种</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="C72" s="1" t="inlineStr">
-        <is>
-          <t>爱国，不能停留在口号上，而是要</t>
+      <c r="E72" s="1" t="inlineStr">
+        <is>
+          <t>基于###历史与文化自信###（填写自信的基础）的</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="D73" s="1" t="inlineStr">
-        <is>
-          <t>把自己的理想同###祖国的前途、民族的命运###（填写需要紧密联系的对象）紧密联系在一起</t>
+      <c r="E73" s="1" t="inlineStr">
+        <is>
+          <t>###从容理性、不卑不亢、开放包容###（填写胸怀的特征）的胸怀</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="D74" s="1" t="inlineStr">
-        <is>
-          <t>以实际行动体现</t>
+      <c r="E74" s="1" t="inlineStr">
+        <is>
+          <t>根植于</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="E75" s="1" t="inlineStr">
-        <is>
-          <t>###对祖国的热爱###（填写以实际行动体现的情感之一）</t>
+      <c r="F75" s="1" t="inlineStr">
+        <is>
+          <t>###文明传统###（填写根植的基础之一）</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="E76" s="1" t="inlineStr">
-        <is>
-          <t>###对党的热爱###（填写以实际行动体现的情感之二）</t>
+      <c r="F76" s="1" t="inlineStr">
+        <is>
+          <t>###中国特色社会主义实践###（填写根植的基础之二）</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="E77" s="1" t="inlineStr">
-        <is>
-          <t>###对社会主义的热爱###（填写以实际行动体现的情感之三）</t>
+      <c r="D77" s="1" t="inlineStr">
+        <is>
+          <t>当代青年作为'###平视世界###'（填写青年的时代特征）的一代</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="D78" s="1" t="inlineStr">
-        <is>
-          <t>###扎根人民，奉献国家###（填写爱国行动的具体要求）</t>
+      <c r="E78" s="1" t="inlineStr">
+        <is>
+          <t>应在###更广阔舞台###（填写展现风貌的场所）上</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="D79" s="1" t="inlineStr">
-        <is>
-          <t>以###一生的真情投人、一辈子的顽强奋斗###（填写践行爱国主义的方式）来践行爱国主义</t>
+      <c r="E79" s="1" t="inlineStr">
+        <is>
+          <t>展现###昂扬风貌###（填写展现的精神面貌）</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="B80" s="1" t="inlineStr">
-        <is>
-          <t>为什么全球治理倡议正逢其时### ###</t>
+      <c r="E80" s="1" t="inlineStr">
+        <is>
+          <t>续写###时代荣光###（填写续写的辉煌）</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="C81" s="1" t="inlineStr">
-        <is>
-          <t>当前国际形势###变乱交织###（填写国际形势的特征）</t>
+      <c r="B81" s="1" t="inlineStr">
+        <is>
+          <t>正确二战史观### ###</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="C82" s="1" t="inlineStr">
         <is>
-          <t>###联合国和多边主义###（填写受到冲击的对象）受到冲击</t>
+          <t>坚持###正确二战史观###（填写应坚持的历史观）、捍卫###历史正义###（填写应捍卫的正义类型）</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="C83" s="1" t="inlineStr">
         <is>
-          <t>###全球治理赤字###（填写持续扩大的问题）持续扩大</t>
+          <t>既是对###历史###（填写总结的对象）的总结</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="C84" s="1" t="inlineStr">
         <is>
-          <t>现行国际机制存在###三大短板###（填写存在问题的数量）</t>
+          <t>也是对###未来###（填写指引的对象）的指引</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="D85" s="1" t="inlineStr">
-        <is>
-          <t>第一，###全球南方###（填写代表性严重不足的地区）在国际机制中的代表性严重不足</t>
+      <c r="C85" s="1" t="inlineStr">
+        <is>
+          <t>第一，汲取###历史教训###（填写现实需要的内容）的现实需要</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="E86" s="1" t="inlineStr">
-        <is>
-          <t>###新兴市场国家和发展中国家###（填写群体性崛起的国家类型）群体性崛起</t>
+      <c r="D86" s="1" t="inlineStr">
+        <is>
+          <t>历史是###教科书与清醒剂###（填写历史的双重作用）</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="E87" s="1" t="inlineStr">
-        <is>
-          <t>有必要提升###全球南方代表性###（填写需要提升的方面）并纠正###历史不公###（填写需要纠正的问题）</t>
+      <c r="D87" s="1" t="inlineStr">
+        <is>
+          <t>坚持###正确史观###（填写坚持的史观类型），引导国际社会系统反思###二战###（填写反思的历史事件）</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="D88" s="1" t="inlineStr">
         <is>
-          <t>第二，###权威性###（填写遭到侵蚀的性质）遭到侵蚀</t>
+          <t>（对西方）抵制###否定成果、歪曲真相的错误思潮###（填写抵制的思潮类型）</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="E89" s="1" t="inlineStr">
-        <is>
-          <t>###全球性问题###（填写超越国界、需国际协作的挑战）是超越国界、需国际协作的复杂挑战</t>
+      <c r="D89" s="1" t="inlineStr">
+        <is>
+          <t>（对日本）警惕###军国主义###（填写警惕的主义），防止###悲剧重演###（填写防止的事件）</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="E90" s="1" t="inlineStr">
-        <is>
-          <t>###多边主义###（填写全球治理的基本路径）是全球治理的基本路径</t>
+      <c r="C90" s="1" t="inlineStr">
+        <is>
+          <t>第二，凝聚###历史共识###（填写现实需要的内容）的现实需要</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="E91" s="1" t="inlineStr">
-        <is>
-          <t>当前，###联合国宗旨和原则###（填写未能得到有效遵守的对象）未能得到有效遵守</t>
+      <c r="D91" s="1" t="inlineStr">
+        <is>
+          <t>铭记历史是为###共同引以为戒###（填写铭记历史的目的）</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="F92" s="1" t="inlineStr">
-        <is>
-          <t>###安理会决议###（填写受到抵制的对象）受到抵制</t>
+      <c r="D92" s="1" t="inlineStr">
+        <is>
+          <t>形成关于###反法西斯战争###（填写形成正确历史认知的对象）的正确历史认知与国际共识</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="F93" s="1" t="inlineStr">
-        <is>
-          <t>###单边制裁###（填写违反国际法并破坏国际秩序的行径）等行径违反国际法并破坏国际秩序</t>
+      <c r="D93" s="1" t="inlineStr">
+        <is>
+          <t>有助于为建设###公正、合理的美好世界###（填写奠定思想基础的目标世界）奠定思想基础</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="D94" s="1" t="inlineStr">
-        <is>
-          <t>第三，从治理效能看，###有效性###（填写亟待提升的方面）亟待提升</t>
+      <c r="C94" s="1" t="inlineStr">
+        <is>
+          <t>第三，把握###发展趋势###（填写现实需要的内容）的现实需要</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="E95" s="1" t="inlineStr">
-        <is>
-          <t>###联合国2030年可持续发展议程###（填写落实进展严重滞后的议程）落实进展严重滞后</t>
+      <c r="D95" s="1" t="inlineStr">
+        <is>
+          <t>当前国际形势###变乱交织###（填写国际形势的特征）</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="E96" s="1" t="inlineStr">
-        <is>
-          <t>###气候变化、数字鸿沟###（填写日益突出的问题）等问题日益突出</t>
+      <c r="D96" s="1" t="inlineStr">
+        <is>
+          <t>需弘扬###正确二战史观###（填写需弘扬的历史观）</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="E97" s="1" t="inlineStr">
-        <is>
-          <t>###人工智能、网络空间###（填写治理存在缺位的新疆域）等新疆域治理存在缺位</t>
+      <c r="D97" s="1" t="inlineStr">
+        <is>
+          <t>深刻认识践行###真正多边主义###（填写应践行的主义）、维护###国际规则与秩序###（填写应维护的对象）的重要性</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="C98" s="1" t="inlineStr">
-        <is>
-          <t>在此背景下，###构建与改革全球治理体系###（填写国际社会的重大命题）成为国际社会重大命题</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="C99" s="1" t="inlineStr">
-        <is>
-          <t>中国提出的###全球治理倡议###（填写回应了时代之问的倡议）回应了时代之问</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="D100" s="1" t="inlineStr">
-        <is>
-          <t>该倡议引领了###全球治理变革方向###（填写引领的方向）</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="D101" s="1" t="inlineStr">
-        <is>
-          <t>该倡议符合当今世界的###紧迫需求###（填写符合的需求类型）</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>全球治理倡议是中国向世界提供的重要公共产品### ###</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="C103" s="1" t="inlineStr">
-        <is>
-          <t>核心理念与原则</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="D104" s="1" t="inlineStr">
-        <is>
-          <t>秉承###《联合国宪章》宗旨###（填写秉承的宗旨），呼应###各国普遍期待###（填写呼应的期待）</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="D105" s="1" t="inlineStr">
-        <is>
-          <t>体现中国引领应对###全球治理赤字###（填写应对的赤字类型）、推动构建###人类命运共同体###（填写推动构建的共同体）的担当</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="C106" s="1" t="inlineStr">
-        <is>
-          <t>改革路径与目标</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="D107" s="1" t="inlineStr">
-        <is>
-          <t>非###颠覆性改革###（填写改革的性质），而是提升###现行国际体系与机制###（填写提升效能的对象）的效能</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="D108" s="1" t="inlineStr">
-        <is>
-          <t>使其更适应形势，有效应对###全球挑战###（填写应对的挑战类型），更好服务###各国尤其是发展中国家###（填写服务的对象）利益</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="C109" s="1" t="inlineStr">
-        <is>
-          <t>贡献与反响</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="D110" s="1" t="inlineStr">
-        <is>
-          <t>提出###全球治理改革的中国方案###（填写提出的方案类型），贡献###治理智慧###（填写贡献的内容）</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="D111" s="1" t="inlineStr">
-        <is>
-          <t>作为重要###国际公共产品###（填写产品的属性），获广泛积极响应</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>以辩证思维认识与处理新旧关系### ###</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="C113" s="1" t="inlineStr">
-        <is>
-          <t>新旧###对立统一###（填写新旧关系的性质），相互依存贯通，可在###一定条件###（填写转化的条件）下转化</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="C114" s="1" t="inlineStr">
-        <is>
-          <t>以###联系、发展的观点###（填写看问题的观点）看问题，在###对立统一###（填写把握关系的原则）中把握关系</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="D115" s="1" t="inlineStr">
-        <is>
-          <t>用###联系眼光###（填写看待新旧关系的眼光）看待新旧，###转换思路、创造条件###（填写采取的行动），化不利为有利，寻求新突破</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="D116" s="1" t="inlineStr">
-        <is>
-          <t>用###发展眼光###（填写看待旧资源的眼光）看待旧资源，###把握趋势、找准新方向###（填写采取的行动），放大自身优势</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="C117" s="1" t="inlineStr">
-        <is>
-          <t>新旧非绝对对立，其###交织交融###（填写新旧关系的状态）能激发新活力</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>辩证否定原理### ###</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="C119" s="1" t="inlineStr">
-        <is>
-          <t>事物发展通过###内在矛盾自我否定###（填写事物发展的实现方式）实现</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="C120" s="1" t="inlineStr">
-        <is>
-          <t>（发展）否定是###旧事物向新事物###（填写否定的转变方向）的转变与质的飞跃</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="C121" s="1" t="inlineStr">
-        <is>
-          <t>（联系）新事物孕育于###旧事物###（填写新事物的孕育场所），二者通过###否定###（填写联系的方式）相联系</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="C122" s="1" t="inlineStr">
-        <is>
-          <t>新事物对旧事物###既批判又继承###（填写新事物对旧事物的态度），克服###消极因素###（填写克服的因素），保留###积极因素###（填写保留的因素）</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="C123" s="1" t="inlineStr">
-        <is>
-          <t>并非###简单否定一切###（填写否定的性质）</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="D124" s="1" t="inlineStr">
-        <is>
-          <t>而是从旧事物中吸收###合理成分###（填写吸收的内容）</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="D125" s="1" t="inlineStr">
-        <is>
-          <t>加入###新内容###（填写加入的内容）</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="D126" s="1" t="inlineStr">
-        <is>
-          <t>形成具有###新结构功能###（填写形成的事物的特征）的事物以适应变化</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="B127" s="1" t="inlineStr">
-        <is>
-          <t>为什么要改善民生### ###</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="C128" s="1" t="inlineStr">
-        <is>
-          <t>第一，###中国式现代化###（填写坚持民生为大的现代化类型）坚持民生为大</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="D129" s="1" t="inlineStr">
-        <is>
-          <t>###保障和改善民生###（填写重大任务的内容）是重大任务</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="D130" s="1" t="inlineStr">
-        <is>
-          <t>“投资于人”、服务民生，体现了以人民为中心的发展思想</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="E131" s="1" t="inlineStr">
-        <is>
-          <t>人是###消费主体、生产核心和创新源泉###（填写人在经济社会中的角色）</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="E132" s="1" t="inlineStr">
-        <is>
-          <t>投资于人的###多维需求与全面发展###（填写投资的对象）</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="F133" s="1" t="inlineStr">
-        <is>
-          <t>涵盖###就业、收入、教育、医疗###（填写涵盖的领域）等领域，旨在提升###民众福祉与能力###（填写提升的目标）</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="D134" s="1" t="inlineStr">
-        <is>
-          <t>对###高质量发展###（填写具有长远意义的领域）的长远意义</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="E135" s="1" t="inlineStr">
-        <is>
-          <t>有助于释放###消费潜力###（填写有助于释放的潜力），培育###强大国内市场###（填写培育的市场类型），畅通###国内大循环###（填写畅通的循环类型）</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="E136" s="1" t="inlineStr">
-        <is>
-          <t>可积累###人力资本###（填写积累的资本类型），激发###创新活力###（填写激发的活力类型），加快###新质生产力###（填写加快发展的生产力类型）发展，夯实###高质量发展###（填写夯实的根基类型）根基</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="C137" s="1" t="inlineStr">
-        <is>
-          <t>第二，“投资于人”是高质量发展的长远举措</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="D138" s="1" t="inlineStr">
-        <is>
-          <t>通过满足人的###全面需求###（填写满足的需求类型），促进###能消费、敢消费、愿消费###（填写促进的消费状态）</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="D139" s="1" t="inlineStr">
-        <is>
-          <t>既破解###消费增长困境###（填写破解的困境），又为###创新与新质生产力发展###（填写注入动力的领域）注入动力，巩固###发展根基###（填写巩固的根基）</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="B140" s="1" t="inlineStr">
-        <is>
-          <t>如何认识经济发展与改善民生### ###</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="C141" s="1" t="inlineStr">
-        <is>
-          <t>发展是解决民生的“总钥匙”，民生是发展的“指南针”</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="C142" s="1" t="inlineStr">
-        <is>
-          <t>第一，发展是民生的###物质基础###（填写发展的作用）</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="D143" s="1" t="inlineStr">
-        <is>
-          <t>离开###发展###（填写民生改善的前提）则民生改善无从谈起</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="D144" s="1" t="inlineStr">
-        <is>
-          <t>发展必须回应###人民期待###（填写回应的对象）、带来###实际利益###（填写带来的利益），才可持续</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="C145" s="1" t="inlineStr">
-        <is>
-          <t>第二，###民生###（填写促进发展的因素）促进发展</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="D146" s="1" t="inlineStr">
-        <is>
-          <t>抓###民生###（填写即抓发展的对象）即抓发展</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="D147" s="1" t="inlineStr">
-        <is>
-          <t>持续改善民生能缓解###群众后顾之忧###（填写缓解的担忧）</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="E148" s="1" t="inlineStr">
-        <is>
-          <t>调动###生产积极性###（填写调动的积极性），提升###消费预期###（填写提升的预期）</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="E149" s="1" t="inlineStr">
-        <is>
-          <t>从而扩大###内需###（填写扩大的需求类型）、催生###新增长点###（填写催生的增长类型）</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="C150" s="1" t="inlineStr">
-        <is>
-          <t>第三，实现###民生与发展###（填写实现良性互动的两个方面）的良性互动</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="D151" s="1" t="inlineStr">
-        <is>
-          <t>应全面把握二者###互为牵动、互为条件###（填写二者关系的特征）的关系</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="D152" s="1" t="inlineStr">
-        <is>
-          <t>推动###民生改善与经济发展###（填写推动对接的两个方面）有效对接</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="D153" s="1" t="inlineStr">
-        <is>
-          <t>形成###有机统一###（填写长效机制的特征）的长效机制</t>
+      <c r="D98" s="1" t="inlineStr">
+        <is>
+          <t>把握###国际秩序发展前景###（填写把握的前景），推动'###全球倡议###'（填写推动落实的倡议）落实</t>
         </is>
       </c>
     </row>

--- a/Note/输出.xlsx
+++ b/Note/输出.xlsx
@@ -621,7 +621,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -629,6 +629,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1011,730 +1014,582 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H98"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.888888888888889" defaultRowHeight="14.4"/>
+  <dimension ref="A1:J58"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9.66666666666667" defaultRowHeight="14.4"/>
   <cols>
-    <col width="9.66666666666667" customWidth="1" style="1" min="1" max="1"/>
-    <col width="8.888888888888889" customWidth="1" style="1" min="2" max="16384"/>
+    <col width="9.66666666666667" customWidth="1" style="3" min="1" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" s="1">
-      <c r="A1" s="3">
+    <row r="1" customFormat="1" s="3">
+      <c r="A1" s="4">
         <f>SUM(B1:AZ1)</f>
         <v/>
       </c>
-      <c r="B1" s="3">
-        <f>COUNTA(B2:B1698)/COLUMN()</f>
+      <c r="B1" s="4">
+        <f>COUNTA(B2:B2220)/COLUMN()</f>
         <v/>
       </c>
-      <c r="C1" s="3">
-        <f>COUNTA(C2:C1698)/COLUMN()</f>
+      <c r="C1" s="4">
+        <f>COUNTA(C2:C2220)/COLUMN()</f>
         <v/>
       </c>
-      <c r="D1" s="3">
-        <f>COUNTA(D2:D1698)/COLUMN()</f>
+      <c r="D1" s="4">
+        <f>COUNTA(D2:D2220)/COLUMN()</f>
         <v/>
       </c>
-      <c r="E1" s="3">
-        <f>COUNTA(E2:E1698)/COLUMN()</f>
+      <c r="E1" s="4">
+        <f>COUNTA(E2:E2220)/COLUMN()</f>
         <v/>
       </c>
-      <c r="F1" s="3">
-        <f>COUNTA(F2:F1698)/COLUMN()</f>
+      <c r="F1" s="4">
+        <f>COUNTA(F2:F2220)/COLUMN()</f>
         <v/>
       </c>
-      <c r="G1" s="3">
-        <f>COUNTA(G2:G1698)/COLUMN()</f>
+      <c r="G1" s="4">
+        <f>COUNTA(G2:G2220)/COLUMN()</f>
         <v/>
       </c>
-      <c r="H1" s="3">
-        <f>COUNTA(H2:H1698)/COLUMN()</f>
+      <c r="H1" s="4">
+        <f>COUNTA(H2:H2220)/COLUMN()</f>
         <v/>
       </c>
-    </row>
-    <row r="2" customFormat="1" s="1">
-      <c r="A2" s="1">
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+    </row>
+    <row r="2" customFormat="1" s="3">
+      <c r="A2" s="3">
         <f t="array" ref="A2">_wpsfn.SHEETSNAME(A1)</f>
         <v/>
       </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>中国的投资价值### ###</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" customFormat="1" s="1">
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>第一，坚持###高水平对外开放###（填写坚持的开放战略）</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" customFormat="1" s="1">
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>###对外开放###（填写基本国策的内容）是基本国策</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" customFormat="1" s="1">
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>正稳步推进###规则、规制等制度型开放###（填写推进的开放类型）</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" customFormat="1" s="1">
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>###利用外资政策###（填写长期稳定的政策类型）长期稳定</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" customFormat="1" s="1">
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>第二，###市场潜力巨大且转型加速###（填写中国的市场特征）</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" customFormat="1" s="1">
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t>作为全球第二大消费市场，拥有###最大规模中等收入群体###（填写拥有的消费群体特征）</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" customFormat="1" s="1">
-      <c r="D9" s="1" t="inlineStr">
-        <is>
-          <t>###绿色化、数字化、智能化###（填写转型加快的领域）转型加快，产业配套强</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" customFormat="1" s="1">
-      <c r="D10" s="1" t="inlineStr">
-        <is>
-          <t>是###科技革命与产业变革###（填写最佳应用场景的领域）的最佳应用场景</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" customFormat="1" s="1">
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>第三，###外资法规政策体系###（填写健全的体系类型）健全</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" customFormat="1" s="1">
-      <c r="D12" s="1" t="inlineStr">
-        <is>
-          <t>已形成较为完备的###利用外资法规政策与工作体系###（填写形成的体系类型）</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" customFormat="1" s="1">
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>第四，###社会环境###（填写安全稳定的领域）安全稳定</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" customFormat="1" s="1">
-      <c r="D14" s="1" t="inlineStr">
-        <is>
-          <t>长期保持###政局稳定与社会安定###（填写长期保持的状态）</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" customFormat="1" s="1">
-      <c r="D15" s="1" t="inlineStr">
-        <is>
-          <t>是国际公认的###最安全国家之一###（填写中国的国际安全地位）</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" customFormat="1" s="1">
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>抗日是持久战### ###</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" customFormat="1" s="1">
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>战争性质：是###半殖民地中国###（填写战争一方）与###帝国主义日本###（填写战争另一方）之间的决死战争</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" customFormat="1" s="1">
-      <c r="C18" s="1" t="inlineStr">
-        <is>
-          <t>第一方面：###强弱对比###（填写决定战争形态的因素）决定战争形态</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" customFormat="1" s="1">
-      <c r="D19" s="1" t="inlineStr">
-        <is>
-          <t>日本是###强国###（填写日本的实力地位）</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" customFormat="1" s="1">
-      <c r="D20" s="1" t="inlineStr">
-        <is>
-          <t>中国是###弱国###（填写中国的实力地位）</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" customFormat="1" s="1">
-      <c r="D21" s="1" t="inlineStr">
-        <is>
-          <t>###强弱对比###（填写决定战争形态的关键因素）决定了抗日战争只能是持久战</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" customFormat="1" s="1">
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>第二方面：###多因素对比###（填写决定最终胜利的因素）决定最终胜利</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" customFormat="1" s="1">
-      <c r="D23" s="1" t="inlineStr">
-        <is>
-          <t>日本是###小国###（填写日本的国家规模），进行###退步、野蛮的侵略战争###（填写日本进行的战争性质），在国际上###失道寡助###（填写日本在国际上的处境）</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" customFormat="1" s="1">
-      <c r="D24" s="1" t="inlineStr">
-        <is>
-          <t>中国是###大国###（填写中国的国家规模），进行###进步、正义的反侵略战争###（填写中国进行的战争性质），在国际上###得道多助###（填写中国在国际上的处境）</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" customFormat="1" s="1">
-      <c r="D25" s="1" t="inlineStr">
-        <is>
-          <t>中国已有政治上成熟的###中国共产党###（填写政治上成熟的政党）及其领导的###抗日根据地与人民军队###（填写党领导的抗战力量）</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" customFormat="1" s="1">
-      <c r="C26" s="1" t="inlineStr">
-        <is>
-          <t>因此，###最后胜利###（填写必将属于中国的成果）必将属于中国。</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" customFormat="1" s="1">
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>敌后战场的作用### ###</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>决策内容与意义</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="D29" s="1" t="inlineStr">
-        <is>
-          <t>为执行###全面抗战路线###（填写执行的路线），作出开辟###敌后战场###（填写开辟的战场类型）的决策</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="E30" s="1" t="inlineStr">
-        <is>
-          <t>延续###农村包围城市、武装夺取政权###（填写延续的革命道路）的道路</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="D31" s="1" t="inlineStr">
-        <is>
-          <t>###敌后战场###（填写为抗战胜利作出巨大贡献的战场）的坚持与发展为抗战胜利作出巨大贡献</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="E32" s="1" t="inlineStr">
-        <is>
-          <t>起到###改变战局的战略引领###（填写起到的作用类型）作用</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="C33" s="1" t="inlineStr">
-        <is>
-          <t>敌后战场在各阶段的作用</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="D34" s="1" t="inlineStr">
-        <is>
-          <t>战略防御阶段</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="E35" s="1" t="inlineStr">
-        <is>
-          <t>###正面战场###（填写为主战场的战场类型）为主战场</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="E36" s="1" t="inlineStr">
-        <is>
-          <t>###敌后战场###（填写是重要力量的战场类型）是重要力量</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="E37" s="1" t="inlineStr">
-        <is>
-          <t>推动战争转入###相持阶段###（填写转入的阶段），实现###持久抗战###（填写实现的战略）</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="D38" s="1" t="inlineStr">
-        <is>
-          <t>战略相持阶段</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="E39" s="1" t="inlineStr">
-        <is>
-          <t>###敌后战场###（填写逐渐成为主战场的战场）逐渐成为主战场</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="E40" s="1" t="inlineStr">
-        <is>
-          <t>极大振奋###全国信心###（填写振奋的对象）</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="E41" s="1" t="inlineStr">
-        <is>
-          <t>展现###人民战争###（填写展现的战争类型）的强大威力</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="D42" s="1" t="inlineStr">
-        <is>
-          <t>战略反攻阶段</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="E43" s="1" t="inlineStr">
-        <is>
-          <t>###敌后战场###（填写成为决胜力量的战场）成为决胜力量</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="C44" s="1" t="inlineStr">
-        <is>
-          <t>总结</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="D45" s="1" t="inlineStr">
-        <is>
-          <t>###中国共产党###（填写领导人民武装的政党）领导的人民武装在敌后战场发展壮大，由弱变强</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="D46" s="1" t="inlineStr">
-        <is>
-          <t>为夺取###最后胜利###（填写发挥决定性作用的目标）发挥决定性作用</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="1" t="inlineStr">
-        <is>
-          <t>崇尚英雄### ###</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="C48" s="1" t="inlineStr">
-        <is>
-          <t>伟大时代与英雄精神</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="D49" s="1" t="inlineStr">
-        <is>
-          <t>###伟大时代###（填写呼唤并造就英雄的时代）呼唤并造就英雄，###英雄辈出###（填写推动事业兴旺发达的因素）推动党和人民事业兴旺发达</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="D50" s="1" t="inlineStr">
-        <is>
-          <t>###崇尚英雄###（填写产生英雄的前提）才能产生英雄，###争做英雄###（填写英雄辈出的条件）方能英雄辈出</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="C51" s="1" t="inlineStr">
-        <is>
-          <t>英雄精神对民族复兴的意义</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="D52" s="1" t="inlineStr">
-        <is>
-          <t>###国家强盛与民族复兴###（填写既需物质积累又需精神文明升华的目标）既需物质积累，亦需精神文明升华</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="D53" s="1" t="inlineStr">
-        <is>
-          <t>###缅怀英烈事迹、传承英烈精神###（填写对价值观的洗礼活动）是对价值观的洗礼</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="E54" s="1" t="inlineStr">
-        <is>
-          <t>可转化为###爱国情、强国志、报国行###（填写转化的内生动力内容）的内生动力</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="C55" s="1" t="inlineStr">
-        <is>
-          <t>纪念活动的现实作用</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="D56" s="1" t="inlineStr">
-        <is>
-          <t>在###烈士纪念日###（填写追思先烈的日期）追思先烈、致敬英雄，有助于增强###历史自信、激扬历史主动精神###（填写有助于增强的精神）</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="D57" s="1" t="inlineStr">
-        <is>
-          <t>使###爱国主义与革命英雄主义###（填写成为强大精神动力的主义）成为引领向前、催人奋斗的强大精神动力</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="B58" s="1" t="inlineStr">
-        <is>
-          <t>做堂堂正正光荣自豪的中国人### ###</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="C59" s="1" t="inlineStr">
-        <is>
-          <t>一、'###堂堂正正###'的民族气节</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="D60" s="1" t="inlineStr">
-        <is>
-          <t>中华民族在磨难中###愈挫愈勇、奋起成长###（填写中华民族在磨难中的表现）</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="D61" s="1" t="inlineStr">
-        <is>
-          <t>'堂堂正正'体现为</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="E62" s="1" t="inlineStr">
-        <is>
-          <t>###危难中不甘屈辱###（填写'堂堂正正'的体现之一）</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="E63" s="1" t="inlineStr">
-        <is>
-          <t>###敢于斗争的精神坚守与担当###（填写'堂堂正正'的体现之二）</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="D64" s="1" t="inlineStr">
-        <is>
-          <t>这种姿态是百年风雨淬炼出的###民族气质###（填写淬炼出的精神品质）</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="D65" s="1" t="inlineStr">
-        <is>
-          <t>是亿万中国人的###血脉共鸣与心灵选择###（填写是亿万中国人的情感认同）</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="C66" s="1" t="inlineStr">
-        <is>
-          <t>二、'###光荣自豪###'的从容自信</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="D67" s="1" t="inlineStr">
-        <is>
-          <t>体现为</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="E68" s="1" t="inlineStr">
-        <is>
-          <t>###面对压力有信心###（填写'光荣自豪'的体现之一）</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="E69" s="1" t="inlineStr">
-        <is>
-          <t>###应对挑战有定力###（填写'光荣自豪'的体现之二）</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="E70" s="1" t="inlineStr">
-        <is>
-          <t>###面向世界有风采###（填写'光荣自豪'的体现之三）</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="D71" s="1" t="inlineStr">
-        <is>
-          <t>这是一种</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="E72" s="1" t="inlineStr">
-        <is>
-          <t>基于###历史与文化自信###（填写自信的基础）的</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="E73" s="1" t="inlineStr">
-        <is>
-          <t>###从容理性、不卑不亢、开放包容###（填写胸怀的特征）的胸怀</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="E74" s="1" t="inlineStr">
-        <is>
-          <t>根植于</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="F75" s="1" t="inlineStr">
-        <is>
-          <t>###文明传统###（填写根植的基础之一）</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="F76" s="1" t="inlineStr">
-        <is>
-          <t>###中国特色社会主义实践###（填写根植的基础之二）</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="D77" s="1" t="inlineStr">
-        <is>
-          <t>当代青年作为'###平视世界###'（填写青年的时代特征）的一代</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="E78" s="1" t="inlineStr">
-        <is>
-          <t>应在###更广阔舞台###（填写展现风貌的场所）上</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="E79" s="1" t="inlineStr">
-        <is>
-          <t>展现###昂扬风貌###（填写展现的精神面貌）</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="E80" s="1" t="inlineStr">
-        <is>
-          <t>续写###时代荣光###（填写续写的辉煌）</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="B81" s="1" t="inlineStr">
-        <is>
-          <t>正确二战史观### ###</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="C82" s="1" t="inlineStr">
-        <is>
-          <t>坚持###正确二战史观###（填写应坚持的历史观）、捍卫###历史正义###（填写应捍卫的正义类型）</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="C83" s="1" t="inlineStr">
-        <is>
-          <t>既是对###历史###（填写总结的对象）的总结</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="C84" s="1" t="inlineStr">
-        <is>
-          <t>也是对###未来###（填写指引的对象）的指引</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="C85" s="1" t="inlineStr">
-        <is>
-          <t>第一，汲取###历史教训###（填写现实需要的内容）的现实需要</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="D86" s="1" t="inlineStr">
-        <is>
-          <t>历史是###教科书与清醒剂###（填写历史的双重作用）</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="D87" s="1" t="inlineStr">
-        <is>
-          <t>坚持###正确史观###（填写坚持的史观类型），引导国际社会系统反思###二战###（填写反思的历史事件）</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="D88" s="1" t="inlineStr">
-        <is>
-          <t>（对西方）抵制###否定成果、歪曲真相的错误思潮###（填写抵制的思潮类型）</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="D89" s="1" t="inlineStr">
-        <is>
-          <t>（对日本）警惕###军国主义###（填写警惕的主义），防止###悲剧重演###（填写防止的事件）</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="C90" s="1" t="inlineStr">
-        <is>
-          <t>第二，凝聚###历史共识###（填写现实需要的内容）的现实需要</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="D91" s="1" t="inlineStr">
-        <is>
-          <t>铭记历史是为###共同引以为戒###（填写铭记历史的目的）</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="D92" s="1" t="inlineStr">
-        <is>
-          <t>形成关于###反法西斯战争###（填写形成正确历史认知的对象）的正确历史认知与国际共识</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="D93" s="1" t="inlineStr">
-        <is>
-          <t>有助于为建设###公正、合理的美好世界###（填写奠定思想基础的目标世界）奠定思想基础</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="C94" s="1" t="inlineStr">
-        <is>
-          <t>第三，把握###发展趋势###（填写现实需要的内容）的现实需要</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="D95" s="1" t="inlineStr">
-        <is>
-          <t>当前国际形势###变乱交织###（填写国际形势的特征）</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="D96" s="1" t="inlineStr">
-        <is>
-          <t>需弘扬###正确二战史观###（填写需弘扬的历史观）</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="D97" s="1" t="inlineStr">
-        <is>
-          <t>深刻认识践行###真正多边主义###（填写应践行的主义）、维护###国际规则与秩序###（填写应维护的对象）的重要性</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="D98" s="1" t="inlineStr">
-        <is>
-          <t>把握###国际秩序发展前景###（填写把握的前景），推动'###全球倡议###'（填写推动落实的倡议）落实</t>
-        </is>
-      </c>
-    </row>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>如何认识关税战、贸易战### ###</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+      <c r="I2" s="3" t="n"/>
+      <c r="J2" s="3" t="n"/>
+    </row>
+    <row r="3" customFormat="1" s="3">
+      <c r="A3" s="3" t="n"/>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>一、基本论断：贸易战与保护主义的后果</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+      <c r="I3" s="3" t="n"/>
+      <c r="J3" s="3" t="n"/>
+    </row>
+    <row r="4" customFormat="1" s="3">
+      <c r="A4" s="3" t="n"/>
+      <c r="B4" s="3" t="n"/>
+      <c r="C4" s="3" t="n"/>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>总体定性</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+      <c r="I4" s="3" t="n"/>
+      <c r="J4" s="3" t="n"/>
+    </row>
+    <row r="5" customFormat="1" s="3">
+      <c r="A5" s="3" t="n"/>
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>###贸易战、关税战没有赢家###（填写贸易战的总体定性之一）</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+      <c r="I5" s="3" t="n"/>
+      <c r="J5" s="3" t="n"/>
+    </row>
+    <row r="6" customFormat="1" s="3">
+      <c r="A6" s="3" t="n"/>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>###保护主义没有出路###（填写贸易战的总体定性之二）</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+      <c r="I6" s="3" t="n"/>
+      <c r="J6" s="3" t="n"/>
+    </row>
+    <row r="7" customFormat="1" s="3">
+      <c r="A7" s="3" t="n"/>
+      <c r="B7" s="3" t="n"/>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>二、对美国关税行为的指控</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+      <c r="I7" s="3" t="n"/>
+      <c r="J7" s="3" t="n"/>
+    </row>
+    <row r="8" customFormat="1" s="3">
+      <c r="A8" s="3" t="n"/>
+      <c r="B8" s="3" t="n"/>
+      <c r="C8" s="3" t="n"/>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>行为概述：美国以各种借口宣布对包括###中国###在内的所有贸易伙伴滥施关税（填写美国关税行为针对的对象）</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3" t="n"/>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+      <c r="I8" s="3" t="n"/>
+      <c r="J8" s="3" t="n"/>
+    </row>
+    <row r="9" customFormat="1" s="3">
+      <c r="A9" s="3" t="n"/>
+      <c r="B9" s="3" t="n"/>
+      <c r="C9" s="3" t="n"/>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>行为的四重“严重”危害</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="n"/>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+      <c r="I9" s="3" t="n"/>
+      <c r="J9" s="3" t="n"/>
+    </row>
+    <row r="10" customFormat="1" s="3">
+      <c r="A10" s="3" t="n"/>
+      <c r="B10" s="3" t="n"/>
+      <c r="C10" s="3" t="n"/>
+      <c r="D10" s="3" t="n"/>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>侵犯权益：严重侵犯###各国正当权益###（填写美国关税行为的危害之一）</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="n"/>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
+      <c r="I10" s="3" t="n"/>
+      <c r="J10" s="3" t="n"/>
+    </row>
+    <row r="11" customFormat="1" s="3">
+      <c r="A11" s="3" t="n"/>
+      <c r="B11" s="3" t="n"/>
+      <c r="C11" s="3" t="n"/>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>违反规则：严重违反###世界贸易组织规则###（填写美国关税行为的危害之二）</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+      <c r="I11" s="3" t="n"/>
+      <c r="J11" s="3" t="n"/>
+    </row>
+    <row r="12" customFormat="1" s="3">
+      <c r="A12" s="3" t="n"/>
+      <c r="B12" s="3" t="n"/>
+      <c r="C12" s="3" t="n"/>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>损害体制：严重损害###以规则为基础的多边贸易体制###（填写美国关税行为的危害之三）</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="n"/>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
+      <c r="I12" s="3" t="n"/>
+      <c r="J12" s="3" t="n"/>
+    </row>
+    <row r="13" customFormat="1" s="3">
+      <c r="A13" s="3" t="n"/>
+      <c r="B13" s="3" t="n"/>
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>冲击秩序：严重冲击###全球经济秩序稳定###（填写美国关税行为的危害之四）</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="n"/>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+      <c r="I13" s="3" t="n"/>
+      <c r="J13" s="3" t="n"/>
+    </row>
+    <row r="14" customFormat="1" s="3">
+      <c r="A14" s="3" t="n"/>
+      <c r="B14" s="3" t="n"/>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>三、对美国行为本质的分析</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="n"/>
+      <c r="E14" s="3" t="n"/>
+      <c r="F14" s="3" t="n"/>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
+      <c r="I14" s="3" t="n"/>
+      <c r="J14" s="3" t="n"/>
+    </row>
+    <row r="15" customFormat="1" s="3">
+      <c r="A15" s="3" t="n"/>
+      <c r="B15" s="3" t="n"/>
+      <c r="C15" s="3" t="n"/>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>违背基本规律与原则：美国有关做法违背###基本经济规律###和###市场原则###（填写美国做法违背的规律和原则）</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n"/>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+      <c r="I15" s="3" t="n"/>
+      <c r="J15" s="3" t="n"/>
+    </row>
+    <row r="16" customFormat="1" s="3">
+      <c r="A16" s="3" t="n"/>
+      <c r="B16" s="3" t="n"/>
+      <c r="C16" s="3" t="n"/>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>三“无视”的行径特征</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n"/>
+      <c r="F16" s="3" t="n"/>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
+      <c r="I16" s="3" t="n"/>
+      <c r="J16" s="3" t="n"/>
+    </row>
+    <row r="17" customFormat="1" s="3">
+      <c r="A17" s="3" t="n"/>
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>罔顾平衡：罔顾###多边贸易谈判达成的利益平衡结果###（填写美国行径的特征之一）</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="n"/>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+      <c r="I17" s="3" t="n"/>
+      <c r="J17" s="3" t="n"/>
+    </row>
+    <row r="18" customFormat="1" s="3">
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>无视事实：无视###美国长期从国际贸易中大量获利###的事实（填写美国行径的特征之二）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" customFormat="1" s="3">
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>滥用工具：将###关税###作为实施极限施压、谋取私利的武器（填写美国滥用的工具）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" customFormat="1" s="3">
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>行为的根本定性：这是典型的###单边主义###、###保护主义###和###经济霸凌###行径（填写美国行为的三种性质）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" customFormat="1" s="3">
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>旗号与本质的矛盾</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" customFormat="1" s="3">
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>旗号：美国打着所谓追求###“对等”“公平”###的旗号（填写美国行为的旗号）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" customFormat="1" s="3">
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>实质</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" customFormat="1" s="3">
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>搞零和博弈：搞零和博弈</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" customFormat="1" s="3">
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>追求“美国优先”：本质上是追求###“美国优先”“美国特殊”###（填写美国行为的实质之二）</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" customFormat="1" s="3">
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>四、对全球化趋势的研判与展望</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" customFormat="1" s="3">
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>当今世界的现实：当今世界是###经济全球化###塑造的世界（填写塑造当今世界的力量）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" customFormat="1" s="3">
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>共同的职责：维护###健康的国际经贸秩序###和###全球产供链安全稳定###，是各方共同的职责（填写需要维护的两个方面）</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" customFormat="1" s="3">
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>保护主义的局限性：###保护主义###改变不了###经济全球化###大势（填写局限性体现的主义和大势）</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" customFormat="1" s="3">
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>未来的必然趋势</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" customFormat="1" s="3">
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>必由之路：###经济全球化###始终是人类社会前进的必由之路（填写人类社会前进的必由之路）</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" customFormat="1" s="3">
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>时代潮流：###不可逆转的时代潮流###（填写经济全球化的性质）</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" customFormat="1" s="3">
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>为什么要倡导普惠包容的经济全球化### ###</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" customFormat="1" s="3">
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>一、普惠的经济全球化</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" customFormat="1" s="3">
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>核心目标：处理好发展与分配
+：做大并分好经济发展的“蛋糕”</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" customFormat="1" s="3">
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>确保广泛参与与共享</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" customFormat="1" s="3">
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>参与主体：让###不同国家###、###不同阶层###、###不同人群###都能参与（填写普惠全球化确保参与的三类主体）</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" customFormat="1" s="3">
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>享有成果：并享有###经济社会发展###的成果（填写普惠全球化确保享有的成果）</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" customFormat="1" s="3">
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>解决关键问题：妥善解决###国家间###和###各国内部发展失衡###问题（填写普惠全球化要解决的关键问题）</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" customFormat="1" s="3">
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>最终愿景：实现###共同发展###、###共同繁荣###（填写普惠全球化的最终愿景）</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" customFormat="1" s="3">
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>二、包容的经济全球化</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" customFormat="1" s="3">
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>尊重发展道路多样性：支持各国走出###符合自身国情的发展道路###（填写包容的经济全球化对发展道路的态度）</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" customFormat="1" s="3">
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>反对单一与排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" customFormat="1" s="3">
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>反对模式单一：不搞###发展模式的单一化###（填写包容全球化反对的做法之一）</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" customFormat="1" s="3">
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>摒弃错误主义：摒弃###损人利己的单边主义###、###保护主义###（填写包容全球化摒弃的错误主义）</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" customFormat="1" s="3">
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>维护经济系统稳定与活力</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" customFormat="1" s="3">
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>稳定供应链：维护###全球产业链供应链的稳定畅通###（填写包容全球化维护的目标之一）</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" customFormat="1" s="3">
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>保持增长动力：保持###世界经济增长活力与动力###（填写包容全球化维护的目标之二）</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" customFormat="1" s="3">
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>三、普惠包容全球化的性质与中国角色</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" customFormat="1" s="3">
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>根本定位：普惠包容全球化是###人心所向###、###人间正道###（填写普惠包容全球化的根本定位）</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" customFormat="1" s="3">
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>中国倡导的现实意义：具有针对性：中国倡导并推动此举，有着###现实针对性###和###战略指导性###（填写中国倡导的现实意义）</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" customFormat="1" s="3">
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>中国的引领与贡献</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" customFormat="1" s="3">
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>引领方向：将引领###经济全球化正确方向###（填写中国在全球化中的角色之一）</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" customFormat="1" s="3">
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>贡献智慧：为解决当今世界面临的一系列###重大问题和挑战###贡献中国智慧（填写中国贡献智慧的对象）</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" customFormat="1" s="3">
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>提供依托：为构建###人类命运共同体###提供坚实依托（填写中国提供依托的目标）</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" customFormat="1" s="3">
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>总体评价：###普惠包容全球化###具有重要深远意义（填写具有重要深远意义的事物）</t>
+        </is>
+      </c>
+    </row>
+    <row r="58"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/Note/输出.xlsx
+++ b/Note/输出.xlsx
@@ -625,15 +625,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1014,13 +1012,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J58"/>
+  <dimension ref="A1:M45"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.66666666666667" defaultRowHeight="14.4"/>
   <cols>
     <col width="9.66666666666667" customWidth="1" style="3" min="1" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" s="3">
+    <row r="1" s="3">
       <c r="A1" s="4">
         <f>SUM(B1:AZ1)</f>
         <v/>
@@ -1053,543 +1051,794 @@
         <f>COUNTA(H2:H2220)/COLUMN()</f>
         <v/>
       </c>
-      <c r="I1" s="3" t="n"/>
-      <c r="J1" s="3" t="n"/>
-    </row>
-    <row r="2" customFormat="1" s="3">
-      <c r="A2" s="3">
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="2" t="n"/>
+    </row>
+    <row r="2" s="3">
+      <c r="A2" s="2">
         <f t="array" ref="A2">_wpsfn.SHEETSNAME(A1)</f>
         <v/>
       </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>如何认识关税战、贸易战### ###</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="3" t="n"/>
-      <c r="H2" s="3" t="n"/>
-      <c r="I2" s="3" t="n"/>
-      <c r="J2" s="3" t="n"/>
-    </row>
-    <row r="3" customFormat="1" s="3">
-      <c r="A3" s="3" t="n"/>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>一、基本论断：贸易战与保护主义的后果</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="n"/>
-      <c r="H3" s="3" t="n"/>
-      <c r="I3" s="3" t="n"/>
-      <c r="J3" s="3" t="n"/>
-    </row>
-    <row r="4" customFormat="1" s="3">
-      <c r="A4" s="3" t="n"/>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>总体定性</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="n"/>
-      <c r="F4" s="3" t="n"/>
-      <c r="G4" s="3" t="n"/>
-      <c r="H4" s="3" t="n"/>
-      <c r="I4" s="3" t="n"/>
-      <c r="J4" s="3" t="n"/>
-    </row>
-    <row r="5" customFormat="1" s="3">
-      <c r="A5" s="3" t="n"/>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>###贸易战、关税战没有赢家###（填写贸易战的总体定性之一）</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="3" t="n"/>
-      <c r="H5" s="3" t="n"/>
-      <c r="I5" s="3" t="n"/>
-      <c r="J5" s="3" t="n"/>
-    </row>
-    <row r="6" customFormat="1" s="3">
-      <c r="A6" s="3" t="n"/>
-      <c r="B6" s="3" t="n"/>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="3" t="n"/>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>###保护主义没有出路###（填写贸易战的总体定性之二）</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="n"/>
-      <c r="G6" s="3" t="n"/>
-      <c r="H6" s="3" t="n"/>
-      <c r="I6" s="3" t="n"/>
-      <c r="J6" s="3" t="n"/>
-    </row>
-    <row r="7" customFormat="1" s="3">
-      <c r="A7" s="3" t="n"/>
-      <c r="B7" s="3" t="n"/>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>二、对美国关税行为的指控</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="n"/>
-      <c r="E7" s="3" t="n"/>
-      <c r="F7" s="3" t="n"/>
-      <c r="G7" s="3" t="n"/>
-      <c r="H7" s="3" t="n"/>
-      <c r="I7" s="3" t="n"/>
-      <c r="J7" s="3" t="n"/>
-    </row>
-    <row r="8" customFormat="1" s="3">
-      <c r="A8" s="3" t="n"/>
-      <c r="B8" s="3" t="n"/>
-      <c r="C8" s="3" t="n"/>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>行为概述：美国以各种借口宣布对包括###中国###在内的所有贸易伙伴滥施关税（填写美国关税行为针对的对象）</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="n"/>
-      <c r="F8" s="3" t="n"/>
-      <c r="G8" s="3" t="n"/>
-      <c r="H8" s="3" t="n"/>
-      <c r="I8" s="3" t="n"/>
-      <c r="J8" s="3" t="n"/>
-    </row>
-    <row r="9" customFormat="1" s="3">
-      <c r="A9" s="3" t="n"/>
-      <c r="B9" s="3" t="n"/>
-      <c r="C9" s="3" t="n"/>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>行为的四重“严重”危害</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="n"/>
-      <c r="F9" s="3" t="n"/>
-      <c r="G9" s="3" t="n"/>
-      <c r="H9" s="3" t="n"/>
-      <c r="I9" s="3" t="n"/>
-      <c r="J9" s="3" t="n"/>
-    </row>
-    <row r="10" customFormat="1" s="3">
-      <c r="A10" s="3" t="n"/>
-      <c r="B10" s="3" t="n"/>
-      <c r="C10" s="3" t="n"/>
-      <c r="D10" s="3" t="n"/>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>侵犯权益：严重侵犯###各国正当权益###（填写美国关税行为的危害之一）</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="n"/>
-      <c r="G10" s="3" t="n"/>
-      <c r="H10" s="3" t="n"/>
-      <c r="I10" s="3" t="n"/>
-      <c r="J10" s="3" t="n"/>
-    </row>
-    <row r="11" customFormat="1" s="3">
-      <c r="A11" s="3" t="n"/>
-      <c r="B11" s="3" t="n"/>
-      <c r="C11" s="3" t="n"/>
-      <c r="D11" s="3" t="n"/>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>违反规则：严重违反###世界贸易组织规则###（填写美国关税行为的危害之二）</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="n"/>
-      <c r="G11" s="3" t="n"/>
-      <c r="H11" s="3" t="n"/>
-      <c r="I11" s="3" t="n"/>
-      <c r="J11" s="3" t="n"/>
-    </row>
-    <row r="12" customFormat="1" s="3">
-      <c r="A12" s="3" t="n"/>
-      <c r="B12" s="3" t="n"/>
-      <c r="C12" s="3" t="n"/>
-      <c r="D12" s="3" t="n"/>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>损害体制：严重损害###以规则为基础的多边贸易体制###（填写美国关税行为的危害之三）</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="n"/>
-      <c r="G12" s="3" t="n"/>
-      <c r="H12" s="3" t="n"/>
-      <c r="I12" s="3" t="n"/>
-      <c r="J12" s="3" t="n"/>
-    </row>
-    <row r="13" customFormat="1" s="3">
-      <c r="A13" s="3" t="n"/>
-      <c r="B13" s="3" t="n"/>
-      <c r="C13" s="3" t="n"/>
-      <c r="D13" s="3" t="n"/>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>冲击秩序：严重冲击###全球经济秩序稳定###（填写美国关税行为的危害之四）</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="n"/>
-      <c r="G13" s="3" t="n"/>
-      <c r="H13" s="3" t="n"/>
-      <c r="I13" s="3" t="n"/>
-      <c r="J13" s="3" t="n"/>
-    </row>
-    <row r="14" customFormat="1" s="3">
-      <c r="A14" s="3" t="n"/>
-      <c r="B14" s="3" t="n"/>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>三、对美国行为本质的分析</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="n"/>
-      <c r="E14" s="3" t="n"/>
-      <c r="F14" s="3" t="n"/>
-      <c r="G14" s="3" t="n"/>
-      <c r="H14" s="3" t="n"/>
-      <c r="I14" s="3" t="n"/>
-      <c r="J14" s="3" t="n"/>
-    </row>
-    <row r="15" customFormat="1" s="3">
-      <c r="A15" s="3" t="n"/>
-      <c r="B15" s="3" t="n"/>
-      <c r="C15" s="3" t="n"/>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>违背基本规律与原则：美国有关做法违背###基本经济规律###和###市场原则###（填写美国做法违背的规律和原则）</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="n"/>
-      <c r="F15" s="3" t="n"/>
-      <c r="G15" s="3" t="n"/>
-      <c r="H15" s="3" t="n"/>
-      <c r="I15" s="3" t="n"/>
-      <c r="J15" s="3" t="n"/>
-    </row>
-    <row r="16" customFormat="1" s="3">
-      <c r="A16" s="3" t="n"/>
-      <c r="B16" s="3" t="n"/>
-      <c r="C16" s="3" t="n"/>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>三“无视”的行径特征</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="n"/>
-      <c r="F16" s="3" t="n"/>
-      <c r="G16" s="3" t="n"/>
-      <c r="H16" s="3" t="n"/>
-      <c r="I16" s="3" t="n"/>
-      <c r="J16" s="3" t="n"/>
-    </row>
-    <row r="17" customFormat="1" s="3">
-      <c r="A17" s="3" t="n"/>
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="3" t="n"/>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>罔顾平衡：罔顾###多边贸易谈判达成的利益平衡结果###（填写美国行径的特征之一）</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="n"/>
-      <c r="G17" s="3" t="n"/>
-      <c r="H17" s="3" t="n"/>
-      <c r="I17" s="3" t="n"/>
-      <c r="J17" s="3" t="n"/>
-    </row>
-    <row r="18" customFormat="1" s="3">
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>无视事实：无视###美国长期从国际贸易中大量获利###的事实（填写美国行径的特征之二）</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" customFormat="1" s="3">
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>滥用工具：将###关税###作为实施极限施压、谋取私利的武器（填写美国滥用的工具）</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" customFormat="1" s="3">
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>行为的根本定性：这是典型的###单边主义###、###保护主义###和###经济霸凌###行径（填写美国行为的三种性质）</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" customFormat="1" s="3">
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>旗号与本质的矛盾</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" customFormat="1" s="3">
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>旗号：美国打着所谓追求###“对等”“公平”###的旗号（填写美国行为的旗号）</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" customFormat="1" s="3">
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>实质</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" customFormat="1" s="3">
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>搞零和博弈：搞零和博弈</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" customFormat="1" s="3">
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>追求“美国优先”：本质上是追求###“美国优先”“美国特殊”###（填写美国行为的实质之二）</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" customFormat="1" s="3">
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>四、对全球化趋势的研判与展望</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" customFormat="1" s="3">
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>当今世界的现实：当今世界是###经济全球化###塑造的世界（填写塑造当今世界的力量）</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" customFormat="1" s="3">
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>共同的职责：维护###健康的国际经贸秩序###和###全球产供链安全稳定###，是各方共同的职责（填写需要维护的两个方面）</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" customFormat="1" s="3">
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>保护主义的局限性：###保护主义###改变不了###经济全球化###大势（填写局限性体现的主义和大势）</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" customFormat="1" s="3">
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>未来的必然趋势</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" customFormat="1" s="3">
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>必由之路：###经济全球化###始终是人类社会前进的必由之路（填写人类社会前进的必由之路）</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" customFormat="1" s="3">
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>时代潮流：###不可逆转的时代潮流###（填写经济全球化的性质）</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" customFormat="1" s="3">
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>为什么要倡导普惠包容的经济全球化### ###</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" customFormat="1" s="3">
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>一、普惠的经济全球化</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" customFormat="1" s="3">
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>核心目标：处理好发展与分配
-：做大并分好经济发展的“蛋糕”</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" customFormat="1" s="3">
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>确保广泛参与与共享</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" customFormat="1" s="3">
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>参与主体：让###不同国家###、###不同阶层###、###不同人群###都能参与（填写普惠全球化确保参与的三类主体）</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" customFormat="1" s="3">
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>享有成果：并享有###经济社会发展###的成果（填写普惠全球化确保享有的成果）</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" customFormat="1" s="3">
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>解决关键问题：妥善解决###国家间###和###各国内部发展失衡###问题（填写普惠全球化要解决的关键问题）</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" customFormat="1" s="3">
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>最终愿景：实现###共同发展###、###共同繁荣###（填写普惠全球化的最终愿景）</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" customFormat="1" s="3">
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>二、包容的经济全球化</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" customFormat="1" s="3">
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>尊重发展道路多样性：支持各国走出###符合自身国情的发展道路###（填写包容的经济全球化对发展道路的态度）</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" customFormat="1" s="3">
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>反对单一与排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" customFormat="1" s="3">
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t>反对模式单一：不搞###发展模式的单一化###（填写包容全球化反对的做法之一）</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" customFormat="1" s="3">
-      <c r="E45" s="3" t="inlineStr">
-        <is>
-          <t>摒弃错误主义：摒弃###损人利己的单边主义###、###保护主义###（填写包容全球化摒弃的错误主义）</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" customFormat="1" s="3">
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>维护经济系统稳定与活力</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" customFormat="1" s="3">
-      <c r="E47" s="3" t="inlineStr">
-        <is>
-          <t>稳定供应链：维护###全球产业链供应链的稳定畅通###（填写包容全球化维护的目标之一）</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" customFormat="1" s="3">
-      <c r="E48" s="3" t="inlineStr">
-        <is>
-          <t>保持增长动力：保持###世界经济增长活力与动力###（填写包容全球化维护的目标之二）</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" customFormat="1" s="3">
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>三、普惠包容全球化的性质与中国角色</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" customFormat="1" s="3">
-      <c r="D50" s="3" t="inlineStr">
-        <is>
-          <t>根本定位：普惠包容全球化是###人心所向###、###人间正道###（填写普惠包容全球化的根本定位）</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" customFormat="1" s="3">
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>中国倡导的现实意义：具有针对性：中国倡导并推动此举，有着###现实针对性###和###战略指导性###（填写中国倡导的现实意义）</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" customFormat="1" s="3">
-      <c r="D52" s="3" t="inlineStr">
-        <is>
-          <t>中国的引领与贡献</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" customFormat="1" s="3">
-      <c r="E53" s="3" t="inlineStr">
-        <is>
-          <t>引领方向：将引领###经济全球化正确方向###（填写中国在全球化中的角色之一）</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" customFormat="1" s="3">
-      <c r="E54" s="3" t="inlineStr">
-        <is>
-          <t>贡献智慧：为解决当今世界面临的一系列###重大问题和挑战###贡献中国智慧（填写中国贡献智慧的对象）</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" customFormat="1" s="3">
-      <c r="E55" s="3" t="inlineStr">
-        <is>
-          <t>提供依托：为构建###人类命运共同体###提供坚实依托（填写中国提供依托的目标）</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" customFormat="1" s="3">
-      <c r="C56" s="3" t="inlineStr">
-        <is>
-          <t>总体评价：###普惠包容全球化###具有重要深远意义（填写具有重要深远意义的事物）</t>
-        </is>
-      </c>
-    </row>
-    <row r="58"/>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>防沙治沙是恢复原貌### ###</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
+      <c r="L2" s="2" t="n"/>
+    </row>
+    <row r="3" s="3">
+      <c r="A3" s="2" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>一、总的核心原则</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+    </row>
+    <row r="4" s="3">
+      <c r="A4" s="2" t="n"/>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>生态保护和修复既要###尊重客观规律###（填写核心原则）</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="n"/>
+      <c r="K4" s="2" t="n"/>
+      <c r="L4" s="2" t="n"/>
+    </row>
+    <row r="5" s="3">
+      <c r="A5" s="2" t="n"/>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>也要###充分发挥主观能动性###（填写核心原则）</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
+      <c r="J5" s="2" t="n"/>
+      <c r="K5" s="2" t="n"/>
+      <c r="L5" s="2" t="n"/>
+    </row>
+    <row r="6" s="3">
+      <c r="A6" s="2" t="n"/>
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>二、尊重客观规律是前提</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
+      <c r="J6" s="2" t="n"/>
+      <c r="K6" s="2" t="n"/>
+      <c r="L6" s="2" t="n"/>
+    </row>
+    <row r="7" s="3">
+      <c r="A7" s="2" t="n"/>
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>基本定位：###尊重客观规律###是正确发挥主观能动性的前提（填写核心概念）</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
+      <c r="G7" s="2" t="n"/>
+      <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="n"/>
+      <c r="J7" s="2" t="n"/>
+      <c r="K7" s="2" t="n"/>
+      <c r="L7" s="2" t="n"/>
+    </row>
+    <row r="8" s="3">
+      <c r="A8" s="2" t="n"/>
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>根本定义：规律是事物变化发展过程中###内在的、本质的、必然的联系###（填写规律的本质特征）</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
+      <c r="G8" s="2" t="n"/>
+      <c r="H8" s="2" t="n"/>
+      <c r="I8" s="2" t="n"/>
+      <c r="J8" s="2" t="n"/>
+      <c r="K8" s="2" t="n"/>
+      <c r="L8" s="2" t="n"/>
+    </row>
+    <row r="9" s="3">
+      <c r="A9" s="2" t="n"/>
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>###正确行动的基础###（填写作用或地位）</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" s="2" t="n"/>
+      <c r="H9" s="2" t="n"/>
+      <c r="I9" s="2" t="n"/>
+      <c r="J9" s="2" t="n"/>
+      <c r="K9" s="2" t="n"/>
+      <c r="L9" s="2" t="n"/>
+    </row>
+    <row r="10" s="3">
+      <c r="A10" s="2" t="n"/>
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>认识世界的前提：人们只有在###认识和掌握客观规律###的基础上，才能正确地认识世界（填写前提条件）</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="n"/>
+      <c r="G10" s="2" t="n"/>
+      <c r="H10" s="2" t="n"/>
+      <c r="I10" s="2" t="n"/>
+      <c r="J10" s="2" t="n"/>
+      <c r="K10" s="2" t="n"/>
+      <c r="L10" s="2" t="n"/>
+    </row>
+    <row r="11" s="3">
+      <c r="A11" s="2" t="n"/>
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>改造世界的前提：才能有效地改造世界</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="n"/>
+      <c r="G11" s="2" t="n"/>
+      <c r="H11" s="2" t="n"/>
+      <c r="I11" s="2" t="n"/>
+      <c r="J11" s="2" t="n"/>
+      <c r="K11" s="2" t="n"/>
+      <c r="L11" s="2" t="n"/>
+    </row>
+    <row r="12" s="3">
+      <c r="A12" s="2" t="n"/>
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>三、必须充分发挥主观能动性</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" s="2" t="n"/>
+      <c r="F12" s="2" t="n"/>
+      <c r="G12" s="2" t="n"/>
+      <c r="H12" s="2" t="n"/>
+      <c r="I12" s="2" t="n"/>
+      <c r="J12" s="2" t="n"/>
+      <c r="K12" s="2" t="n"/>
+      <c r="L12" s="2" t="n"/>
+    </row>
+    <row r="13" s="3">
+      <c r="A13" s="2" t="n"/>
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>能动性的关键作用：只有###充分发挥主观能动性###，才能正确认识和利用客观规律（填写关键作用的前提）</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n"/>
+      <c r="F13" s="2" t="n"/>
+      <c r="G13" s="2" t="n"/>
+      <c r="H13" s="2" t="n"/>
+      <c r="I13" s="2" t="n"/>
+      <c r="J13" s="2" t="n"/>
+      <c r="K13" s="2" t="n"/>
+      <c r="L13" s="2" t="n"/>
+    </row>
+    <row r="14" s="3">
+      <c r="A14" s="2" t="n"/>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>对规律客观性的正确态度</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n"/>
+      <c r="F14" s="2" t="n"/>
+      <c r="G14" s="2" t="n"/>
+      <c r="H14" s="2" t="n"/>
+      <c r="I14" s="2" t="n"/>
+      <c r="J14" s="2" t="n"/>
+      <c r="K14" s="2" t="n"/>
+      <c r="L14" s="2" t="n"/>
+    </row>
+    <row r="15" s="3">
+      <c r="A15" s="2" t="n"/>
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n"/>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>非消极无为：###承认规律的客观性###，并非说人在规律面前无能为力、无所作为（填写正确观点）</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="n"/>
+      <c r="G15" s="2" t="n"/>
+      <c r="H15" s="2" t="n"/>
+      <c r="I15" s="2" t="n"/>
+      <c r="J15" s="2" t="n"/>
+      <c r="K15" s="2" t="n"/>
+      <c r="L15" s="2" t="n"/>
+    </row>
+    <row r="16" s="3">
+      <c r="A16" s="2" t="n"/>
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="n"/>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>###人的能动作用###（填写人的能力）</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="n"/>
+      <c r="G16" s="2" t="n"/>
+      <c r="H16" s="2" t="n"/>
+      <c r="I16" s="2" t="n"/>
+      <c r="J16" s="2" t="n"/>
+      <c r="K16" s="2" t="n"/>
+      <c r="L16" s="2" t="n"/>
+    </row>
+    <row r="17" s="3">
+      <c r="A17" s="2" t="n"/>
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n"/>
+      <c r="E17" s="2" t="n"/>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>能够认识规律：###人能够通过自觉活动去认识规律###（填写人的能力）</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="n"/>
+      <c r="H17" s="2" t="n"/>
+      <c r="I17" s="2" t="n"/>
+      <c r="J17" s="2" t="n"/>
+      <c r="K17" s="2" t="n"/>
+      <c r="L17" s="2" t="n"/>
+    </row>
+    <row r="18" s="3">
+      <c r="B18" s="2" t="n"/>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="2" t="n"/>
+      <c r="E18" s="2" t="n"/>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>能够改造世界：并能###按照客观规律去改造世界###，以满足自身的需要（填写改造世界的方式）</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="n"/>
+      <c r="H18" s="2" t="n"/>
+      <c r="I18" s="2" t="n"/>
+      <c r="J18" s="2" t="n"/>
+      <c r="K18" s="2" t="n"/>
+      <c r="L18" s="2" t="n"/>
+    </row>
+    <row r="19" s="3">
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>四、实例：自然生态系统的治理</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n"/>
+      <c r="E19" s="2" t="n"/>
+      <c r="F19" s="2" t="n"/>
+      <c r="G19" s="2" t="n"/>
+      <c r="H19" s="2" t="n"/>
+      <c r="I19" s="2" t="n"/>
+      <c r="J19" s="2" t="n"/>
+      <c r="K19" s="2" t="n"/>
+      <c r="L19" s="2" t="n"/>
+    </row>
+    <row r="20" s="3">
+      <c r="B20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>生态系统的基本属性</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n"/>
+      <c r="F20" s="2" t="n"/>
+      <c r="G20" s="2" t="n"/>
+      <c r="H20" s="2" t="n"/>
+      <c r="I20" s="2" t="n"/>
+      <c r="J20" s="2" t="n"/>
+      <c r="K20" s="2" t="n"/>
+      <c r="L20" s="2" t="n"/>
+    </row>
+    <row r="21" s="3">
+      <c r="B21" s="2" t="n"/>
+      <c r="C21" s="2" t="n"/>
+      <c r="D21" s="2" t="n"/>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>有机生命躯体：###自然生态系统是一个有机生命躯体###（填写生态系统的比喻或属性）</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="n"/>
+      <c r="G21" s="2" t="n"/>
+      <c r="H21" s="2" t="n"/>
+      <c r="I21" s="2" t="n"/>
+      <c r="J21" s="2" t="n"/>
+      <c r="K21" s="2" t="n"/>
+      <c r="L21" s="2" t="n"/>
+    </row>
+    <row r="22" s="3">
+      <c r="B22" s="2" t="n"/>
+      <c r="C22" s="2" t="n"/>
+      <c r="D22" s="2" t="n"/>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>具有客观规律：###有其自身发展演化的客观规律###，要充分尊重和顺应自然（填写生态系统的特点）</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="n"/>
+      <c r="G22" s="2" t="n"/>
+      <c r="H22" s="2" t="n"/>
+      <c r="I22" s="2" t="n"/>
+      <c r="J22" s="2" t="n"/>
+      <c r="K22" s="2" t="n"/>
+      <c r="L22" s="2" t="n"/>
+    </row>
+    <row r="23" s="3">
+      <c r="B23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>荒漠治理的辩证实践</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n"/>
+      <c r="F23" s="2" t="n"/>
+      <c r="G23" s="2" t="n"/>
+      <c r="H23" s="2" t="n"/>
+      <c r="I23" s="2" t="n"/>
+      <c r="J23" s="2" t="n"/>
+      <c r="K23" s="2" t="n"/>
+      <c r="L23" s="2" t="n"/>
+    </row>
+    <row r="24" s="3">
+      <c r="B24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n"/>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>认识到荒漠的价值：###认识到天然的荒漠也是一种有价值的生态系统###（填写对荒漠的认识）</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="n"/>
+      <c r="G24" s="2" t="n"/>
+      <c r="H24" s="2" t="n"/>
+      <c r="I24" s="2" t="n"/>
+      <c r="J24" s="2" t="n"/>
+      <c r="K24" s="2" t="n"/>
+      <c r="L24" s="2" t="n"/>
+    </row>
+    <row r="25" s="3">
+      <c r="B25" s="2" t="n"/>
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="n"/>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>治理实践中的平衡</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="n"/>
+      <c r="G25" s="2" t="n"/>
+      <c r="H25" s="2" t="n"/>
+      <c r="I25" s="2" t="n"/>
+      <c r="J25" s="2" t="n"/>
+      <c r="K25" s="2" t="n"/>
+      <c r="L25" s="2" t="n"/>
+    </row>
+    <row r="26" s="3">
+      <c r="B26" s="2" t="n"/>
+      <c r="C26" s="2" t="n"/>
+      <c r="D26" s="2" t="n"/>
+      <c r="E26" s="2" t="n"/>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>主动治理：###人们在发挥主观能动性治理荒漠化的同时###（填写治理实践）</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="n"/>
+      <c r="H26" s="2" t="n"/>
+      <c r="I26" s="2" t="n"/>
+      <c r="J26" s="2" t="n"/>
+      <c r="K26" s="2" t="n"/>
+      <c r="L26" s="2" t="n"/>
+    </row>
+    <row r="27" s="3">
+      <c r="B27" s="2" t="n"/>
+      <c r="C27" s="2" t="n"/>
+      <c r="D27" s="2" t="n"/>
+      <c r="E27" s="2" t="n"/>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>顺应与保留：###也保留了地球上原有的沙漠和荒漠###（填写治理实践的另一面）</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="n"/>
+      <c r="H27" s="2" t="n"/>
+      <c r="I27" s="2" t="n"/>
+      <c r="J27" s="2" t="n"/>
+      <c r="K27" s="2" t="n"/>
+      <c r="L27" s="2" t="n"/>
+    </row>
+    <row r="28" s="3">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>人与自然的关系### ###</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n"/>
+      <c r="D28" s="2" t="n"/>
+      <c r="E28" s="2" t="n"/>
+      <c r="F28" s="2" t="n"/>
+      <c r="G28" s="2" t="n"/>
+      <c r="H28" s="2" t="n"/>
+      <c r="I28" s="2" t="n"/>
+      <c r="J28" s="2" t="n"/>
+      <c r="K28" s="2" t="n"/>
+      <c r="L28" s="2" t="n"/>
+      <c r="M28" s="2" t="n"/>
+    </row>
+    <row r="29" s="3">
+      <c r="B29" s="2" t="n"/>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>一、自然地理环境的基础性地位：作为生存与发展的根本条件</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n"/>
+      <c r="E29" s="2" t="n"/>
+      <c r="F29" s="2" t="n"/>
+      <c r="G29" s="2" t="n"/>
+      <c r="H29" s="2" t="n"/>
+      <c r="I29" s="2" t="n"/>
+      <c r="J29" s="2" t="n"/>
+      <c r="K29" s="2" t="n"/>
+      <c r="L29" s="2" t="n"/>
+      <c r="M29" s="2" t="n"/>
+    </row>
+    <row r="30" s="3">
+      <c r="B30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>永恒且必要的条件：###自然地理环境是人类社会生存和发展永恒的、必要的条件###（填写自然地理环境的地位）</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="n"/>
+      <c r="F30" s="2" t="n"/>
+      <c r="G30" s="2" t="n"/>
+      <c r="H30" s="2" t="n"/>
+      <c r="I30" s="2" t="n"/>
+      <c r="J30" s="2" t="n"/>
+      <c r="K30" s="2" t="n"/>
+      <c r="L30" s="2" t="n"/>
+      <c r="M30" s="2" t="n"/>
+    </row>
+    <row r="31" s="3">
+      <c r="B31" s="2" t="n"/>
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>生活与生产的自然基础：###是人们生活和生产的自然基础###（填写自然地理环境的作用）</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="n"/>
+      <c r="F31" s="2" t="n"/>
+      <c r="G31" s="2" t="n"/>
+      <c r="H31" s="2" t="n"/>
+      <c r="I31" s="2" t="n"/>
+      <c r="J31" s="2" t="n"/>
+      <c r="K31" s="2" t="n"/>
+      <c r="L31" s="2" t="n"/>
+      <c r="M31" s="2" t="n"/>
+    </row>
+    <row r="32" s="3">
+      <c r="B32" s="2" t="n"/>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>二、生态平衡与资源利用的重要性</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n"/>
+      <c r="E32" s="2" t="n"/>
+      <c r="F32" s="2" t="n"/>
+      <c r="G32" s="2" t="n"/>
+      <c r="H32" s="2" t="n"/>
+      <c r="I32" s="2" t="n"/>
+      <c r="J32" s="2" t="n"/>
+      <c r="K32" s="2" t="n"/>
+      <c r="L32" s="2" t="n"/>
+      <c r="M32" s="2" t="n"/>
+    </row>
+    <row r="33" s="3">
+      <c r="B33" s="2" t="n"/>
+      <c r="C33" s="2" t="n"/>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>生态平衡的社会作用：###自然生态平衡对社会生活起着重要作用###（填写生态平衡的作用）</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="n"/>
+      <c r="F33" s="2" t="n"/>
+      <c r="G33" s="2" t="n"/>
+      <c r="H33" s="2" t="n"/>
+      <c r="I33" s="2" t="n"/>
+      <c r="J33" s="2" t="n"/>
+      <c r="K33" s="2" t="n"/>
+      <c r="L33" s="2" t="n"/>
+      <c r="M33" s="2" t="n"/>
+    </row>
+    <row r="34" s="3">
+      <c r="B34" s="2" t="n"/>
+      <c r="C34" s="2" t="n"/>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>合理利用与保护的必要性：###合理地利用自然资源，保护生态平衡，是社会得以正常发展的必要条件###（填写必要性）</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="n"/>
+      <c r="F34" s="2" t="n"/>
+      <c r="G34" s="2" t="n"/>
+      <c r="H34" s="2" t="n"/>
+      <c r="I34" s="2" t="n"/>
+      <c r="J34" s="2" t="n"/>
+      <c r="K34" s="2" t="n"/>
+      <c r="L34" s="2" t="n"/>
+      <c r="M34" s="2" t="n"/>
+    </row>
+    <row r="35" s="3">
+      <c r="B35" s="2" t="n"/>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>三、人类实践必须遵循自然规律</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n"/>
+      <c r="E35" s="2" t="n"/>
+      <c r="F35" s="2" t="n"/>
+      <c r="G35" s="2" t="n"/>
+      <c r="H35" s="2" t="n"/>
+      <c r="I35" s="2" t="n"/>
+      <c r="J35" s="2" t="n"/>
+      <c r="K35" s="2" t="n"/>
+      <c r="L35" s="2" t="n"/>
+      <c r="M35" s="2" t="n"/>
+    </row>
+    <row r="36" s="3">
+      <c r="B36" s="2" t="n"/>
+      <c r="C36" s="2" t="n"/>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>改造世界的双重性</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="n"/>
+      <c r="F36" s="2" t="n"/>
+      <c r="G36" s="2" t="n"/>
+      <c r="H36" s="2" t="n"/>
+      <c r="I36" s="2" t="n"/>
+      <c r="J36" s="2" t="n"/>
+      <c r="K36" s="2" t="n"/>
+      <c r="L36" s="2" t="n"/>
+      <c r="M36" s="2" t="n"/>
+    </row>
+    <row r="37" s="3">
+      <c r="B37" s="2" t="n"/>
+      <c r="C37" s="2" t="n"/>
+      <c r="D37" s="2" t="n"/>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>按意愿改造：###人类在实践活动中按照自己的意愿改造世界###（填写人类实践的特点）</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="n"/>
+      <c r="G37" s="2" t="n"/>
+      <c r="H37" s="2" t="n"/>
+      <c r="I37" s="2" t="n"/>
+      <c r="J37" s="2" t="n"/>
+      <c r="K37" s="2" t="n"/>
+      <c r="L37" s="2" t="n"/>
+      <c r="M37" s="2" t="n"/>
+    </row>
+    <row r="38" s="3">
+      <c r="B38" s="2" t="n"/>
+      <c r="C38" s="2" t="n"/>
+      <c r="D38" s="2" t="n"/>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>必须遵循规律：的同时###必须遵循自然规律###（填写必须遵循的内容）</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="n"/>
+      <c r="G38" s="2" t="n"/>
+      <c r="H38" s="2" t="n"/>
+      <c r="I38" s="2" t="n"/>
+      <c r="J38" s="2" t="n"/>
+      <c r="K38" s="2" t="n"/>
+      <c r="L38" s="2" t="n"/>
+      <c r="M38" s="2" t="n"/>
+    </row>
+    <row r="39" s="3">
+      <c r="B39" s="2" t="n"/>
+      <c r="C39" s="2" t="n"/>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>违背规律的后果：否则将会###导致人与自然关系的失衡###（填写后果）</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="n"/>
+      <c r="F39" s="2" t="n"/>
+      <c r="G39" s="2" t="n"/>
+      <c r="H39" s="2" t="n"/>
+      <c r="I39" s="2" t="n"/>
+      <c r="J39" s="2" t="n"/>
+      <c r="K39" s="2" t="n"/>
+      <c r="L39" s="2" t="n"/>
+      <c r="M39" s="2" t="n"/>
+    </row>
+    <row r="40" s="3">
+      <c r="B40" s="2" t="n"/>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>四、马克思的观点及和谐共生的体现</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n"/>
+      <c r="E40" s="2" t="n"/>
+      <c r="F40" s="2" t="n"/>
+      <c r="G40" s="2" t="n"/>
+      <c r="H40" s="2" t="n"/>
+      <c r="I40" s="2" t="n"/>
+      <c r="J40" s="2" t="n"/>
+      <c r="K40" s="2" t="n"/>
+      <c r="L40" s="2" t="n"/>
+      <c r="M40" s="2" t="n"/>
+    </row>
+    <row r="41" s="3">
+      <c r="B41" s="2" t="n"/>
+      <c r="C41" s="2" t="n"/>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>马克思的核心主张</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="n"/>
+      <c r="F41" s="2" t="n"/>
+      <c r="G41" s="2" t="n"/>
+      <c r="H41" s="2" t="n"/>
+      <c r="I41" s="2" t="n"/>
+      <c r="J41" s="2" t="n"/>
+      <c r="K41" s="2" t="n"/>
+      <c r="L41" s="2" t="n"/>
+      <c r="M41" s="2" t="n"/>
+    </row>
+    <row r="42" s="3">
+      <c r="B42" s="2" t="n"/>
+      <c r="C42" s="2" t="n"/>
+      <c r="D42" s="2" t="n"/>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>调节物质变换：###应当合理地调节人与自然之间的物质变换###（填写马克思的主张）</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="n"/>
+      <c r="G42" s="2" t="n"/>
+      <c r="H42" s="2" t="n"/>
+      <c r="I42" s="2" t="n"/>
+      <c r="J42" s="2" t="n"/>
+      <c r="K42" s="2" t="n"/>
+      <c r="L42" s="2" t="n"/>
+      <c r="M42" s="2" t="n"/>
+    </row>
+    <row r="43" s="3">
+      <c r="B43" s="2" t="n"/>
+      <c r="C43" s="2" t="n"/>
+      <c r="D43" s="2" t="n"/>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>最适合的条件：###在最无愧于和最适合人类本性的条件下进行这种物质变换###（填写条件）</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="n"/>
+      <c r="G43" s="2" t="n"/>
+      <c r="H43" s="2" t="n"/>
+      <c r="I43" s="2" t="n"/>
+      <c r="J43" s="2" t="n"/>
+      <c r="K43" s="2" t="n"/>
+      <c r="L43" s="2" t="n"/>
+      <c r="M43" s="2" t="n"/>
+    </row>
+    <row r="44" s="3">
+      <c r="B44" s="2" t="n"/>
+      <c r="C44" s="2" t="n"/>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>当代实践的例证</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="n"/>
+      <c r="F44" s="2" t="n"/>
+      <c r="G44" s="2" t="n"/>
+      <c r="H44" s="2" t="n"/>
+      <c r="I44" s="2" t="n"/>
+      <c r="J44" s="2" t="n"/>
+      <c r="K44" s="2" t="n"/>
+      <c r="L44" s="2" t="n"/>
+      <c r="M44" s="2" t="n"/>
+    </row>
+    <row r="45" s="3">
+      <c r="B45" s="2" t="n"/>
+      <c r="C45" s="2" t="n"/>
+      <c r="D45" s="2" t="n"/>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>“在公园中留荒野”正是###坚持人与自然和谐共生的体现###（填写体现的理念）</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="n"/>
+      <c r="G45" s="2" t="n"/>
+      <c r="H45" s="2" t="n"/>
+      <c r="I45" s="2" t="n"/>
+      <c r="J45" s="2" t="n"/>
+      <c r="K45" s="2" t="n"/>
+      <c r="L45" s="2" t="n"/>
+      <c r="M45" s="2" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/Note/输出.xlsx
+++ b/Note/输出.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="23040" windowHeight="9180" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="11520" windowHeight="9180" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待处理" sheetId="1" state="visible" r:id="rId1"/>
@@ -621,17 +621,16 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1012,832 +1011,647 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M45"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9.66666666666667" defaultRowHeight="14.4"/>
+  <dimension ref="A1:H86"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.888888888888889" defaultRowHeight="14.4"/>
   <cols>
-    <col width="9.66666666666667" customWidth="1" style="3" min="1" max="16384"/>
+    <col width="9.66666666666667" customWidth="1" style="1" min="1" max="1"/>
+    <col width="8.888888888888889" customWidth="1" style="1" min="2" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" s="3">
-      <c r="A1" s="4">
+    <row r="1" customFormat="1" s="1">
+      <c r="A1" s="3">
         <f>SUM(B1:AZ1)</f>
         <v/>
       </c>
-      <c r="B1" s="4">
+      <c r="B1" s="3">
         <f>COUNTA(B2:B2220)/COLUMN()</f>
         <v/>
       </c>
-      <c r="C1" s="4">
+      <c r="C1" s="3">
         <f>COUNTA(C2:C2220)/COLUMN()</f>
         <v/>
       </c>
-      <c r="D1" s="4">
+      <c r="D1" s="3">
         <f>COUNTA(D2:D2220)/COLUMN()</f>
         <v/>
       </c>
-      <c r="E1" s="4">
+      <c r="E1" s="3">
         <f>COUNTA(E2:E2220)/COLUMN()</f>
         <v/>
       </c>
-      <c r="F1" s="4">
+      <c r="F1" s="3">
         <f>COUNTA(F2:F2220)/COLUMN()</f>
         <v/>
       </c>
-      <c r="G1" s="4">
+      <c r="G1" s="3">
         <f>COUNTA(G2:G2220)/COLUMN()</f>
         <v/>
       </c>
-      <c r="H1" s="4">
+      <c r="H1" s="3">
         <f>COUNTA(H2:H2220)/COLUMN()</f>
         <v/>
       </c>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
-    </row>
-    <row r="2" s="3">
-      <c r="A2" s="2">
+    </row>
+    <row r="2" customFormat="1" s="1">
+      <c r="A2" s="1">
         <f t="array" ref="A2">_wpsfn.SHEETSNAME(A1)</f>
         <v/>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>防沙治沙是恢复原貌### ###</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="2" t="n"/>
-      <c r="H2" s="2" t="n"/>
-      <c r="I2" s="2" t="n"/>
-      <c r="J2" s="2" t="n"/>
-      <c r="K2" s="2" t="n"/>
-      <c r="L2" s="2" t="n"/>
-    </row>
-    <row r="3" s="3">
-      <c r="A3" s="2" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>一、总的核心原则</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="n"/>
-      <c r="G3" s="2" t="n"/>
-      <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-    </row>
-    <row r="4" s="3">
-      <c r="A4" s="2" t="n"/>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>生态保护和修复既要###尊重客观规律###（填写核心原则）</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
-      <c r="G4" s="2" t="n"/>
-      <c r="H4" s="2" t="n"/>
-      <c r="I4" s="2" t="n"/>
-      <c r="J4" s="2" t="n"/>
-      <c r="K4" s="2" t="n"/>
-      <c r="L4" s="2" t="n"/>
-    </row>
-    <row r="5" s="3">
-      <c r="A5" s="2" t="n"/>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>也要###充分发挥主观能动性###（填写核心原则）</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="n"/>
-      <c r="G5" s="2" t="n"/>
-      <c r="H5" s="2" t="n"/>
-      <c r="I5" s="2" t="n"/>
-      <c r="J5" s="2" t="n"/>
-      <c r="K5" s="2" t="n"/>
-      <c r="L5" s="2" t="n"/>
-    </row>
-    <row r="6" s="3">
-      <c r="A6" s="2" t="n"/>
-      <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>二、尊重客观规律是前提</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="n"/>
-      <c r="H6" s="2" t="n"/>
-      <c r="I6" s="2" t="n"/>
-      <c r="J6" s="2" t="n"/>
-      <c r="K6" s="2" t="n"/>
-      <c r="L6" s="2" t="n"/>
-    </row>
-    <row r="7" s="3">
-      <c r="A7" s="2" t="n"/>
-      <c r="B7" s="2" t="n"/>
-      <c r="C7" s="2" t="n"/>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>基本定位：###尊重客观规律###是正确发挥主观能动性的前提（填写核心概念）</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
-      <c r="G7" s="2" t="n"/>
-      <c r="H7" s="2" t="n"/>
-      <c r="I7" s="2" t="n"/>
-      <c r="J7" s="2" t="n"/>
-      <c r="K7" s="2" t="n"/>
-      <c r="L7" s="2" t="n"/>
-    </row>
-    <row r="8" s="3">
-      <c r="A8" s="2" t="n"/>
-      <c r="B8" s="2" t="n"/>
-      <c r="C8" s="2" t="n"/>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>根本定义：规律是事物变化发展过程中###内在的、本质的、必然的联系###（填写规律的本质特征）</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="2" t="n"/>
-      <c r="G8" s="2" t="n"/>
-      <c r="H8" s="2" t="n"/>
-      <c r="I8" s="2" t="n"/>
-      <c r="J8" s="2" t="n"/>
-      <c r="K8" s="2" t="n"/>
-      <c r="L8" s="2" t="n"/>
-    </row>
-    <row r="9" s="3">
-      <c r="A9" s="2" t="n"/>
-      <c r="B9" s="2" t="n"/>
-      <c r="C9" s="2" t="n"/>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>###正确行动的基础###（填写作用或地位）</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="n"/>
-      <c r="F9" s="2" t="n"/>
-      <c r="G9" s="2" t="n"/>
-      <c r="H9" s="2" t="n"/>
-      <c r="I9" s="2" t="n"/>
-      <c r="J9" s="2" t="n"/>
-      <c r="K9" s="2" t="n"/>
-      <c r="L9" s="2" t="n"/>
-    </row>
-    <row r="10" s="3">
-      <c r="A10" s="2" t="n"/>
-      <c r="B10" s="2" t="n"/>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n"/>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>认识世界的前提：人们只有在###认识和掌握客观规律###的基础上，才能正确地认识世界（填写前提条件）</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="n"/>
-      <c r="G10" s="2" t="n"/>
-      <c r="H10" s="2" t="n"/>
-      <c r="I10" s="2" t="n"/>
-      <c r="J10" s="2" t="n"/>
-      <c r="K10" s="2" t="n"/>
-      <c r="L10" s="2" t="n"/>
-    </row>
-    <row r="11" s="3">
-      <c r="A11" s="2" t="n"/>
-      <c r="B11" s="2" t="n"/>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2" t="n"/>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>改造世界的前提：才能有效地改造世界</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="n"/>
-      <c r="G11" s="2" t="n"/>
-      <c r="H11" s="2" t="n"/>
-      <c r="I11" s="2" t="n"/>
-      <c r="J11" s="2" t="n"/>
-      <c r="K11" s="2" t="n"/>
-      <c r="L11" s="2" t="n"/>
-    </row>
-    <row r="12" s="3">
-      <c r="A12" s="2" t="n"/>
-      <c r="B12" s="2" t="n"/>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>三、必须充分发挥主观能动性</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="n"/>
-      <c r="E12" s="2" t="n"/>
-      <c r="F12" s="2" t="n"/>
-      <c r="G12" s="2" t="n"/>
-      <c r="H12" s="2" t="n"/>
-      <c r="I12" s="2" t="n"/>
-      <c r="J12" s="2" t="n"/>
-      <c r="K12" s="2" t="n"/>
-      <c r="L12" s="2" t="n"/>
-    </row>
-    <row r="13" s="3">
-      <c r="A13" s="2" t="n"/>
-      <c r="B13" s="2" t="n"/>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>能动性的关键作用：只有###充分发挥主观能动性###，才能正确认识和利用客观规律（填写关键作用的前提）</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="n"/>
-      <c r="F13" s="2" t="n"/>
-      <c r="G13" s="2" t="n"/>
-      <c r="H13" s="2" t="n"/>
-      <c r="I13" s="2" t="n"/>
-      <c r="J13" s="2" t="n"/>
-      <c r="K13" s="2" t="n"/>
-      <c r="L13" s="2" t="n"/>
-    </row>
-    <row r="14" s="3">
-      <c r="A14" s="2" t="n"/>
-      <c r="B14" s="2" t="n"/>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>对规律客观性的正确态度</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="n"/>
-      <c r="F14" s="2" t="n"/>
-      <c r="G14" s="2" t="n"/>
-      <c r="H14" s="2" t="n"/>
-      <c r="I14" s="2" t="n"/>
-      <c r="J14" s="2" t="n"/>
-      <c r="K14" s="2" t="n"/>
-      <c r="L14" s="2" t="n"/>
-    </row>
-    <row r="15" s="3">
-      <c r="A15" s="2" t="n"/>
-      <c r="B15" s="2" t="n"/>
-      <c r="C15" s="2" t="n"/>
-      <c r="D15" s="2" t="n"/>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>非消极无为：###承认规律的客观性###，并非说人在规律面前无能为力、无所作为（填写正确观点）</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="n"/>
-      <c r="G15" s="2" t="n"/>
-      <c r="H15" s="2" t="n"/>
-      <c r="I15" s="2" t="n"/>
-      <c r="J15" s="2" t="n"/>
-      <c r="K15" s="2" t="n"/>
-      <c r="L15" s="2" t="n"/>
-    </row>
-    <row r="16" s="3">
-      <c r="A16" s="2" t="n"/>
-      <c r="B16" s="2" t="n"/>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="n"/>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>###人的能动作用###（填写人的能力）</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="n"/>
-      <c r="G16" s="2" t="n"/>
-      <c r="H16" s="2" t="n"/>
-      <c r="I16" s="2" t="n"/>
-      <c r="J16" s="2" t="n"/>
-      <c r="K16" s="2" t="n"/>
-      <c r="L16" s="2" t="n"/>
-    </row>
-    <row r="17" s="3">
-      <c r="A17" s="2" t="n"/>
-      <c r="B17" s="2" t="n"/>
-      <c r="C17" s="2" t="n"/>
-      <c r="D17" s="2" t="n"/>
-      <c r="E17" s="2" t="n"/>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>能够认识规律：###人能够通过自觉活动去认识规律###（填写人的能力）</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="n"/>
-      <c r="H17" s="2" t="n"/>
-      <c r="I17" s="2" t="n"/>
-      <c r="J17" s="2" t="n"/>
-      <c r="K17" s="2" t="n"/>
-      <c r="L17" s="2" t="n"/>
-    </row>
-    <row r="18" s="3">
-      <c r="B18" s="2" t="n"/>
-      <c r="C18" s="2" t="n"/>
-      <c r="D18" s="2" t="n"/>
-      <c r="E18" s="2" t="n"/>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>能够改造世界：并能###按照客观规律去改造世界###，以满足自身的需要（填写改造世界的方式）</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="n"/>
-      <c r="H18" s="2" t="n"/>
-      <c r="I18" s="2" t="n"/>
-      <c r="J18" s="2" t="n"/>
-      <c r="K18" s="2" t="n"/>
-      <c r="L18" s="2" t="n"/>
-    </row>
-    <row r="19" s="3">
-      <c r="B19" s="2" t="n"/>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>四、实例：自然生态系统的治理</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="n"/>
-      <c r="E19" s="2" t="n"/>
-      <c r="F19" s="2" t="n"/>
-      <c r="G19" s="2" t="n"/>
-      <c r="H19" s="2" t="n"/>
-      <c r="I19" s="2" t="n"/>
-      <c r="J19" s="2" t="n"/>
-      <c r="K19" s="2" t="n"/>
-      <c r="L19" s="2" t="n"/>
-    </row>
-    <row r="20" s="3">
-      <c r="B20" s="2" t="n"/>
-      <c r="C20" s="2" t="n"/>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>生态系统的基本属性</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="n"/>
-      <c r="F20" s="2" t="n"/>
-      <c r="G20" s="2" t="n"/>
-      <c r="H20" s="2" t="n"/>
-      <c r="I20" s="2" t="n"/>
-      <c r="J20" s="2" t="n"/>
-      <c r="K20" s="2" t="n"/>
-      <c r="L20" s="2" t="n"/>
-    </row>
-    <row r="21" s="3">
-      <c r="B21" s="2" t="n"/>
-      <c r="C21" s="2" t="n"/>
-      <c r="D21" s="2" t="n"/>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>有机生命躯体：###自然生态系统是一个有机生命躯体###（填写生态系统的比喻或属性）</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="n"/>
-      <c r="G21" s="2" t="n"/>
-      <c r="H21" s="2" t="n"/>
-      <c r="I21" s="2" t="n"/>
-      <c r="J21" s="2" t="n"/>
-      <c r="K21" s="2" t="n"/>
-      <c r="L21" s="2" t="n"/>
-    </row>
-    <row r="22" s="3">
-      <c r="B22" s="2" t="n"/>
-      <c r="C22" s="2" t="n"/>
-      <c r="D22" s="2" t="n"/>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>具有客观规律：###有其自身发展演化的客观规律###，要充分尊重和顺应自然（填写生态系统的特点）</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="n"/>
-      <c r="G22" s="2" t="n"/>
-      <c r="H22" s="2" t="n"/>
-      <c r="I22" s="2" t="n"/>
-      <c r="J22" s="2" t="n"/>
-      <c r="K22" s="2" t="n"/>
-      <c r="L22" s="2" t="n"/>
-    </row>
-    <row r="23" s="3">
-      <c r="B23" s="2" t="n"/>
-      <c r="C23" s="2" t="n"/>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>荒漠治理的辩证实践</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="n"/>
-      <c r="F23" s="2" t="n"/>
-      <c r="G23" s="2" t="n"/>
-      <c r="H23" s="2" t="n"/>
-      <c r="I23" s="2" t="n"/>
-      <c r="J23" s="2" t="n"/>
-      <c r="K23" s="2" t="n"/>
-      <c r="L23" s="2" t="n"/>
-    </row>
-    <row r="24" s="3">
-      <c r="B24" s="2" t="n"/>
-      <c r="C24" s="2" t="n"/>
-      <c r="D24" s="2" t="n"/>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>认识到荒漠的价值：###认识到天然的荒漠也是一种有价值的生态系统###（填写对荒漠的认识）</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="n"/>
-      <c r="G24" s="2" t="n"/>
-      <c r="H24" s="2" t="n"/>
-      <c r="I24" s="2" t="n"/>
-      <c r="J24" s="2" t="n"/>
-      <c r="K24" s="2" t="n"/>
-      <c r="L24" s="2" t="n"/>
-    </row>
-    <row r="25" s="3">
-      <c r="B25" s="2" t="n"/>
-      <c r="C25" s="2" t="n"/>
-      <c r="D25" s="2" t="n"/>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>治理实践中的平衡</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="n"/>
-      <c r="G25" s="2" t="n"/>
-      <c r="H25" s="2" t="n"/>
-      <c r="I25" s="2" t="n"/>
-      <c r="J25" s="2" t="n"/>
-      <c r="K25" s="2" t="n"/>
-      <c r="L25" s="2" t="n"/>
-    </row>
-    <row r="26" s="3">
-      <c r="B26" s="2" t="n"/>
-      <c r="C26" s="2" t="n"/>
-      <c r="D26" s="2" t="n"/>
-      <c r="E26" s="2" t="n"/>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>主动治理：###人们在发挥主观能动性治理荒漠化的同时###（填写治理实践）</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="n"/>
-      <c r="H26" s="2" t="n"/>
-      <c r="I26" s="2" t="n"/>
-      <c r="J26" s="2" t="n"/>
-      <c r="K26" s="2" t="n"/>
-      <c r="L26" s="2" t="n"/>
-    </row>
-    <row r="27" s="3">
-      <c r="B27" s="2" t="n"/>
-      <c r="C27" s="2" t="n"/>
-      <c r="D27" s="2" t="n"/>
-      <c r="E27" s="2" t="n"/>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>顺应与保留：###也保留了地球上原有的沙漠和荒漠###（填写治理实践的另一面）</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="n"/>
-      <c r="H27" s="2" t="n"/>
-      <c r="I27" s="2" t="n"/>
-      <c r="J27" s="2" t="n"/>
-      <c r="K27" s="2" t="n"/>
-      <c r="L27" s="2" t="n"/>
-    </row>
-    <row r="28" s="3">
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>人与自然的关系### ###</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="n"/>
-      <c r="D28" s="2" t="n"/>
-      <c r="E28" s="2" t="n"/>
-      <c r="F28" s="2" t="n"/>
-      <c r="G28" s="2" t="n"/>
-      <c r="H28" s="2" t="n"/>
-      <c r="I28" s="2" t="n"/>
-      <c r="J28" s="2" t="n"/>
-      <c r="K28" s="2" t="n"/>
-      <c r="L28" s="2" t="n"/>
-      <c r="M28" s="2" t="n"/>
-    </row>
-    <row r="29" s="3">
-      <c r="B29" s="2" t="n"/>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>一、自然地理环境的基础性地位：作为生存与发展的根本条件</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="n"/>
-      <c r="E29" s="2" t="n"/>
-      <c r="F29" s="2" t="n"/>
-      <c r="G29" s="2" t="n"/>
-      <c r="H29" s="2" t="n"/>
-      <c r="I29" s="2" t="n"/>
-      <c r="J29" s="2" t="n"/>
-      <c r="K29" s="2" t="n"/>
-      <c r="L29" s="2" t="n"/>
-      <c r="M29" s="2" t="n"/>
-    </row>
-    <row r="30" s="3">
-      <c r="B30" s="2" t="n"/>
-      <c r="C30" s="2" t="n"/>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>永恒且必要的条件：###自然地理环境是人类社会生存和发展永恒的、必要的条件###（填写自然地理环境的地位）</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="n"/>
-      <c r="F30" s="2" t="n"/>
-      <c r="G30" s="2" t="n"/>
-      <c r="H30" s="2" t="n"/>
-      <c r="I30" s="2" t="n"/>
-      <c r="J30" s="2" t="n"/>
-      <c r="K30" s="2" t="n"/>
-      <c r="L30" s="2" t="n"/>
-      <c r="M30" s="2" t="n"/>
-    </row>
-    <row r="31" s="3">
-      <c r="B31" s="2" t="n"/>
-      <c r="C31" s="2" t="n"/>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>生活与生产的自然基础：###是人们生活和生产的自然基础###（填写自然地理环境的作用）</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="n"/>
-      <c r="F31" s="2" t="n"/>
-      <c r="G31" s="2" t="n"/>
-      <c r="H31" s="2" t="n"/>
-      <c r="I31" s="2" t="n"/>
-      <c r="J31" s="2" t="n"/>
-      <c r="K31" s="2" t="n"/>
-      <c r="L31" s="2" t="n"/>
-      <c r="M31" s="2" t="n"/>
-    </row>
-    <row r="32" s="3">
-      <c r="B32" s="2" t="n"/>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>二、生态平衡与资源利用的重要性</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="n"/>
-      <c r="E32" s="2" t="n"/>
-      <c r="F32" s="2" t="n"/>
-      <c r="G32" s="2" t="n"/>
-      <c r="H32" s="2" t="n"/>
-      <c r="I32" s="2" t="n"/>
-      <c r="J32" s="2" t="n"/>
-      <c r="K32" s="2" t="n"/>
-      <c r="L32" s="2" t="n"/>
-      <c r="M32" s="2" t="n"/>
-    </row>
-    <row r="33" s="3">
-      <c r="B33" s="2" t="n"/>
-      <c r="C33" s="2" t="n"/>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>生态平衡的社会作用：###自然生态平衡对社会生活起着重要作用###（填写生态平衡的作用）</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="n"/>
-      <c r="F33" s="2" t="n"/>
-      <c r="G33" s="2" t="n"/>
-      <c r="H33" s="2" t="n"/>
-      <c r="I33" s="2" t="n"/>
-      <c r="J33" s="2" t="n"/>
-      <c r="K33" s="2" t="n"/>
-      <c r="L33" s="2" t="n"/>
-      <c r="M33" s="2" t="n"/>
-    </row>
-    <row r="34" s="3">
-      <c r="B34" s="2" t="n"/>
-      <c r="C34" s="2" t="n"/>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>合理利用与保护的必要性：###合理地利用自然资源，保护生态平衡，是社会得以正常发展的必要条件###（填写必要性）</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="n"/>
-      <c r="F34" s="2" t="n"/>
-      <c r="G34" s="2" t="n"/>
-      <c r="H34" s="2" t="n"/>
-      <c r="I34" s="2" t="n"/>
-      <c r="J34" s="2" t="n"/>
-      <c r="K34" s="2" t="n"/>
-      <c r="L34" s="2" t="n"/>
-      <c r="M34" s="2" t="n"/>
-    </row>
-    <row r="35" s="3">
-      <c r="B35" s="2" t="n"/>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>三、人类实践必须遵循自然规律</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="n"/>
-      <c r="E35" s="2" t="n"/>
-      <c r="F35" s="2" t="n"/>
-      <c r="G35" s="2" t="n"/>
-      <c r="H35" s="2" t="n"/>
-      <c r="I35" s="2" t="n"/>
-      <c r="J35" s="2" t="n"/>
-      <c r="K35" s="2" t="n"/>
-      <c r="L35" s="2" t="n"/>
-      <c r="M35" s="2" t="n"/>
-    </row>
-    <row r="36" s="3">
-      <c r="B36" s="2" t="n"/>
-      <c r="C36" s="2" t="n"/>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>改造世界的双重性</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="n"/>
-      <c r="F36" s="2" t="n"/>
-      <c r="G36" s="2" t="n"/>
-      <c r="H36" s="2" t="n"/>
-      <c r="I36" s="2" t="n"/>
-      <c r="J36" s="2" t="n"/>
-      <c r="K36" s="2" t="n"/>
-      <c r="L36" s="2" t="n"/>
-      <c r="M36" s="2" t="n"/>
-    </row>
-    <row r="37" s="3">
-      <c r="B37" s="2" t="n"/>
-      <c r="C37" s="2" t="n"/>
-      <c r="D37" s="2" t="n"/>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>按意愿改造：###人类在实践活动中按照自己的意愿改造世界###（填写人类实践的特点）</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="n"/>
-      <c r="G37" s="2" t="n"/>
-      <c r="H37" s="2" t="n"/>
-      <c r="I37" s="2" t="n"/>
-      <c r="J37" s="2" t="n"/>
-      <c r="K37" s="2" t="n"/>
-      <c r="L37" s="2" t="n"/>
-      <c r="M37" s="2" t="n"/>
-    </row>
-    <row r="38" s="3">
-      <c r="B38" s="2" t="n"/>
-      <c r="C38" s="2" t="n"/>
-      <c r="D38" s="2" t="n"/>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>必须遵循规律：的同时###必须遵循自然规律###（填写必须遵循的内容）</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="n"/>
-      <c r="G38" s="2" t="n"/>
-      <c r="H38" s="2" t="n"/>
-      <c r="I38" s="2" t="n"/>
-      <c r="J38" s="2" t="n"/>
-      <c r="K38" s="2" t="n"/>
-      <c r="L38" s="2" t="n"/>
-      <c r="M38" s="2" t="n"/>
-    </row>
-    <row r="39" s="3">
-      <c r="B39" s="2" t="n"/>
-      <c r="C39" s="2" t="n"/>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>违背规律的后果：否则将会###导致人与自然关系的失衡###（填写后果）</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="n"/>
-      <c r="F39" s="2" t="n"/>
-      <c r="G39" s="2" t="n"/>
-      <c r="H39" s="2" t="n"/>
-      <c r="I39" s="2" t="n"/>
-      <c r="J39" s="2" t="n"/>
-      <c r="K39" s="2" t="n"/>
-      <c r="L39" s="2" t="n"/>
-      <c r="M39" s="2" t="n"/>
-    </row>
-    <row r="40" s="3">
-      <c r="B40" s="2" t="n"/>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>四、马克思的观点及和谐共生的体现</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="n"/>
-      <c r="E40" s="2" t="n"/>
-      <c r="F40" s="2" t="n"/>
-      <c r="G40" s="2" t="n"/>
-      <c r="H40" s="2" t="n"/>
-      <c r="I40" s="2" t="n"/>
-      <c r="J40" s="2" t="n"/>
-      <c r="K40" s="2" t="n"/>
-      <c r="L40" s="2" t="n"/>
-      <c r="M40" s="2" t="n"/>
-    </row>
-    <row r="41" s="3">
-      <c r="B41" s="2" t="n"/>
-      <c r="C41" s="2" t="n"/>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>马克思的核心主张</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="n"/>
-      <c r="F41" s="2" t="n"/>
-      <c r="G41" s="2" t="n"/>
-      <c r="H41" s="2" t="n"/>
-      <c r="I41" s="2" t="n"/>
-      <c r="J41" s="2" t="n"/>
-      <c r="K41" s="2" t="n"/>
-      <c r="L41" s="2" t="n"/>
-      <c r="M41" s="2" t="n"/>
-    </row>
-    <row r="42" s="3">
-      <c r="B42" s="2" t="n"/>
-      <c r="C42" s="2" t="n"/>
-      <c r="D42" s="2" t="n"/>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>调节物质变换：###应当合理地调节人与自然之间的物质变换###（填写马克思的主张）</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="n"/>
-      <c r="G42" s="2" t="n"/>
-      <c r="H42" s="2" t="n"/>
-      <c r="I42" s="2" t="n"/>
-      <c r="J42" s="2" t="n"/>
-      <c r="K42" s="2" t="n"/>
-      <c r="L42" s="2" t="n"/>
-      <c r="M42" s="2" t="n"/>
-    </row>
-    <row r="43" s="3">
-      <c r="B43" s="2" t="n"/>
-      <c r="C43" s="2" t="n"/>
-      <c r="D43" s="2" t="n"/>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>最适合的条件：###在最无愧于和最适合人类本性的条件下进行这种物质变换###（填写条件）</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="n"/>
-      <c r="G43" s="2" t="n"/>
-      <c r="H43" s="2" t="n"/>
-      <c r="I43" s="2" t="n"/>
-      <c r="J43" s="2" t="n"/>
-      <c r="K43" s="2" t="n"/>
-      <c r="L43" s="2" t="n"/>
-      <c r="M43" s="2" t="n"/>
-    </row>
-    <row r="44" s="3">
-      <c r="B44" s="2" t="n"/>
-      <c r="C44" s="2" t="n"/>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>当代实践的例证</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="n"/>
-      <c r="F44" s="2" t="n"/>
-      <c r="G44" s="2" t="n"/>
-      <c r="H44" s="2" t="n"/>
-      <c r="I44" s="2" t="n"/>
-      <c r="J44" s="2" t="n"/>
-      <c r="K44" s="2" t="n"/>
-      <c r="L44" s="2" t="n"/>
-      <c r="M44" s="2" t="n"/>
-    </row>
-    <row r="45" s="3">
-      <c r="B45" s="2" t="n"/>
-      <c r="C45" s="2" t="n"/>
-      <c r="D45" s="2" t="n"/>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>“在公园中留荒野”正是###坚持人与自然和谐共生的体现###（填写体现的理念）</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="n"/>
-      <c r="G45" s="2" t="n"/>
-      <c r="H45" s="2" t="n"/>
-      <c r="I45" s="2" t="n"/>
-      <c r="J45" s="2" t="n"/>
-      <c r="K45" s="2" t="n"/>
-      <c r="L45" s="2" t="n"/>
-      <c r="M45" s="2" t="n"/>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>平凡岗位与实现社会价值### ###</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" customFormat="1" s="1">
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>一、根本尺度的客观标准：核心依据：是否符合社会规律、促进历史进步</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" customFormat="1" s="1">
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>实践活动的检验标准：看一个人的实践活动是否###符合社会发展的客观规律###（填写实践活动标准）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" customFormat="1" s="1">
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>历史作用的检验标准：看一个人的实践活动是否###促进了历史的进步###（填写历史作用标准）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" customFormat="1" s="1">
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>二、当今社会的具体衡量标准：核心标准：为国家社会奉献，为人民服务</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" customFormat="1" s="1">
+      <c r="D7" s="1" t="inlineStr">
+        <is>
+          <t>奉献才智：看一个人是否用自己的劳动和聪明才智###为国家和社会真诚奉献###（填写奉献目标）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" customFormat="1" s="1">
+      <c r="D8" s="1" t="inlineStr">
+        <is>
+          <t>尽心服务：看一个人是否为###人民群众###（填写服务对象）尽心尽力服务</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" customFormat="1" s="1">
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>三、对奉献与平凡价值的阐释</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" customFormat="1" s="1">
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>核心观点：###奉献即成功，平凡孕伟大###（填写核心观点）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" customFormat="1" s="1">
+      <c r="E11" s="1" t="inlineStr">
+        <is>
+          <t>成功的本质：成功在于###奉献###（填写成功本质）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" customFormat="1" s="1">
+      <c r="E12" s="1" t="inlineStr">
+        <is>
+          <t>伟大的源泉：平凡孕育###伟大###（填写源泉指向）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" customFormat="1" s="1">
+      <c r="D13" s="1" t="inlineStr">
+        <is>
+          <t>对普通劳动者的激励与肯定</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" customFormat="1" s="1">
+      <c r="E14" s="1" t="inlineStr">
+        <is>
+          <t>实现价值的前提：只要有###志气、有闯劲###（填写前提条件）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" customFormat="1" s="1">
+      <c r="E15" s="1" t="inlineStr">
+        <is>
+          <t>实现价值的场域：普通劳动者都可以在宽广舞台上###实现自己的人生价值###（填写实现目标）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" customFormat="1" s="1">
+      <c r="E16" s="1" t="inlineStr">
+        <is>
+          <t>实现价值的方式：在平凡岗位上###干出不平凡的业绩###（填写实现方式）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" customFormat="1" s="1">
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>弘扬志愿精神### ###</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" customFormat="1" s="1">
+      <c r="C18" s="1" t="inlineStr">
+        <is>
+          <t>一、志愿服务的精神内涵</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" customFormat="1" s="1">
+      <c r="D19" s="1" t="inlineStr">
+        <is>
+          <t>核心定义：志愿服务的精神是###奉献、友爱、互助、进步###（填写精神内涵）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" customFormat="1" s="1">
+      <c r="D20" s="1" t="inlineStr">
+        <is>
+          <t>精神精髓：核心是###奉献###（填写精神精髓）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" customFormat="1" s="1">
+      <c r="C21" s="1" t="inlineStr">
+        <is>
+          <t>二、志愿服务活动的双重作用</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" customFormat="1" s="1">
+      <c r="D22" s="1" t="inlineStr">
+        <is>
+          <t>对社会的作用</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" customFormat="1" s="1">
+      <c r="E23" s="1" t="inlineStr">
+        <is>
+          <t>直接帮助：###帮助了他人###（填写作用）</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" customFormat="1" s="1">
+      <c r="E24" s="1" t="inlineStr">
+        <is>
+          <t>服务社会：###服务了社会###（填写作用）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" customFormat="1" s="1">
+      <c r="E25" s="1" t="inlineStr">
+        <is>
+          <t>道德提升：###推动了社会道德水平的提高###（填写作用）</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" customFormat="1" s="1">
+      <c r="D26" s="1" t="inlineStr">
+        <is>
+          <t>对个人的作用</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" customFormat="1" s="1">
+      <c r="E27" s="1" t="inlineStr">
+        <is>
+          <t>视为义务与职责：把为社会和他人的服务看作###自己应尽的义务和光荣的职责###（填写视为内容）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" customFormat="1" s="1">
+      <c r="E28" s="1" t="inlineStr">
+        <is>
+          <t>获得内在回报</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" customFormat="1" s="1">
+      <c r="F29" s="1" t="inlineStr">
+        <is>
+          <t>得到成就感：从服务社会和帮助他人中获得###成就感###（填写获得内容）</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" customFormat="1" s="1">
+      <c r="F30" s="1" t="inlineStr">
+        <is>
+          <t>得到幸福感：获得###幸福感###（填写获得内容）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" customFormat="1" s="1">
+      <c r="C31" s="1" t="inlineStr">
+        <is>
+          <t>三、对新时代青年的核心要求</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" customFormat="1" s="1">
+      <c r="D32" s="1" t="inlineStr">
+        <is>
+          <t>结合自身提供服务</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" customFormat="1" s="1">
+      <c r="E33" s="1" t="inlineStr">
+        <is>
+          <t>匹配能力特长：应结合自身的###能力、专业、特长###（填写结合内容）</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" customFormat="1" s="1">
+      <c r="E34" s="1" t="inlineStr">
+        <is>
+          <t>提供优质服务：在最需要的地方提供###优质高效的服务###（填写服务要求）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" customFormat="1" s="1">
+      <c r="D35" s="1" t="inlineStr">
+        <is>
+          <t>关爱特定群体：为最需要关爱的群体###送温暖、献爱心###（填写关爱方式）</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" customFormat="1" s="1">
+      <c r="D36" s="1" t="inlineStr">
+        <is>
+          <t>实现自我成长：增长###知识与才干###（填写增长内容）</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" customFormat="1" s="1">
+      <c r="E37" s="1" t="inlineStr">
+        <is>
+          <t>在志愿服务中###长知识###（填写成长内容）</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" customFormat="1" s="1">
+      <c r="E38" s="1" t="inlineStr">
+        <is>
+          <t>###强本领###（填写成长内容）</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" customFormat="1" s="1">
+      <c r="E39" s="1" t="inlineStr">
+        <is>
+          <t>###增才干###（填写成长内容）</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" customFormat="1" s="1">
+      <c r="B40" s="1" t="inlineStr">
+        <is>
+          <t>为什么要推进平等有序的世界多极化### ###</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" customFormat="1" s="1">
+      <c r="C41" s="1" t="inlineStr">
+        <is>
+          <t>一、世界多极化的基本定位：当代趋势与历史方向</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" customFormat="1" s="1">
+      <c r="D42" s="1" t="inlineStr">
+        <is>
+          <t>多极化是当今世界的###基本趋势###（填写趋势定位）</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" customFormat="1" s="1">
+      <c r="D43" s="1" t="inlineStr">
+        <is>
+          <t>也是###历史进步的方向###（填写方向定位）</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" customFormat="1" s="1">
+      <c r="C44" s="1" t="inlineStr">
+        <is>
+          <t>二、平等的世界多极化</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" customFormat="1" s="1">
+      <c r="D45" s="1" t="inlineStr">
+        <is>
+          <t>核心原则：国家不分大小强弱，均应在多极化进程中###平等参与、享受权利、发挥作用###（填写核心原则）</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" customFormat="1" s="1">
+      <c r="D46" s="1" t="inlineStr">
+        <is>
+          <t>具体目标与实践方向</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" customFormat="1" s="1">
+      <c r="E47" s="1" t="inlineStr">
+        <is>
+          <t>推进国际关系民主化：切实推进###国际关系民主化###（填写推进目标）</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" customFormat="1" s="1">
+      <c r="E48" s="1" t="inlineStr">
+        <is>
+          <t>增强发展中国家话语权：增强广大发展中国家的###代表性和发言权###（填写增强内容）</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" customFormat="1" s="1">
+      <c r="E49" s="1" t="inlineStr">
+        <is>
+          <t>反对霸权与强权：反对###霸权主义和强权政治###（填写反对对象）</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" customFormat="1" s="1">
+      <c r="C50" s="1" t="inlineStr">
+        <is>
+          <t>三、有序的世界多极化</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" customFormat="1" s="1">
+      <c r="D51" s="1" t="inlineStr">
+        <is>
+          <t>维护的三大核心支柱</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" customFormat="1" s="1">
+      <c r="E52" s="1" t="inlineStr">
+        <is>
+          <t>以联合国为核心：坚定维护###以联合国为核心的国际体系###（填写维护对象）</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" customFormat="1" s="1">
+      <c r="E53" s="1" t="inlineStr">
+        <is>
+          <t>以国际法为基础：维护###以国际法为基础的国际秩序###（填写维护对象）</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" customFormat="1" s="1">
+      <c r="E54" s="1" t="inlineStr">
+        <is>
+          <t>以宪章宗旨原则为基础：维护###以联合国宪章宗旨和原则为基础的国际关系基本准则###（填写维护对象）</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" customFormat="1" s="1">
+      <c r="D55" s="1" t="inlineStr">
+        <is>
+          <t>秉持的理念与反对的倾向</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" customFormat="1" s="1">
+      <c r="E56" s="1" t="inlineStr">
+        <is>
+          <t>秉持###真正多边主义###（填写秉持理念）</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" customFormat="1" s="1">
+      <c r="E57" s="1" t="inlineStr">
+        <is>
+          <t>反对错误倾向</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" customFormat="1" s="1">
+      <c r="D58" s="1" t="n"/>
+      <c r="E58" s="1" t="n"/>
+      <c r="F58" s="1" t="inlineStr">
+        <is>
+          <t>反对###阵营化###（填写反对倾向）</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" customFormat="1" s="1">
+      <c r="F59" s="1" t="inlineStr">
+        <is>
+          <t>反对###碎片化###（填写反对倾向）</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" customFormat="1" s="1">
+      <c r="F60" s="1" t="inlineStr">
+        <is>
+          <t>反对###无序化###（填写反对倾向）</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" customFormat="1" s="1">
+      <c r="C61" s="1" t="inlineStr">
+        <is>
+          <t>四、平等有序世界多极化的意义</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" customFormat="1" s="1">
+      <c r="D62" s="1" t="inlineStr">
+        <is>
+          <t>契合普遍诉求：契合了大多数国家和各国民众的###普遍诉求###（填写契合对象）</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" customFormat="1" s="1">
+      <c r="D63" s="1" t="inlineStr">
+        <is>
+          <t>指明未来方向：走向长治久安：为国际社会###从变乱交织走向长治久安###（填写方向转变）指明了方向</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" customFormat="1" s="1">
+      <c r="D64" s="1" t="inlineStr">
+        <is>
+          <t>提供重要路径</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" customFormat="1" s="1">
+      <c r="E65" s="1" t="inlineStr">
+        <is>
+          <t>推动构建全球治理体系：为推动构建###公正合理的全球治理体系###（填写体系性质）提供了重要路径</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" customFormat="1" s="1">
+      <c r="E66" s="1" t="inlineStr">
+        <is>
+          <t>推动构建人类命运共同体：为推动构建###人类命运共同体###（填写共同体类型）提供了重要路径</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" customFormat="1" s="1">
+      <c r="B67" s="1" t="inlineStr">
+        <is>
+          <t>为什么要坚守多边主义### ###</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" customFormat="1" s="1">
+      <c r="C68" s="1" t="inlineStr">
+        <is>
+          <t>一、历史所昭示的核心论断：多边主义的根本定位</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" customFormat="1" s="1">
+      <c r="D69" s="1" t="inlineStr">
+        <is>
+          <t>是人心所向：多边主义是###人心所向###（填写根本定位）</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" customFormat="1" s="1">
+      <c r="D70" s="1" t="inlineStr">
+        <is>
+          <t>是###大势所趋###（填写根本定位）</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" customFormat="1" s="1">
+      <c r="D71" s="1" t="inlineStr">
+        <is>
+          <t>关键依靠：对和平与发展的意义：是世界和平与发展的###重要依靠###（填写关键定位）</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" customFormat="1" s="1">
+      <c r="C72" s="1" t="inlineStr">
+        <is>
+          <t>二、当前世界面临的突出问题</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" customFormat="1" s="1">
+      <c r="D73" s="1" t="inlineStr">
+        <is>
+          <t>三大失衡失序</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" customFormat="1" s="1">
+      <c r="E74" s="1" t="inlineStr">
+        <is>
+          <t>###安全失序###（填写突出问题）</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" customFormat="1" s="1">
+      <c r="E75" s="1" t="inlineStr">
+        <is>
+          <t>###发展失衡###（填写突出问题）</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" customFormat="1" s="1">
+      <c r="E76" s="1" t="inlineStr">
+        <is>
+          <t>###治理失效###（填写突出问题）</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" customFormat="1" s="1">
+      <c r="D77" s="1" t="inlineStr">
+        <is>
+          <t>具体矛盾冲突频发</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" customFormat="1" s="1">
+      <c r="E78" s="1" t="inlineStr">
+        <is>
+          <t>###热点冲突###（填写具体矛盾）</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" customFormat="1" s="1">
+      <c r="E79" s="1" t="inlineStr">
+        <is>
+          <t>###大国对抗###（填写具体矛盾）</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" customFormat="1" s="1">
+      <c r="E80" s="1" t="inlineStr">
+        <is>
+          <t>###地缘矛盾###（填写具体矛盾）</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" customFormat="1" s="1">
+      <c r="D81" s="1" t="inlineStr">
+        <is>
+          <t>引发的普遍忧虑：对未来的担忧：人们对这个星球的未来更为###忧虑###（填写普遍情绪）</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" customFormat="1" s="1">
+      <c r="C82" s="1" t="inlineStr">
+        <is>
+          <t>三、应对变局的必然选择</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" customFormat="1" s="1">
+      <c r="D83" s="1" t="inlineStr">
+        <is>
+          <t>总体形势判断：国际形势###变乱交织###（填写形势特点）</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" customFormat="1" s="1">
+      <c r="D84" s="1" t="inlineStr">
+        <is>
+          <t>应对挑战的根本路径</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" customFormat="1" s="1">
+      <c r="E85" s="1" t="inlineStr">
+        <is>
+          <t>针对当下：应对当前全球性挑战，多边主义是###必然选择###（填写选择定位）</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" customFormat="1" s="1">
+      <c r="E86" s="1" t="inlineStr">
+        <is>
+          <t>面向未来：共创人类美好明天，多边主义是###必然选择###（填写选择定位）</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
